--- a/Excel Files IPEDS/Trimmed/c2011_trimmed_file.xlsx
+++ b/Excel Files IPEDS/Trimmed/c2011_trimmed_file.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L411"/>
+  <dimension ref="A1:M411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,35 +456,40 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>CTOTALW</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>CUNKNT</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>CBKAAT</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>CASIAT</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>CNHPIT</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>CHISPT</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>CWHITT</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
@@ -510,10 +515,10 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -522,9 +527,12 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -545,10 +553,10 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -560,9 +568,12 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>4</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -583,7 +594,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -595,12 +606,15 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -621,7 +635,7 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -636,9 +650,12 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>8</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -659,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -677,6 +694,9 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -712,9 +732,12 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -735,7 +758,7 @@
         <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -750,9 +773,12 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -773,7 +799,7 @@
         <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -785,12 +811,15 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
         <v>3</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -811,7 +840,7 @@
         <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -823,12 +852,15 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -849,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -864,9 +896,12 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -905,6 +940,9 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -925,7 +963,7 @@
         <v>9</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -940,9 +978,12 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>4</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -963,24 +1004,27 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>3</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
         <v>4</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1001,10 +1045,10 @@
         <v>12</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1016,9 +1060,12 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>6</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1039,24 +1086,27 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1077,10 +1127,10 @@
         <v>4</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1092,9 +1142,12 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>3</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1115,7 +1168,7 @@
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1130,9 +1183,12 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>3</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1153,7 +1209,7 @@
         <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1168,9 +1224,12 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1191,24 +1250,27 @@
         <v>7</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>4</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1229,24 +1291,27 @@
         <v>24</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
         <v>10</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1267,7 +1332,7 @@
         <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1279,12 +1344,15 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1308,7 +1376,7 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1320,9 +1388,12 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>3</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1346,7 +1417,7 @@
         <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1358,9 +1429,12 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>3</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1381,24 +1455,27 @@
         <v>7</v>
       </c>
       <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
         <v>3</v>
       </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1422,21 +1499,24 @@
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
         <v>3</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1460,21 +1540,24 @@
         <v>7</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
         <v>5</v>
       </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
         <v>18</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1498,21 +1581,24 @@
         <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
         <v>3</v>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" t="n">
         <v>15</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1533,24 +1619,27 @@
         <v>19</v>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
         <v>19</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1574,7 +1663,7 @@
         <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1586,9 +1675,12 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>5</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1615,10 +1707,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1627,6 +1719,9 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1647,24 +1742,27 @@
         <v>21</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
+        <v>17</v>
+      </c>
+      <c r="M32" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1685,24 +1783,27 @@
         <v>11</v>
       </c>
       <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
         <v>5</v>
       </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>3</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1732,15 +1833,18 @@
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
+        <v>7</v>
+      </c>
+      <c r="M34" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1761,24 +1865,27 @@
         <v>17</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
         <v>3</v>
       </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>14</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1799,24 +1906,27 @@
         <v>17</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>8</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1837,10 +1947,10 @@
         <v>10</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1849,12 +1959,15 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
+        <v>2</v>
+      </c>
+      <c r="L37" t="n">
         <v>3</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1875,24 +1988,27 @@
         <v>18</v>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
         <v>15</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1913,24 +2029,27 @@
         <v>15</v>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
         <v>10</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1951,24 +2070,27 @@
         <v>13</v>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
         <v>3</v>
       </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
         <v>13</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1989,11 +2111,11 @@
         <v>28</v>
       </c>
       <c r="F41" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" t="n">
         <v>5</v>
       </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
@@ -2004,9 +2126,12 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
         <v>20</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2027,24 +2152,27 @@
         <v>10</v>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
         <v>4</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>8</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2065,24 +2193,27 @@
         <v>6</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>4</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2103,10 +2234,10 @@
         <v>4</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2115,12 +2246,15 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
         <v>3</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2141,24 +2275,27 @@
         <v>7</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
+        <v>7</v>
+      </c>
+      <c r="M45" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2185,18 +2322,21 @@
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2220,13 +2360,13 @@
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2235,6 +2375,9 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2270,9 +2413,12 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2293,24 +2439,27 @@
         <v>18</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="n">
         <v>9</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2331,24 +2480,27 @@
         <v>20</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
         <v>22</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2387,6 +2539,9 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2425,6 +2580,9 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2445,7 +2603,7 @@
         <v>3</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2460,9 +2618,12 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
         <v>4</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2501,6 +2662,9 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2524,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2536,9 +2700,12 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
         <v>6</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2559,10 +2726,10 @@
         <v>5</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2574,9 +2741,12 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
+        <v>2</v>
+      </c>
+      <c r="M56" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2615,6 +2785,9 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2653,6 +2826,9 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2673,7 +2849,7 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2691,6 +2867,9 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2711,7 +2890,7 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2729,6 +2908,9 @@
         <v>0</v>
       </c>
       <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2749,13 +2931,13 @@
         <v>7</v>
       </c>
       <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
         <v>3</v>
       </c>
-      <c r="G61" t="n">
-        <v>1</v>
-      </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -2764,9 +2946,12 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2787,24 +2972,27 @@
         <v>18</v>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
         <v>6</v>
       </c>
-      <c r="L62" t="n">
+      <c r="M62" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2825,24 +3013,27 @@
         <v>2</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
+        <v>1</v>
+      </c>
+      <c r="M63" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2863,10 +3054,10 @@
         <v>2</v>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2881,6 +3072,9 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2901,10 +3095,10 @@
         <v>7</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2916,9 +3110,12 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
         <v>4</v>
       </c>
-      <c r="L65" t="n">
+      <c r="M65" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2942,7 +3139,7 @@
         <v>2</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2954,9 +3151,12 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
         <v>8</v>
       </c>
-      <c r="L66" t="n">
+      <c r="M66" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2995,6 +3195,9 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3030,9 +3233,12 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
+        <v>1</v>
+      </c>
+      <c r="M68" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3053,7 +3259,7 @@
         <v>11</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -3068,9 +3274,12 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
+        <v>2</v>
+      </c>
+      <c r="M69" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3094,7 +3303,7 @@
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -3106,9 +3315,12 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3132,7 +3344,7 @@
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -3144,9 +3356,12 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
+        <v>2</v>
+      </c>
+      <c r="M71" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3167,7 +3382,7 @@
         <v>4</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -3182,9 +3397,12 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
+        <v>2</v>
+      </c>
+      <c r="M72" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3205,7 +3423,7 @@
         <v>4</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -3223,6 +3441,9 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3243,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -3255,12 +3476,15 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
         <v>1</v>
       </c>
       <c r="L74" t="n">
+        <v>1</v>
+      </c>
+      <c r="M74" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3281,7 +3505,7 @@
         <v>2</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -3296,9 +3520,12 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
+        <v>2</v>
+      </c>
+      <c r="M75" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3319,24 +3546,27 @@
         <v>4</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3357,13 +3587,13 @@
         <v>2</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
@@ -3375,6 +3605,9 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3395,7 +3628,7 @@
         <v>15</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -3410,9 +3643,12 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
         <v>4</v>
       </c>
-      <c r="L78" t="n">
+      <c r="M78" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3436,10 +3672,10 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
@@ -3448,9 +3684,12 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
         <v>3</v>
       </c>
-      <c r="L79" t="n">
+      <c r="M79" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3489,6 +3728,9 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3509,13 +3751,13 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -3527,6 +3769,9 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3547,7 +3792,7 @@
         <v>5</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -3562,9 +3807,12 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
+        <v>2</v>
+      </c>
+      <c r="M82" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3585,7 +3833,7 @@
         <v>2</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3600,9 +3848,12 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3641,6 +3892,9 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3673,12 +3927,15 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3717,6 +3974,9 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3737,7 +3997,7 @@
         <v>7</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -3752,9 +4012,12 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
         <v>4</v>
       </c>
-      <c r="L87" t="n">
+      <c r="M87" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3778,7 +4041,7 @@
         <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -3790,9 +4053,12 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
+        <v>7</v>
+      </c>
+      <c r="M88" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3816,7 +4082,7 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -3828,9 +4094,12 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
         <v>4</v>
       </c>
-      <c r="L89" t="n">
+      <c r="M89" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3851,10 +4120,10 @@
         <v>20</v>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3866,9 +4135,12 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
         <v>6</v>
       </c>
-      <c r="L90" t="n">
+      <c r="M90" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3901,12 +4173,15 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3927,13 +4202,13 @@
         <v>6</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
@@ -3942,9 +4217,12 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
+        <v>2</v>
+      </c>
+      <c r="M92" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3965,7 +4243,7 @@
         <v>5</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3980,9 +4258,12 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
         <v>3</v>
       </c>
-      <c r="L93" t="n">
+      <c r="M93" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4021,6 +4302,9 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4041,7 +4325,7 @@
         <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -4059,6 +4343,9 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4079,7 +4366,7 @@
         <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -4094,9 +4381,12 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
+        <v>1</v>
+      </c>
+      <c r="M96" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4117,24 +4407,27 @@
         <v>10</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
+        <v>7</v>
+      </c>
+      <c r="M97" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4155,7 +4448,7 @@
         <v>18</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -4170,9 +4463,12 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
         <v>8</v>
       </c>
-      <c r="L98" t="n">
+      <c r="M98" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4193,13 +4489,13 @@
         <v>1</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
@@ -4208,9 +4504,12 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
         <v>3</v>
       </c>
-      <c r="L99" t="n">
+      <c r="M99" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4231,16 +4530,16 @@
         <v>2</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
         <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -4249,6 +4548,9 @@
         <v>0</v>
       </c>
       <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4269,7 +4571,7 @@
         <v>9</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -4284,9 +4586,12 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
         <v>5</v>
       </c>
-      <c r="L101" t="n">
+      <c r="M101" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4325,6 +4630,9 @@
         <v>0</v>
       </c>
       <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4351,18 +4659,21 @@
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L103" t="n">
+        <v>2</v>
+      </c>
+      <c r="M103" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4398,9 +4709,12 @@
         <v>0</v>
       </c>
       <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
         <v>8</v>
       </c>
-      <c r="L104" t="n">
+      <c r="M104" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4421,7 +4735,7 @@
         <v>3</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -4439,6 +4753,9 @@
         <v>0</v>
       </c>
       <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4459,7 +4776,7 @@
         <v>5</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -4474,9 +4791,12 @@
         <v>0</v>
       </c>
       <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
         <v>3</v>
       </c>
-      <c r="L106" t="n">
+      <c r="M106" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4497,10 +4817,10 @@
         <v>1</v>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -4515,6 +4835,9 @@
         <v>0</v>
       </c>
       <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4535,10 +4858,10 @@
         <v>12</v>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -4550,9 +4873,12 @@
         <v>0</v>
       </c>
       <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
         <v>4</v>
       </c>
-      <c r="L108" t="n">
+      <c r="M108" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4576,21 +4902,24 @@
         <v>1</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L109" t="n">
+        <v>7</v>
+      </c>
+      <c r="M109" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4611,24 +4940,27 @@
         <v>2</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
         <v>5</v>
       </c>
-      <c r="L110" t="n">
+      <c r="M110" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4649,7 +4981,7 @@
         <v>5</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -4664,9 +4996,12 @@
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L111" t="n">
+        <v>2</v>
+      </c>
+      <c r="M111" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4693,10 +5028,10 @@
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -4705,6 +5040,9 @@
         <v>0</v>
       </c>
       <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4725,24 +5063,27 @@
         <v>9</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K113" t="n">
+        <v>1</v>
+      </c>
+      <c r="L113" t="n">
         <v>3</v>
       </c>
-      <c r="L113" t="n">
+      <c r="M113" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4763,24 +5104,27 @@
         <v>32</v>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
       </c>
       <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
         <v>19</v>
       </c>
-      <c r="L114" t="n">
+      <c r="M114" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4801,10 +5145,10 @@
         <v>1</v>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -4819,6 +5163,9 @@
         <v>0</v>
       </c>
       <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4854,9 +5201,12 @@
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L116" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4892,9 +5242,12 @@
         <v>0</v>
       </c>
       <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
         <v>6</v>
       </c>
-      <c r="L117" t="n">
+      <c r="M117" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4930,9 +5283,12 @@
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" t="n">
+        <v>1</v>
+      </c>
+      <c r="M118" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4968,9 +5324,12 @@
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L119" t="n">
+        <v>2</v>
+      </c>
+      <c r="M119" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5009,6 +5368,9 @@
         <v>0</v>
       </c>
       <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5047,6 +5409,9 @@
         <v>0</v>
       </c>
       <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5085,6 +5450,9 @@
         <v>0</v>
       </c>
       <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5120,9 +5488,12 @@
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L123" t="n">
+        <v>2</v>
+      </c>
+      <c r="M123" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5143,10 +5514,10 @@
         <v>6</v>
       </c>
       <c r="F124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5158,9 +5529,12 @@
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L124" t="n">
+        <v>2</v>
+      </c>
+      <c r="M124" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5181,7 +5555,7 @@
         <v>6</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -5196,9 +5570,12 @@
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L125" t="n">
+        <v>7</v>
+      </c>
+      <c r="M125" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5234,9 +5611,12 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L126" t="n">
+        <v>1</v>
+      </c>
+      <c r="M126" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5257,24 +5637,27 @@
         <v>9</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
         <v>1</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
       </c>
       <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
         <v>6</v>
       </c>
-      <c r="L127" t="n">
+      <c r="M127" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5295,7 +5678,7 @@
         <v>10</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -5307,12 +5690,15 @@
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K128" t="n">
+        <v>1</v>
+      </c>
+      <c r="L128" t="n">
         <v>4</v>
       </c>
-      <c r="L128" t="n">
+      <c r="M128" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5333,7 +5719,7 @@
         <v>11</v>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -5348,9 +5734,12 @@
         <v>0</v>
       </c>
       <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
         <v>9</v>
       </c>
-      <c r="L129" t="n">
+      <c r="M129" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5371,24 +5760,27 @@
         <v>8</v>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
       </c>
       <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
         <v>3</v>
       </c>
-      <c r="L130" t="n">
+      <c r="M130" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5424,9 +5816,12 @@
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L131" t="n">
+        <v>1</v>
+      </c>
+      <c r="M131" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5447,24 +5842,27 @@
         <v>6</v>
       </c>
       <c r="F132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
         <v>1</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
       </c>
       <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
         <v>4</v>
       </c>
-      <c r="L132" t="n">
+      <c r="M132" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5485,7 +5883,7 @@
         <v>13</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -5500,9 +5898,12 @@
         <v>0</v>
       </c>
       <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
         <v>8</v>
       </c>
-      <c r="L133" t="n">
+      <c r="M133" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5538,9 +5939,12 @@
         <v>0</v>
       </c>
       <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
         <v>3</v>
       </c>
-      <c r="L134" t="n">
+      <c r="M134" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5576,9 +5980,12 @@
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L135" t="n">
+        <v>1</v>
+      </c>
+      <c r="M135" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5614,9 +6021,12 @@
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L136" t="n">
+        <v>1</v>
+      </c>
+      <c r="M136" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5637,7 +6047,7 @@
         <v>8</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -5649,12 +6059,15 @@
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L137" t="n">
+        <v>2</v>
+      </c>
+      <c r="M137" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5693,6 +6106,9 @@
         <v>0</v>
       </c>
       <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5713,7 +6129,7 @@
         <v>5</v>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -5728,9 +6144,12 @@
         <v>0</v>
       </c>
       <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
         <v>4</v>
       </c>
-      <c r="L139" t="n">
+      <c r="M139" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5751,7 +6170,7 @@
         <v>3</v>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -5766,9 +6185,12 @@
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L140" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5789,7 +6211,7 @@
         <v>8</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -5804,9 +6226,12 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L141" t="n">
+        <v>7</v>
+      </c>
+      <c r="M141" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5842,9 +6267,12 @@
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L142" t="n">
+        <v>1</v>
+      </c>
+      <c r="M142" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5880,9 +6308,12 @@
         <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L143" t="n">
+        <v>1</v>
+      </c>
+      <c r="M143" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5903,10 +6334,10 @@
         <v>9</v>
       </c>
       <c r="F144" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -5915,12 +6346,15 @@
         <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K144" t="n">
+        <v>1</v>
+      </c>
+      <c r="L144" t="n">
         <v>6</v>
       </c>
-      <c r="L144" t="n">
+      <c r="M144" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5941,7 +6375,7 @@
         <v>6</v>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -5953,12 +6387,15 @@
         <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K145" t="n">
+        <v>1</v>
+      </c>
+      <c r="L145" t="n">
         <v>3</v>
       </c>
-      <c r="L145" t="n">
+      <c r="M145" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5994,9 +6431,12 @@
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L146" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6023,10 +6463,10 @@
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -6035,6 +6475,9 @@
         <v>0</v>
       </c>
       <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6070,9 +6513,12 @@
         <v>0</v>
       </c>
       <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
         <v>4</v>
       </c>
-      <c r="L148" t="n">
+      <c r="M148" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6093,7 +6539,7 @@
         <v>4</v>
       </c>
       <c r="F149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -6111,6 +6557,9 @@
         <v>0</v>
       </c>
       <c r="L149" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6146,9 +6595,12 @@
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L150" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6169,7 +6621,7 @@
         <v>1</v>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -6184,9 +6636,12 @@
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L151" t="n">
+        <v>2</v>
+      </c>
+      <c r="M151" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6207,7 +6662,7 @@
         <v>6</v>
       </c>
       <c r="F152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -6222,9 +6677,12 @@
         <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L152" t="n">
+        <v>7</v>
+      </c>
+      <c r="M152" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6245,7 +6703,7 @@
         <v>11</v>
       </c>
       <c r="F153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -6260,9 +6718,12 @@
         <v>0</v>
       </c>
       <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
         <v>8</v>
       </c>
-      <c r="L153" t="n">
+      <c r="M153" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6283,10 +6744,10 @@
         <v>11</v>
       </c>
       <c r="F154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -6295,12 +6756,15 @@
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K154" t="n">
+        <v>1</v>
+      </c>
+      <c r="L154" t="n">
         <v>4</v>
       </c>
-      <c r="L154" t="n">
+      <c r="M154" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6321,13 +6785,13 @@
         <v>4</v>
       </c>
       <c r="F155" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G155" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I155" t="n">
         <v>0</v>
@@ -6336,9 +6800,12 @@
         <v>0</v>
       </c>
       <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
         <v>4</v>
       </c>
-      <c r="L155" t="n">
+      <c r="M155" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6377,6 +6844,9 @@
         <v>0</v>
       </c>
       <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6397,10 +6867,10 @@
         <v>13</v>
       </c>
       <c r="F157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -6412,9 +6882,12 @@
         <v>0</v>
       </c>
       <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
         <v>10</v>
       </c>
-      <c r="L157" t="n">
+      <c r="M157" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6435,10 +6908,10 @@
         <v>31</v>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -6447,12 +6920,15 @@
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" t="n">
+        <v>1</v>
+      </c>
+      <c r="L158" t="n">
         <v>25</v>
       </c>
-      <c r="L158" t="n">
+      <c r="M158" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6473,7 +6949,7 @@
         <v>3</v>
       </c>
       <c r="F159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -6488,9 +6964,12 @@
         <v>0</v>
       </c>
       <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
         <v>4</v>
       </c>
-      <c r="L159" t="n">
+      <c r="M159" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6514,13 +6993,13 @@
         <v>1</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -6529,6 +7008,9 @@
         <v>0</v>
       </c>
       <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6552,7 +7034,7 @@
         <v>1</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -6564,9 +7046,12 @@
         <v>0</v>
       </c>
       <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
         <v>6</v>
       </c>
-      <c r="L161" t="n">
+      <c r="M161" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6587,24 +7072,27 @@
         <v>12</v>
       </c>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K162" t="n">
+        <v>1</v>
+      </c>
+      <c r="L162" t="n">
         <v>4</v>
       </c>
-      <c r="L162" t="n">
+      <c r="M162" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6625,24 +7113,27 @@
         <v>4</v>
       </c>
       <c r="F163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L163" t="n">
+        <v>2</v>
+      </c>
+      <c r="M163" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6663,10 +7154,10 @@
         <v>7</v>
       </c>
       <c r="F164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -6678,9 +7169,12 @@
         <v>0</v>
       </c>
       <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
         <v>3</v>
       </c>
-      <c r="L164" t="n">
+      <c r="M164" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6701,7 +7195,7 @@
         <v>1</v>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -6716,9 +7210,12 @@
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L165" t="n">
+        <v>2</v>
+      </c>
+      <c r="M165" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6739,10 +7236,10 @@
         <v>2</v>
       </c>
       <c r="F166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -6757,6 +7254,9 @@
         <v>0</v>
       </c>
       <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6777,11 +7277,11 @@
         <v>28</v>
       </c>
       <c r="F167" t="n">
+        <v>13</v>
+      </c>
+      <c r="G167" t="n">
         <v>9</v>
       </c>
-      <c r="G167" t="n">
-        <v>0</v>
-      </c>
       <c r="H167" t="n">
         <v>0</v>
       </c>
@@ -6789,12 +7289,15 @@
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="L167" t="n">
+        <v>17</v>
+      </c>
+      <c r="M167" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6815,10 +7318,10 @@
         <v>23</v>
       </c>
       <c r="F168" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -6830,9 +7333,12 @@
         <v>0</v>
       </c>
       <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
         <v>10</v>
       </c>
-      <c r="L168" t="n">
+      <c r="M168" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6853,7 +7359,7 @@
         <v>8</v>
       </c>
       <c r="F169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -6868,9 +7374,12 @@
         <v>0</v>
       </c>
       <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
         <v>3</v>
       </c>
-      <c r="L169" t="n">
+      <c r="M169" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6891,7 +7400,7 @@
         <v>5</v>
       </c>
       <c r="F170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -6906,9 +7415,12 @@
         <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6929,7 +7441,7 @@
         <v>2</v>
       </c>
       <c r="F171" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -6944,9 +7456,12 @@
         <v>0</v>
       </c>
       <c r="K171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L171" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6967,7 +7482,7 @@
         <v>6</v>
       </c>
       <c r="F172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -6982,9 +7497,12 @@
         <v>0</v>
       </c>
       <c r="K172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L172" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7020,9 +7538,12 @@
         <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L173" t="n">
+        <v>2</v>
+      </c>
+      <c r="M173" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7058,9 +7579,12 @@
         <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L174" t="n">
+        <v>1</v>
+      </c>
+      <c r="M174" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7081,24 +7605,27 @@
         <v>26</v>
       </c>
       <c r="F175" t="n">
+        <v>7</v>
+      </c>
+      <c r="G175" t="n">
         <v>5</v>
       </c>
-      <c r="G175" t="n">
-        <v>1</v>
-      </c>
       <c r="H175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
       </c>
       <c r="K175" t="n">
+        <v>0</v>
+      </c>
+      <c r="L175" t="n">
         <v>9</v>
       </c>
-      <c r="L175" t="n">
+      <c r="M175" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7119,11 +7646,11 @@
         <v>5</v>
       </c>
       <c r="F176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" t="n">
         <v>3</v>
       </c>
-      <c r="G176" t="n">
-        <v>0</v>
-      </c>
       <c r="H176" t="n">
         <v>0</v>
       </c>
@@ -7137,6 +7664,9 @@
         <v>0</v>
       </c>
       <c r="L176" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7157,7 +7687,7 @@
         <v>8</v>
       </c>
       <c r="F177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -7172,9 +7702,12 @@
         <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M177" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7195,10 +7728,10 @@
         <v>5</v>
       </c>
       <c r="F178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -7213,6 +7746,9 @@
         <v>0</v>
       </c>
       <c r="L178" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7233,10 +7769,10 @@
         <v>4</v>
       </c>
       <c r="F179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -7248,9 +7784,12 @@
         <v>0</v>
       </c>
       <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
         <v>4</v>
       </c>
-      <c r="L179" t="n">
+      <c r="M179" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7286,9 +7825,12 @@
         <v>0</v>
       </c>
       <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="n">
         <v>3</v>
       </c>
-      <c r="L180" t="n">
+      <c r="M180" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7324,9 +7866,12 @@
         <v>0</v>
       </c>
       <c r="K181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L181" t="n">
+        <v>1</v>
+      </c>
+      <c r="M181" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7362,9 +7907,12 @@
         <v>0</v>
       </c>
       <c r="K182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L182" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7388,7 +7936,7 @@
         <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -7400,9 +7948,12 @@
         <v>0</v>
       </c>
       <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="n">
         <v>3</v>
       </c>
-      <c r="L183" t="n">
+      <c r="M183" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7423,24 +7974,27 @@
         <v>1</v>
       </c>
       <c r="F184" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
       </c>
       <c r="K184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L184" t="n">
+        <v>2</v>
+      </c>
+      <c r="M184" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7461,7 +8015,7 @@
         <v>9</v>
       </c>
       <c r="F185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -7473,12 +8027,15 @@
         <v>0</v>
       </c>
       <c r="J185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K185" t="n">
+        <v>1</v>
+      </c>
+      <c r="L185" t="n">
         <v>5</v>
       </c>
-      <c r="L185" t="n">
+      <c r="M185" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7499,24 +8056,27 @@
         <v>20</v>
       </c>
       <c r="F186" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G186" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H186" t="n">
         <v>2</v>
       </c>
       <c r="I186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K186" t="n">
+        <v>1</v>
+      </c>
+      <c r="L186" t="n">
         <v>14</v>
       </c>
-      <c r="L186" t="n">
+      <c r="M186" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7537,7 +8097,7 @@
         <v>9</v>
       </c>
       <c r="F187" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -7552,9 +8112,12 @@
         <v>0</v>
       </c>
       <c r="K187" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L187" t="n">
+        <v>7</v>
+      </c>
+      <c r="M187" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7575,7 +8138,7 @@
         <v>5</v>
       </c>
       <c r="F188" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -7590,9 +8153,12 @@
         <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L188" t="n">
+        <v>2</v>
+      </c>
+      <c r="M188" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7613,24 +8179,27 @@
         <v>3</v>
       </c>
       <c r="F189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L189" t="n">
+        <v>0</v>
+      </c>
+      <c r="M189" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7654,7 +8223,7 @@
         <v>1</v>
       </c>
       <c r="G190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -7669,6 +8238,9 @@
         <v>0</v>
       </c>
       <c r="L190" t="n">
+        <v>0</v>
+      </c>
+      <c r="M190" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7704,9 +8276,12 @@
         <v>0</v>
       </c>
       <c r="K191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L191" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7727,13 +8302,13 @@
         <v>6</v>
       </c>
       <c r="F192" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H192" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I192" t="n">
         <v>0</v>
@@ -7742,9 +8317,12 @@
         <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L192" t="n">
+        <v>1</v>
+      </c>
+      <c r="M192" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7765,24 +8343,27 @@
         <v>9</v>
       </c>
       <c r="F193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
       </c>
       <c r="H193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
       </c>
       <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="n">
         <v>4</v>
       </c>
-      <c r="L193" t="n">
+      <c r="M193" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7803,7 +8384,7 @@
         <v>1</v>
       </c>
       <c r="F194" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -7818,9 +8399,12 @@
         <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L194" t="n">
+        <v>1</v>
+      </c>
+      <c r="M194" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7844,7 +8428,7 @@
         <v>1</v>
       </c>
       <c r="G195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -7856,9 +8440,12 @@
         <v>0</v>
       </c>
       <c r="K195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L195" t="n">
+        <v>1</v>
+      </c>
+      <c r="M195" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7879,7 +8466,7 @@
         <v>1</v>
       </c>
       <c r="F196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -7894,9 +8481,12 @@
         <v>0</v>
       </c>
       <c r="K196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L196" t="n">
+        <v>1</v>
+      </c>
+      <c r="M196" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7917,13 +8507,13 @@
         <v>5</v>
       </c>
       <c r="F197" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I197" t="n">
         <v>0</v>
@@ -7932,9 +8522,12 @@
         <v>0</v>
       </c>
       <c r="K197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" t="n">
         <v>5</v>
       </c>
-      <c r="L197" t="n">
+      <c r="M197" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7958,21 +8551,24 @@
         <v>0</v>
       </c>
       <c r="G198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I198" t="n">
         <v>0</v>
       </c>
       <c r="J198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K198" t="n">
+        <v>1</v>
+      </c>
+      <c r="L198" t="n">
         <v>10</v>
       </c>
-      <c r="L198" t="n">
+      <c r="M198" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7999,10 +8595,10 @@
         <v>0</v>
       </c>
       <c r="H199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -8011,6 +8607,9 @@
         <v>0</v>
       </c>
       <c r="L199" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8049,6 +8648,9 @@
         <v>0</v>
       </c>
       <c r="L200" t="n">
+        <v>0</v>
+      </c>
+      <c r="M200" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8084,9 +8686,12 @@
         <v>0</v>
       </c>
       <c r="K201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L201" t="n">
+        <v>1</v>
+      </c>
+      <c r="M201" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8107,7 +8712,7 @@
         <v>5</v>
       </c>
       <c r="F202" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -8122,9 +8727,12 @@
         <v>0</v>
       </c>
       <c r="K202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L202" t="n">
+        <v>1</v>
+      </c>
+      <c r="M202" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8145,7 +8753,7 @@
         <v>4</v>
       </c>
       <c r="F203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -8160,9 +8768,12 @@
         <v>0</v>
       </c>
       <c r="K203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L203" t="n">
+        <v>1</v>
+      </c>
+      <c r="M203" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8183,7 +8794,7 @@
         <v>4</v>
       </c>
       <c r="F204" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -8198,9 +8809,12 @@
         <v>0</v>
       </c>
       <c r="K204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L204" t="n">
+        <v>2</v>
+      </c>
+      <c r="M204" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8221,7 +8835,7 @@
         <v>4</v>
       </c>
       <c r="F205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -8236,9 +8850,12 @@
         <v>0</v>
       </c>
       <c r="K205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L205" t="n">
+        <v>2</v>
+      </c>
+      <c r="M205" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8259,7 +8876,7 @@
         <v>8</v>
       </c>
       <c r="F206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -8274,9 +8891,12 @@
         <v>0</v>
       </c>
       <c r="K206" t="n">
+        <v>0</v>
+      </c>
+      <c r="L206" t="n">
         <v>3</v>
       </c>
-      <c r="L206" t="n">
+      <c r="M206" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8297,7 +8917,7 @@
         <v>1</v>
       </c>
       <c r="F207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -8312,9 +8932,12 @@
         <v>0</v>
       </c>
       <c r="K207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L207" t="n">
+        <v>1</v>
+      </c>
+      <c r="M207" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8335,7 +8958,7 @@
         <v>3</v>
       </c>
       <c r="F208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -8353,6 +8976,9 @@
         <v>0</v>
       </c>
       <c r="L208" t="n">
+        <v>0</v>
+      </c>
+      <c r="M208" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8388,9 +9014,12 @@
         <v>0</v>
       </c>
       <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
         <v>3</v>
       </c>
-      <c r="L209" t="n">
+      <c r="M209" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8411,7 +9040,7 @@
         <v>5</v>
       </c>
       <c r="F210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -8426,9 +9055,12 @@
         <v>0</v>
       </c>
       <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="n">
         <v>3</v>
       </c>
-      <c r="L210" t="n">
+      <c r="M210" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8449,7 +9081,7 @@
         <v>12</v>
       </c>
       <c r="F211" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -8464,9 +9096,12 @@
         <v>0</v>
       </c>
       <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="n">
         <v>11</v>
       </c>
-      <c r="L211" t="n">
+      <c r="M211" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8487,10 +9122,10 @@
         <v>6</v>
       </c>
       <c r="F212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -8502,9 +9137,12 @@
         <v>0</v>
       </c>
       <c r="K212" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L212" t="n">
+        <v>7</v>
+      </c>
+      <c r="M212" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8525,10 +9163,10 @@
         <v>8</v>
       </c>
       <c r="F213" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G213" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -8540,9 +9178,12 @@
         <v>0</v>
       </c>
       <c r="K213" t="n">
+        <v>0</v>
+      </c>
+      <c r="L213" t="n">
         <v>6</v>
       </c>
-      <c r="L213" t="n">
+      <c r="M213" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8581,6 +9222,9 @@
         <v>0</v>
       </c>
       <c r="L214" t="n">
+        <v>0</v>
+      </c>
+      <c r="M214" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8616,9 +9260,12 @@
         <v>0</v>
       </c>
       <c r="K215" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L215" t="n">
+        <v>2</v>
+      </c>
+      <c r="M215" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8639,24 +9286,27 @@
         <v>7</v>
       </c>
       <c r="F216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
       </c>
       <c r="H216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
       </c>
       <c r="K216" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" t="n">
         <v>4</v>
       </c>
-      <c r="L216" t="n">
+      <c r="M216" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8677,7 +9327,7 @@
         <v>0</v>
       </c>
       <c r="F217" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -8695,6 +9345,9 @@
         <v>0</v>
       </c>
       <c r="L217" t="n">
+        <v>0</v>
+      </c>
+      <c r="M217" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8721,10 +9374,10 @@
         <v>0</v>
       </c>
       <c r="H218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -8733,6 +9386,9 @@
         <v>0</v>
       </c>
       <c r="L218" t="n">
+        <v>0</v>
+      </c>
+      <c r="M218" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8753,7 +9409,7 @@
         <v>2</v>
       </c>
       <c r="F219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -8768,9 +9424,12 @@
         <v>0</v>
       </c>
       <c r="K219" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L219" t="n">
+        <v>2</v>
+      </c>
+      <c r="M219" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8809,6 +9468,9 @@
         <v>0</v>
       </c>
       <c r="L220" t="n">
+        <v>0</v>
+      </c>
+      <c r="M220" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8829,7 +9491,7 @@
         <v>7</v>
       </c>
       <c r="F221" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -8844,9 +9506,12 @@
         <v>0</v>
       </c>
       <c r="K221" t="n">
+        <v>0</v>
+      </c>
+      <c r="L221" t="n">
         <v>3</v>
       </c>
-      <c r="L221" t="n">
+      <c r="M221" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8882,9 +9547,12 @@
         <v>0</v>
       </c>
       <c r="K222" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L222" t="n">
+        <v>2</v>
+      </c>
+      <c r="M222" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8905,24 +9573,27 @@
         <v>5</v>
       </c>
       <c r="F223" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H223" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I223" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
       </c>
       <c r="K223" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" t="n">
         <v>3</v>
       </c>
-      <c r="L223" t="n">
+      <c r="M223" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8943,7 +9614,7 @@
         <v>2</v>
       </c>
       <c r="F224" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -8958,9 +9629,12 @@
         <v>0</v>
       </c>
       <c r="K224" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L224" t="n">
+        <v>2</v>
+      </c>
+      <c r="M224" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8981,11 +9655,11 @@
         <v>3</v>
       </c>
       <c r="F225" t="n">
+        <v>2</v>
+      </c>
+      <c r="G225" t="n">
         <v>3</v>
       </c>
-      <c r="G225" t="n">
-        <v>0</v>
-      </c>
       <c r="H225" t="n">
         <v>0</v>
       </c>
@@ -8999,6 +9673,9 @@
         <v>0</v>
       </c>
       <c r="L225" t="n">
+        <v>0</v>
+      </c>
+      <c r="M225" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9019,7 +9696,7 @@
         <v>3</v>
       </c>
       <c r="F226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -9031,12 +9708,15 @@
         <v>0</v>
       </c>
       <c r="J226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L226" t="n">
+        <v>2</v>
+      </c>
+      <c r="M226" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9057,24 +9737,27 @@
         <v>5</v>
       </c>
       <c r="F227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
       </c>
       <c r="H227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K227" t="n">
         <v>2</v>
       </c>
       <c r="L227" t="n">
+        <v>2</v>
+      </c>
+      <c r="M227" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9095,7 +9778,7 @@
         <v>5</v>
       </c>
       <c r="F228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -9110,9 +9793,12 @@
         <v>0</v>
       </c>
       <c r="K228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L228" t="n">
+        <v>1</v>
+      </c>
+      <c r="M228" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9133,10 +9819,10 @@
         <v>12</v>
       </c>
       <c r="F229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G229" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -9148,9 +9834,12 @@
         <v>0</v>
       </c>
       <c r="K229" t="n">
+        <v>0</v>
+      </c>
+      <c r="L229" t="n">
         <v>5</v>
       </c>
-      <c r="L229" t="n">
+      <c r="M229" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9186,9 +9875,12 @@
         <v>0</v>
       </c>
       <c r="K230" t="n">
+        <v>0</v>
+      </c>
+      <c r="L230" t="n">
         <v>3</v>
       </c>
-      <c r="L230" t="n">
+      <c r="M230" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9209,7 +9901,7 @@
         <v>5</v>
       </c>
       <c r="F231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -9224,9 +9916,12 @@
         <v>0</v>
       </c>
       <c r="K231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L231" t="n">
+        <v>1</v>
+      </c>
+      <c r="M231" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9247,24 +9942,27 @@
         <v>3</v>
       </c>
       <c r="F232" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
       </c>
       <c r="H232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
       </c>
       <c r="K232" t="n">
+        <v>0</v>
+      </c>
+      <c r="L232" t="n">
         <v>3</v>
       </c>
-      <c r="L232" t="n">
+      <c r="M232" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9285,24 +9983,27 @@
         <v>1</v>
       </c>
       <c r="F233" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
       </c>
       <c r="H233" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I233" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
       </c>
       <c r="K233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L233" t="n">
+        <v>1</v>
+      </c>
+      <c r="M233" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9323,7 +10024,7 @@
         <v>4</v>
       </c>
       <c r="F234" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -9338,9 +10039,12 @@
         <v>0</v>
       </c>
       <c r="K234" t="n">
+        <v>0</v>
+      </c>
+      <c r="L234" t="n">
         <v>5</v>
       </c>
-      <c r="L234" t="n">
+      <c r="M234" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9376,9 +10080,12 @@
         <v>0</v>
       </c>
       <c r="K235" t="n">
+        <v>0</v>
+      </c>
+      <c r="L235" t="n">
         <v>5</v>
       </c>
-      <c r="L235" t="n">
+      <c r="M235" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9399,10 +10106,10 @@
         <v>5</v>
       </c>
       <c r="F236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -9417,6 +10124,9 @@
         <v>0</v>
       </c>
       <c r="L236" t="n">
+        <v>0</v>
+      </c>
+      <c r="M236" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9437,24 +10147,27 @@
         <v>8</v>
       </c>
       <c r="F237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G237" t="n">
         <v>1</v>
       </c>
       <c r="H237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I237" t="n">
         <v>0</v>
       </c>
       <c r="J237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L237" t="n">
+        <v>0</v>
+      </c>
+      <c r="M237" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9490,9 +10203,12 @@
         <v>0</v>
       </c>
       <c r="K238" t="n">
+        <v>0</v>
+      </c>
+      <c r="L238" t="n">
         <v>3</v>
       </c>
-      <c r="L238" t="n">
+      <c r="M238" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9528,9 +10244,12 @@
         <v>0</v>
       </c>
       <c r="K239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L239" t="n">
+        <v>1</v>
+      </c>
+      <c r="M239" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9551,7 +10270,7 @@
         <v>12</v>
       </c>
       <c r="F240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -9563,12 +10282,15 @@
         <v>0</v>
       </c>
       <c r="J240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K240" t="n">
+        <v>1</v>
+      </c>
+      <c r="L240" t="n">
         <v>6</v>
       </c>
-      <c r="L240" t="n">
+      <c r="M240" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9589,10 +10311,10 @@
         <v>9</v>
       </c>
       <c r="F241" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -9604,9 +10326,12 @@
         <v>0</v>
       </c>
       <c r="K241" t="n">
+        <v>0</v>
+      </c>
+      <c r="L241" t="n">
         <v>5</v>
       </c>
-      <c r="L241" t="n">
+      <c r="M241" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9627,10 +10352,10 @@
         <v>21</v>
       </c>
       <c r="F242" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -9642,9 +10367,12 @@
         <v>0</v>
       </c>
       <c r="K242" t="n">
+        <v>0</v>
+      </c>
+      <c r="L242" t="n">
         <v>12</v>
       </c>
-      <c r="L242" t="n">
+      <c r="M242" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9665,24 +10393,27 @@
         <v>21</v>
       </c>
       <c r="F243" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
       </c>
       <c r="K243" t="n">
+        <v>0</v>
+      </c>
+      <c r="L243" t="n">
         <v>11</v>
       </c>
-      <c r="L243" t="n">
+      <c r="M243" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9703,16 +10434,16 @@
         <v>0</v>
       </c>
       <c r="F244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
       </c>
       <c r="H244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -9721,6 +10452,9 @@
         <v>0</v>
       </c>
       <c r="L244" t="n">
+        <v>0</v>
+      </c>
+      <c r="M244" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9741,13 +10475,13 @@
         <v>1</v>
       </c>
       <c r="F245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I245" t="n">
         <v>0</v>
@@ -9759,6 +10493,9 @@
         <v>0</v>
       </c>
       <c r="L245" t="n">
+        <v>0</v>
+      </c>
+      <c r="M245" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9785,18 +10522,21 @@
         <v>0</v>
       </c>
       <c r="H246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
       </c>
       <c r="K246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L246" t="n">
+        <v>1</v>
+      </c>
+      <c r="M246" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9817,7 +10557,7 @@
         <v>5</v>
       </c>
       <c r="F247" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -9829,12 +10569,15 @@
         <v>0</v>
       </c>
       <c r="J247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L247" t="n">
+        <v>2</v>
+      </c>
+      <c r="M247" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9855,24 +10598,27 @@
         <v>1</v>
       </c>
       <c r="F248" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
       </c>
       <c r="H248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
       </c>
       <c r="K248" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L248" t="n">
+        <v>2</v>
+      </c>
+      <c r="M248" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9893,7 +10639,7 @@
         <v>1</v>
       </c>
       <c r="F249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -9905,12 +10651,15 @@
         <v>0</v>
       </c>
       <c r="J249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K249" t="n">
         <v>1</v>
       </c>
       <c r="L249" t="n">
+        <v>1</v>
+      </c>
+      <c r="M249" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9934,7 +10683,7 @@
         <v>2</v>
       </c>
       <c r="G250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -9946,9 +10695,12 @@
         <v>0</v>
       </c>
       <c r="K250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L250" t="n">
+        <v>1</v>
+      </c>
+      <c r="M250" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9972,7 +10724,7 @@
         <v>2</v>
       </c>
       <c r="G251" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -9981,12 +10733,15 @@
         <v>0</v>
       </c>
       <c r="J251" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K251" t="n">
+        <v>1</v>
+      </c>
+      <c r="L251" t="n">
         <v>3</v>
       </c>
-      <c r="L251" t="n">
+      <c r="M251" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10007,7 +10762,7 @@
         <v>8</v>
       </c>
       <c r="F252" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10022,9 +10777,12 @@
         <v>0</v>
       </c>
       <c r="K252" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L252" t="n">
+        <v>7</v>
+      </c>
+      <c r="M252" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10051,18 +10809,21 @@
         <v>0</v>
       </c>
       <c r="H253" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
       </c>
       <c r="K253" t="n">
+        <v>0</v>
+      </c>
+      <c r="L253" t="n">
         <v>4</v>
       </c>
-      <c r="L253" t="n">
+      <c r="M253" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10083,24 +10844,27 @@
         <v>20</v>
       </c>
       <c r="F254" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G254" t="n">
         <v>0</v>
       </c>
       <c r="H254" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J254" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K254" t="n">
+        <v>1</v>
+      </c>
+      <c r="L254" t="n">
         <v>11</v>
       </c>
-      <c r="L254" t="n">
+      <c r="M254" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10121,10 +10885,10 @@
         <v>3</v>
       </c>
       <c r="F255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -10136,9 +10900,12 @@
         <v>0</v>
       </c>
       <c r="K255" t="n">
+        <v>0</v>
+      </c>
+      <c r="L255" t="n">
         <v>3</v>
       </c>
-      <c r="L255" t="n">
+      <c r="M255" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10174,9 +10941,12 @@
         <v>0</v>
       </c>
       <c r="K256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L256" t="n">
+        <v>1</v>
+      </c>
+      <c r="M256" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10212,9 +10982,12 @@
         <v>0</v>
       </c>
       <c r="K257" t="n">
+        <v>0</v>
+      </c>
+      <c r="L257" t="n">
         <v>4</v>
       </c>
-      <c r="L257" t="n">
+      <c r="M257" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10250,9 +11023,12 @@
         <v>0</v>
       </c>
       <c r="K258" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L258" t="n">
+        <v>2</v>
+      </c>
+      <c r="M258" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10288,9 +11064,12 @@
         <v>0</v>
       </c>
       <c r="K259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L259" t="n">
+        <v>1</v>
+      </c>
+      <c r="M259" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10314,7 +11093,7 @@
         <v>1</v>
       </c>
       <c r="G260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -10326,9 +11105,12 @@
         <v>0</v>
       </c>
       <c r="K260" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L260" t="n">
+        <v>2</v>
+      </c>
+      <c r="M260" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10349,7 +11131,7 @@
         <v>8</v>
       </c>
       <c r="F261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G261" t="n">
         <v>0</v>
@@ -10364,9 +11146,12 @@
         <v>0</v>
       </c>
       <c r="K261" t="n">
+        <v>0</v>
+      </c>
+      <c r="L261" t="n">
         <v>4</v>
       </c>
-      <c r="L261" t="n">
+      <c r="M261" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10387,24 +11172,27 @@
         <v>19</v>
       </c>
       <c r="F262" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G262" t="n">
         <v>0</v>
       </c>
       <c r="H262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
       </c>
       <c r="K262" t="n">
+        <v>0</v>
+      </c>
+      <c r="L262" t="n">
         <v>10</v>
       </c>
-      <c r="L262" t="n">
+      <c r="M262" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10425,24 +11213,27 @@
         <v>17</v>
       </c>
       <c r="F263" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K263" t="n">
+        <v>1</v>
+      </c>
+      <c r="L263" t="n">
         <v>6</v>
       </c>
-      <c r="L263" t="n">
+      <c r="M263" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10466,7 +11257,7 @@
         <v>1</v>
       </c>
       <c r="G264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -10478,9 +11269,12 @@
         <v>0</v>
       </c>
       <c r="K264" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L264" t="n">
+        <v>2</v>
+      </c>
+      <c r="M264" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10501,10 +11295,10 @@
         <v>2</v>
       </c>
       <c r="F265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G265" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -10516,9 +11310,12 @@
         <v>0</v>
       </c>
       <c r="K265" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L265" t="n">
+        <v>2</v>
+      </c>
+      <c r="M265" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10539,10 +11336,10 @@
         <v>6</v>
       </c>
       <c r="F266" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -10554,9 +11351,12 @@
         <v>0</v>
       </c>
       <c r="K266" t="n">
+        <v>0</v>
+      </c>
+      <c r="L266" t="n">
         <v>9</v>
       </c>
-      <c r="L266" t="n">
+      <c r="M266" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10577,24 +11377,27 @@
         <v>6</v>
       </c>
       <c r="F267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H267" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I267" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
       </c>
       <c r="K267" t="n">
+        <v>0</v>
+      </c>
+      <c r="L267" t="n">
         <v>3</v>
       </c>
-      <c r="L267" t="n">
+      <c r="M267" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10615,24 +11418,27 @@
         <v>6</v>
       </c>
       <c r="F268" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H268" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I268" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
       </c>
       <c r="K268" t="n">
+        <v>0</v>
+      </c>
+      <c r="L268" t="n">
         <v>3</v>
       </c>
-      <c r="L268" t="n">
+      <c r="M268" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10653,24 +11459,27 @@
         <v>5</v>
       </c>
       <c r="F269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G269" t="n">
         <v>0</v>
       </c>
       <c r="H269" t="n">
+        <v>0</v>
+      </c>
+      <c r="I269" t="n">
         <v>3</v>
       </c>
-      <c r="I269" t="n">
-        <v>0</v>
-      </c>
       <c r="J269" t="n">
         <v>0</v>
       </c>
       <c r="K269" t="n">
+        <v>0</v>
+      </c>
+      <c r="L269" t="n">
         <v>3</v>
       </c>
-      <c r="L269" t="n">
+      <c r="M269" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10691,24 +11500,27 @@
         <v>2</v>
       </c>
       <c r="F270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H270" t="n">
         <v>1</v>
       </c>
       <c r="I270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L270" t="n">
+        <v>0</v>
+      </c>
+      <c r="M270" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10729,7 +11541,7 @@
         <v>11</v>
       </c>
       <c r="F271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G271" t="n">
         <v>0</v>
@@ -10744,9 +11556,12 @@
         <v>0</v>
       </c>
       <c r="K271" t="n">
+        <v>0</v>
+      </c>
+      <c r="L271" t="n">
         <v>9</v>
       </c>
-      <c r="L271" t="n">
+      <c r="M271" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10770,7 +11585,7 @@
         <v>1</v>
       </c>
       <c r="G272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -10782,9 +11597,12 @@
         <v>0</v>
       </c>
       <c r="K272" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L272" t="n">
+        <v>7</v>
+      </c>
+      <c r="M272" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10823,6 +11641,9 @@
         <v>0</v>
       </c>
       <c r="L273" t="n">
+        <v>0</v>
+      </c>
+      <c r="M273" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10843,24 +11664,27 @@
         <v>2</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I274" t="n">
         <v>0</v>
       </c>
       <c r="J274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L274" t="n">
+        <v>0</v>
+      </c>
+      <c r="M274" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10881,7 +11705,7 @@
         <v>14</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G275" t="n">
         <v>0</v>
@@ -10896,9 +11720,12 @@
         <v>0</v>
       </c>
       <c r="K275" t="n">
+        <v>0</v>
+      </c>
+      <c r="L275" t="n">
         <v>8</v>
       </c>
-      <c r="L275" t="n">
+      <c r="M275" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10919,7 +11746,7 @@
         <v>5</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G276" t="n">
         <v>0</v>
@@ -10934,9 +11761,12 @@
         <v>0</v>
       </c>
       <c r="K276" t="n">
+        <v>0</v>
+      </c>
+      <c r="L276" t="n">
         <v>5</v>
       </c>
-      <c r="L276" t="n">
+      <c r="M276" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10972,9 +11802,12 @@
         <v>0</v>
       </c>
       <c r="K277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L277" t="n">
+        <v>1</v>
+      </c>
+      <c r="M277" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11010,9 +11843,12 @@
         <v>0</v>
       </c>
       <c r="K278" t="n">
+        <v>0</v>
+      </c>
+      <c r="L278" t="n">
         <v>3</v>
       </c>
-      <c r="L278" t="n">
+      <c r="M278" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11048,9 +11884,12 @@
         <v>0</v>
       </c>
       <c r="K279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L279" t="n">
+        <v>1</v>
+      </c>
+      <c r="M279" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11089,6 +11928,9 @@
         <v>0</v>
       </c>
       <c r="L280" t="n">
+        <v>0</v>
+      </c>
+      <c r="M280" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11127,6 +11969,9 @@
         <v>0</v>
       </c>
       <c r="L281" t="n">
+        <v>0</v>
+      </c>
+      <c r="M281" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11165,6 +12010,9 @@
         <v>0</v>
       </c>
       <c r="L282" t="n">
+        <v>0</v>
+      </c>
+      <c r="M282" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11185,7 +12033,7 @@
         <v>2</v>
       </c>
       <c r="F283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G283" t="n">
         <v>0</v>
@@ -11203,6 +12051,9 @@
         <v>0</v>
       </c>
       <c r="L283" t="n">
+        <v>0</v>
+      </c>
+      <c r="M283" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11226,7 +12077,7 @@
         <v>1</v>
       </c>
       <c r="G284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -11238,9 +12089,12 @@
         <v>0</v>
       </c>
       <c r="K284" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L284" t="n">
+        <v>1</v>
+      </c>
+      <c r="M284" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11261,7 +12115,7 @@
         <v>1</v>
       </c>
       <c r="F285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G285" t="n">
         <v>0</v>
@@ -11276,9 +12130,12 @@
         <v>0</v>
       </c>
       <c r="K285" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L285" t="n">
+        <v>2</v>
+      </c>
+      <c r="M285" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11299,7 +12156,7 @@
         <v>3</v>
       </c>
       <c r="F286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G286" t="n">
         <v>0</v>
@@ -11317,6 +12174,9 @@
         <v>0</v>
       </c>
       <c r="L286" t="n">
+        <v>0</v>
+      </c>
+      <c r="M286" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11337,10 +12197,10 @@
         <v>7</v>
       </c>
       <c r="F287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -11352,9 +12212,12 @@
         <v>0</v>
       </c>
       <c r="K287" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L287" t="n">
+        <v>2</v>
+      </c>
+      <c r="M287" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11375,10 +12238,10 @@
         <v>3</v>
       </c>
       <c r="F288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -11393,6 +12256,9 @@
         <v>0</v>
       </c>
       <c r="L288" t="n">
+        <v>0</v>
+      </c>
+      <c r="M288" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11413,24 +12279,27 @@
         <v>1</v>
       </c>
       <c r="F289" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H289" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I289" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
       </c>
       <c r="K289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L289" t="n">
+        <v>1</v>
+      </c>
+      <c r="M289" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11469,6 +12338,9 @@
         <v>0</v>
       </c>
       <c r="L290" t="n">
+        <v>0</v>
+      </c>
+      <c r="M290" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11504,9 +12376,12 @@
         <v>0</v>
       </c>
       <c r="K291" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L291" t="n">
+        <v>1</v>
+      </c>
+      <c r="M291" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11545,6 +12420,9 @@
         <v>0</v>
       </c>
       <c r="L292" t="n">
+        <v>0</v>
+      </c>
+      <c r="M292" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11565,7 +12443,7 @@
         <v>4</v>
       </c>
       <c r="F293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G293" t="n">
         <v>0</v>
@@ -11580,9 +12458,12 @@
         <v>0</v>
       </c>
       <c r="K293" t="n">
+        <v>0</v>
+      </c>
+      <c r="L293" t="n">
         <v>4</v>
       </c>
-      <c r="L293" t="n">
+      <c r="M293" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11603,13 +12484,13 @@
         <v>10</v>
       </c>
       <c r="F294" t="n">
+        <v>2</v>
+      </c>
+      <c r="G294" t="n">
         <v>3</v>
       </c>
-      <c r="G294" t="n">
-        <v>1</v>
-      </c>
       <c r="H294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I294" t="n">
         <v>0</v>
@@ -11618,9 +12499,12 @@
         <v>0</v>
       </c>
       <c r="K294" t="n">
+        <v>0</v>
+      </c>
+      <c r="L294" t="n">
         <v>8</v>
       </c>
-      <c r="L294" t="n">
+      <c r="M294" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11641,11 +12525,11 @@
         <v>24</v>
       </c>
       <c r="F295" t="n">
+        <v>2</v>
+      </c>
+      <c r="G295" t="n">
         <v>4</v>
       </c>
-      <c r="G295" t="n">
-        <v>0</v>
-      </c>
       <c r="H295" t="n">
         <v>0</v>
       </c>
@@ -11656,9 +12540,12 @@
         <v>0</v>
       </c>
       <c r="K295" t="n">
+        <v>0</v>
+      </c>
+      <c r="L295" t="n">
         <v>13</v>
       </c>
-      <c r="L295" t="n">
+      <c r="M295" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11679,7 +12566,7 @@
         <v>4</v>
       </c>
       <c r="F296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G296" t="n">
         <v>0</v>
@@ -11694,9 +12581,12 @@
         <v>0</v>
       </c>
       <c r="K296" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L296" t="n">
+        <v>2</v>
+      </c>
+      <c r="M296" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11717,7 +12607,7 @@
         <v>8</v>
       </c>
       <c r="F297" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G297" t="n">
         <v>0</v>
@@ -11732,9 +12622,12 @@
         <v>0</v>
       </c>
       <c r="K297" t="n">
+        <v>0</v>
+      </c>
+      <c r="L297" t="n">
         <v>3</v>
       </c>
-      <c r="L297" t="n">
+      <c r="M297" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11755,7 +12648,7 @@
         <v>0</v>
       </c>
       <c r="F298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G298" t="n">
         <v>0</v>
@@ -11770,9 +12663,12 @@
         <v>0</v>
       </c>
       <c r="K298" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L298" t="n">
+        <v>1</v>
+      </c>
+      <c r="M298" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11793,7 +12689,7 @@
         <v>5</v>
       </c>
       <c r="F299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G299" t="n">
         <v>0</v>
@@ -11808,9 +12704,12 @@
         <v>0</v>
       </c>
       <c r="K299" t="n">
+        <v>0</v>
+      </c>
+      <c r="L299" t="n">
         <v>4</v>
       </c>
-      <c r="L299" t="n">
+      <c r="M299" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11849,6 +12748,9 @@
         <v>0</v>
       </c>
       <c r="L300" t="n">
+        <v>0</v>
+      </c>
+      <c r="M300" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11875,18 +12777,21 @@
         <v>0</v>
       </c>
       <c r="H301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J301" t="n">
         <v>0</v>
       </c>
       <c r="K301" t="n">
+        <v>0</v>
+      </c>
+      <c r="L301" t="n">
         <v>5</v>
       </c>
-      <c r="L301" t="n">
+      <c r="M301" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11907,7 +12812,7 @@
         <v>1</v>
       </c>
       <c r="F302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G302" t="n">
         <v>0</v>
@@ -11919,12 +12824,15 @@
         <v>0</v>
       </c>
       <c r="J302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L302" t="n">
+        <v>0</v>
+      </c>
+      <c r="M302" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11945,7 +12853,7 @@
         <v>4</v>
       </c>
       <c r="F303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G303" t="n">
         <v>0</v>
@@ -11960,9 +12868,12 @@
         <v>0</v>
       </c>
       <c r="K303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L303" t="n">
+        <v>1</v>
+      </c>
+      <c r="M303" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11983,7 +12894,7 @@
         <v>2</v>
       </c>
       <c r="F304" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G304" t="n">
         <v>0</v>
@@ -11998,9 +12909,12 @@
         <v>0</v>
       </c>
       <c r="K304" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L304" t="n">
+        <v>2</v>
+      </c>
+      <c r="M304" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12021,10 +12935,10 @@
         <v>4</v>
       </c>
       <c r="F305" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -12036,9 +12950,12 @@
         <v>0</v>
       </c>
       <c r="K305" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L305" t="n">
+        <v>2</v>
+      </c>
+      <c r="M305" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12059,7 +12976,7 @@
         <v>2</v>
       </c>
       <c r="F306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G306" t="n">
         <v>0</v>
@@ -12077,6 +12994,9 @@
         <v>0</v>
       </c>
       <c r="L306" t="n">
+        <v>0</v>
+      </c>
+      <c r="M306" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12097,7 +13017,7 @@
         <v>1</v>
       </c>
       <c r="F307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G307" t="n">
         <v>0</v>
@@ -12112,9 +13032,12 @@
         <v>0</v>
       </c>
       <c r="K307" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L307" t="n">
+        <v>2</v>
+      </c>
+      <c r="M307" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12150,9 +13073,12 @@
         <v>0</v>
       </c>
       <c r="K308" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L308" t="n">
+        <v>2</v>
+      </c>
+      <c r="M308" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12188,9 +13114,12 @@
         <v>0</v>
       </c>
       <c r="K309" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L309" t="n">
+        <v>2</v>
+      </c>
+      <c r="M309" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12211,10 +13140,10 @@
         <v>10</v>
       </c>
       <c r="F310" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G310" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -12226,9 +13155,12 @@
         <v>0</v>
       </c>
       <c r="K310" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L310" t="n">
+        <v>7</v>
+      </c>
+      <c r="M310" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12249,7 +13181,7 @@
         <v>4</v>
       </c>
       <c r="F311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G311" t="n">
         <v>0</v>
@@ -12264,9 +13196,12 @@
         <v>0</v>
       </c>
       <c r="K311" t="n">
+        <v>0</v>
+      </c>
+      <c r="L311" t="n">
         <v>4</v>
       </c>
-      <c r="L311" t="n">
+      <c r="M311" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12302,9 +13237,12 @@
         <v>0</v>
       </c>
       <c r="K312" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L312" t="n">
+        <v>2</v>
+      </c>
+      <c r="M312" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12343,6 +13281,9 @@
         <v>0</v>
       </c>
       <c r="L313" t="n">
+        <v>0</v>
+      </c>
+      <c r="M313" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12363,10 +13304,10 @@
         <v>2</v>
       </c>
       <c r="F314" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -12381,6 +13322,9 @@
         <v>0</v>
       </c>
       <c r="L314" t="n">
+        <v>0</v>
+      </c>
+      <c r="M314" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12401,7 +13345,7 @@
         <v>14</v>
       </c>
       <c r="F315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G315" t="n">
         <v>0</v>
@@ -12416,9 +13360,12 @@
         <v>0</v>
       </c>
       <c r="K315" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L315" t="n">
+        <v>7</v>
+      </c>
+      <c r="M315" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12439,24 +13386,27 @@
         <v>8</v>
       </c>
       <c r="F316" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G316" t="n">
         <v>0</v>
       </c>
       <c r="H316" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I316" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J316" t="n">
         <v>0</v>
       </c>
       <c r="K316" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L316" t="n">
+        <v>2</v>
+      </c>
+      <c r="M316" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12477,10 +13427,10 @@
         <v>7</v>
       </c>
       <c r="F317" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -12492,9 +13442,12 @@
         <v>0</v>
       </c>
       <c r="K317" t="n">
+        <v>0</v>
+      </c>
+      <c r="L317" t="n">
         <v>5</v>
       </c>
-      <c r="L317" t="n">
+      <c r="M317" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12515,13 +13468,13 @@
         <v>7</v>
       </c>
       <c r="F318" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I318" t="n">
         <v>0</v>
@@ -12530,9 +13483,12 @@
         <v>0</v>
       </c>
       <c r="K318" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L318" t="n">
+        <v>7</v>
+      </c>
+      <c r="M318" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12568,9 +13524,12 @@
         <v>0</v>
       </c>
       <c r="K319" t="n">
+        <v>0</v>
+      </c>
+      <c r="L319" t="n">
         <v>4</v>
       </c>
-      <c r="L319" t="n">
+      <c r="M319" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12591,24 +13550,27 @@
         <v>19</v>
       </c>
       <c r="F320" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G320" t="n">
         <v>0</v>
       </c>
       <c r="H320" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I320" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J320" t="n">
         <v>0</v>
       </c>
       <c r="K320" t="n">
+        <v>0</v>
+      </c>
+      <c r="L320" t="n">
         <v>19</v>
       </c>
-      <c r="L320" t="n">
+      <c r="M320" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12629,24 +13591,27 @@
         <v>10</v>
       </c>
       <c r="F321" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H321" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I321" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J321" t="n">
         <v>0</v>
       </c>
       <c r="K321" t="n">
+        <v>0</v>
+      </c>
+      <c r="L321" t="n">
         <v>8</v>
       </c>
-      <c r="L321" t="n">
+      <c r="M321" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12667,7 +13632,7 @@
         <v>10</v>
       </c>
       <c r="F322" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G322" t="n">
         <v>0</v>
@@ -12682,9 +13647,12 @@
         <v>0</v>
       </c>
       <c r="K322" t="n">
+        <v>0</v>
+      </c>
+      <c r="L322" t="n">
         <v>5</v>
       </c>
-      <c r="L322" t="n">
+      <c r="M322" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12705,24 +13673,27 @@
         <v>5</v>
       </c>
       <c r="F323" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G323" t="n">
         <v>0</v>
       </c>
       <c r="H323" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J323" t="n">
         <v>0</v>
       </c>
       <c r="K323" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L323" t="n">
+        <v>1</v>
+      </c>
+      <c r="M323" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12743,7 +13714,7 @@
         <v>1</v>
       </c>
       <c r="F324" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G324" t="n">
         <v>0</v>
@@ -12761,6 +13732,9 @@
         <v>0</v>
       </c>
       <c r="L324" t="n">
+        <v>0</v>
+      </c>
+      <c r="M324" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12796,9 +13770,12 @@
         <v>0</v>
       </c>
       <c r="K325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L325" t="n">
+        <v>1</v>
+      </c>
+      <c r="M325" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12819,7 +13796,7 @@
         <v>7</v>
       </c>
       <c r="F326" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G326" t="n">
         <v>0</v>
@@ -12834,9 +13811,12 @@
         <v>0</v>
       </c>
       <c r="K326" t="n">
+        <v>0</v>
+      </c>
+      <c r="L326" t="n">
         <v>4</v>
       </c>
-      <c r="L326" t="n">
+      <c r="M326" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12857,7 +13837,7 @@
         <v>13</v>
       </c>
       <c r="F327" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G327" t="n">
         <v>0</v>
@@ -12872,9 +13852,12 @@
         <v>0</v>
       </c>
       <c r="K327" t="n">
+        <v>0</v>
+      </c>
+      <c r="L327" t="n">
         <v>5</v>
       </c>
-      <c r="L327" t="n">
+      <c r="M327" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12913,6 +13896,9 @@
         <v>0</v>
       </c>
       <c r="L328" t="n">
+        <v>0</v>
+      </c>
+      <c r="M328" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12948,9 +13934,12 @@
         <v>0</v>
       </c>
       <c r="K329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L329" t="n">
+        <v>1</v>
+      </c>
+      <c r="M329" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12971,7 +13960,7 @@
         <v>2</v>
       </c>
       <c r="F330" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G330" t="n">
         <v>0</v>
@@ -12986,9 +13975,12 @@
         <v>0</v>
       </c>
       <c r="K330" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L330" t="n">
+        <v>1</v>
+      </c>
+      <c r="M330" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13009,10 +14001,10 @@
         <v>4</v>
       </c>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -13024,9 +14016,12 @@
         <v>0</v>
       </c>
       <c r="K331" t="n">
+        <v>0</v>
+      </c>
+      <c r="L331" t="n">
         <v>5</v>
       </c>
-      <c r="L331" t="n">
+      <c r="M331" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13047,7 +14042,7 @@
         <v>5</v>
       </c>
       <c r="F332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G332" t="n">
         <v>0</v>
@@ -13062,9 +14057,12 @@
         <v>0</v>
       </c>
       <c r="K332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L332" t="n">
+        <v>1</v>
+      </c>
+      <c r="M332" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13091,18 +14089,21 @@
         <v>0</v>
       </c>
       <c r="H333" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I333" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J333" t="n">
         <v>0</v>
       </c>
       <c r="K333" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L333" t="n">
+        <v>1</v>
+      </c>
+      <c r="M333" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13123,7 +14124,7 @@
         <v>1</v>
       </c>
       <c r="F334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G334" t="n">
         <v>0</v>
@@ -13138,9 +14139,12 @@
         <v>0</v>
       </c>
       <c r="K334" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L334" t="n">
+        <v>2</v>
+      </c>
+      <c r="M334" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13179,6 +14183,9 @@
         <v>0</v>
       </c>
       <c r="L335" t="n">
+        <v>0</v>
+      </c>
+      <c r="M335" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13199,24 +14206,27 @@
         <v>4</v>
       </c>
       <c r="F336" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G336" t="n">
+        <v>0</v>
+      </c>
+      <c r="H336" t="n">
         <v>5</v>
       </c>
-      <c r="H336" t="n">
-        <v>0</v>
-      </c>
       <c r="I336" t="n">
         <v>0</v>
       </c>
       <c r="J336" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L336" t="n">
+        <v>0</v>
+      </c>
+      <c r="M336" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13237,7 +14247,7 @@
         <v>4</v>
       </c>
       <c r="F337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G337" t="n">
         <v>0</v>
@@ -13252,9 +14262,12 @@
         <v>0</v>
       </c>
       <c r="K337" t="n">
+        <v>0</v>
+      </c>
+      <c r="L337" t="n">
         <v>4</v>
       </c>
-      <c r="L337" t="n">
+      <c r="M337" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13275,7 +14288,7 @@
         <v>4</v>
       </c>
       <c r="F338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G338" t="n">
         <v>0</v>
@@ -13290,9 +14303,12 @@
         <v>0</v>
       </c>
       <c r="K338" t="n">
+        <v>0</v>
+      </c>
+      <c r="L338" t="n">
         <v>4</v>
       </c>
-      <c r="L338" t="n">
+      <c r="M338" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13316,7 +14332,7 @@
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -13328,9 +14344,12 @@
         <v>0</v>
       </c>
       <c r="K339" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L339" t="n">
+        <v>2</v>
+      </c>
+      <c r="M339" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13351,24 +14370,27 @@
         <v>4</v>
       </c>
       <c r="F340" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G340" t="n">
         <v>0</v>
       </c>
       <c r="H340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J340" t="n">
         <v>0</v>
       </c>
       <c r="K340" t="n">
+        <v>0</v>
+      </c>
+      <c r="L340" t="n">
         <v>5</v>
       </c>
-      <c r="L340" t="n">
+      <c r="M340" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13389,7 +14411,7 @@
         <v>6</v>
       </c>
       <c r="F341" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G341" t="n">
         <v>0</v>
@@ -13404,9 +14426,12 @@
         <v>0</v>
       </c>
       <c r="K341" t="n">
+        <v>0</v>
+      </c>
+      <c r="L341" t="n">
         <v>4</v>
       </c>
-      <c r="L341" t="n">
+      <c r="M341" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13445,6 +14470,9 @@
         <v>0</v>
       </c>
       <c r="L342" t="n">
+        <v>0</v>
+      </c>
+      <c r="M342" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13483,6 +14511,9 @@
         <v>0</v>
       </c>
       <c r="L343" t="n">
+        <v>0</v>
+      </c>
+      <c r="M343" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13503,7 +14534,7 @@
         <v>4</v>
       </c>
       <c r="F344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G344" t="n">
         <v>0</v>
@@ -13518,9 +14549,12 @@
         <v>0</v>
       </c>
       <c r="K344" t="n">
+        <v>0</v>
+      </c>
+      <c r="L344" t="n">
         <v>5</v>
       </c>
-      <c r="L344" t="n">
+      <c r="M344" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13556,9 +14590,12 @@
         <v>0</v>
       </c>
       <c r="K345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L345" t="n">
+        <v>1</v>
+      </c>
+      <c r="M345" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13591,12 +14628,15 @@
         <v>0</v>
       </c>
       <c r="J346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K346" t="n">
+        <v>1</v>
+      </c>
+      <c r="L346" t="n">
         <v>3</v>
       </c>
-      <c r="L346" t="n">
+      <c r="M346" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13617,24 +14657,27 @@
         <v>7</v>
       </c>
       <c r="F347" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G347" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H347" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I347" t="n">
         <v>0</v>
       </c>
       <c r="J347" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K347" t="n">
         <v>1</v>
       </c>
       <c r="L347" t="n">
+        <v>1</v>
+      </c>
+      <c r="M347" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13655,7 +14698,7 @@
         <v>6</v>
       </c>
       <c r="F348" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G348" t="n">
         <v>0</v>
@@ -13670,9 +14713,12 @@
         <v>0</v>
       </c>
       <c r="K348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L348" t="n">
+        <v>1</v>
+      </c>
+      <c r="M348" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13693,7 +14739,7 @@
         <v>7</v>
       </c>
       <c r="F349" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G349" t="n">
         <v>0</v>
@@ -13708,9 +14754,12 @@
         <v>0</v>
       </c>
       <c r="K349" t="n">
+        <v>0</v>
+      </c>
+      <c r="L349" t="n">
         <v>3</v>
       </c>
-      <c r="L349" t="n">
+      <c r="M349" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13746,9 +14795,12 @@
         <v>0</v>
       </c>
       <c r="K350" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L350" t="n">
+        <v>2</v>
+      </c>
+      <c r="M350" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13775,18 +14827,21 @@
         <v>0</v>
       </c>
       <c r="H351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J351" t="n">
         <v>0</v>
       </c>
       <c r="K351" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L351" t="n">
+        <v>2</v>
+      </c>
+      <c r="M351" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13819,12 +14874,15 @@
         <v>0</v>
       </c>
       <c r="J352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L352" t="n">
+        <v>0</v>
+      </c>
+      <c r="M352" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13845,24 +14903,27 @@
         <v>12</v>
       </c>
       <c r="F353" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G353" t="n">
         <v>0</v>
       </c>
       <c r="H353" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I353" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J353" t="n">
         <v>0</v>
       </c>
       <c r="K353" t="n">
+        <v>0</v>
+      </c>
+      <c r="L353" t="n">
         <v>3</v>
       </c>
-      <c r="L353" t="n">
+      <c r="M353" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13883,24 +14944,27 @@
         <v>9</v>
       </c>
       <c r="F354" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
       </c>
       <c r="I354" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J354" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K354" t="n">
+        <v>1</v>
+      </c>
+      <c r="L354" t="n">
         <v>5</v>
       </c>
-      <c r="L354" t="n">
+      <c r="M354" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13939,6 +15003,9 @@
         <v>0</v>
       </c>
       <c r="L355" t="n">
+        <v>0</v>
+      </c>
+      <c r="M355" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13977,6 +15044,9 @@
         <v>0</v>
       </c>
       <c r="L356" t="n">
+        <v>0</v>
+      </c>
+      <c r="M356" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14015,6 +15085,9 @@
         <v>0</v>
       </c>
       <c r="L357" t="n">
+        <v>0</v>
+      </c>
+      <c r="M357" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14035,7 +15108,7 @@
         <v>2</v>
       </c>
       <c r="F358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G358" t="n">
         <v>0</v>
@@ -14050,9 +15123,12 @@
         <v>0</v>
       </c>
       <c r="K358" t="n">
+        <v>0</v>
+      </c>
+      <c r="L358" t="n">
         <v>3</v>
       </c>
-      <c r="L358" t="n">
+      <c r="M358" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14073,24 +15149,27 @@
         <v>10</v>
       </c>
       <c r="F359" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H359" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I359" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K359" t="n">
+        <v>1</v>
+      </c>
+      <c r="L359" t="n">
         <v>5</v>
       </c>
-      <c r="L359" t="n">
+      <c r="M359" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14111,24 +15190,27 @@
         <v>15</v>
       </c>
       <c r="F360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G360" t="n">
         <v>0</v>
       </c>
       <c r="H360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K360" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L360" t="n">
+        <v>2</v>
+      </c>
+      <c r="M360" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14149,13 +15231,13 @@
         <v>3</v>
       </c>
       <c r="F361" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G361" t="n">
         <v>1</v>
       </c>
       <c r="H361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I361" t="n">
         <v>0</v>
@@ -14164,9 +15246,12 @@
         <v>0</v>
       </c>
       <c r="K361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L361" t="n">
+        <v>1</v>
+      </c>
+      <c r="M361" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14187,10 +15272,10 @@
         <v>4</v>
       </c>
       <c r="F362" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -14199,12 +15284,15 @@
         <v>0</v>
       </c>
       <c r="J362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K362" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L362" t="n">
+        <v>2</v>
+      </c>
+      <c r="M362" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14225,24 +15313,27 @@
         <v>8</v>
       </c>
       <c r="F363" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G363" t="n">
         <v>0</v>
       </c>
       <c r="H363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K363" t="n">
+        <v>1</v>
+      </c>
+      <c r="L363" t="n">
         <v>3</v>
       </c>
-      <c r="L363" t="n">
+      <c r="M363" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14266,21 +15357,24 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H364" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I364" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K364" t="n">
+        <v>1</v>
+      </c>
+      <c r="L364" t="n">
         <v>9</v>
       </c>
-      <c r="L364" t="n">
+      <c r="M364" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14301,7 +15395,7 @@
         <v>9</v>
       </c>
       <c r="F365" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G365" t="n">
         <v>0</v>
@@ -14316,9 +15410,12 @@
         <v>0</v>
       </c>
       <c r="K365" t="n">
+        <v>0</v>
+      </c>
+      <c r="L365" t="n">
         <v>4</v>
       </c>
-      <c r="L365" t="n">
+      <c r="M365" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14339,7 +15436,7 @@
         <v>3</v>
       </c>
       <c r="F366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G366" t="n">
         <v>0</v>
@@ -14354,9 +15451,12 @@
         <v>0</v>
       </c>
       <c r="K366" t="n">
+        <v>0</v>
+      </c>
+      <c r="L366" t="n">
         <v>3</v>
       </c>
-      <c r="L366" t="n">
+      <c r="M366" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14377,7 +15477,7 @@
         <v>2</v>
       </c>
       <c r="F367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G367" t="n">
         <v>0</v>
@@ -14389,12 +15489,15 @@
         <v>0</v>
       </c>
       <c r="J367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L367" t="n">
+        <v>0</v>
+      </c>
+      <c r="M367" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14430,9 +15533,12 @@
         <v>0</v>
       </c>
       <c r="K368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L368" t="n">
+        <v>1</v>
+      </c>
+      <c r="M368" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14468,9 +15574,12 @@
         <v>0</v>
       </c>
       <c r="K369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L369" t="n">
+        <v>1</v>
+      </c>
+      <c r="M369" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14491,7 +15600,7 @@
         <v>5</v>
       </c>
       <c r="F370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G370" t="n">
         <v>0</v>
@@ -14503,12 +15612,15 @@
         <v>0</v>
       </c>
       <c r="J370" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K370" t="n">
+        <v>2</v>
+      </c>
+      <c r="L370" t="n">
         <v>3</v>
       </c>
-      <c r="L370" t="n">
+      <c r="M370" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14529,7 +15641,7 @@
         <v>3</v>
       </c>
       <c r="F371" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G371" t="n">
         <v>0</v>
@@ -14544,9 +15656,12 @@
         <v>0</v>
       </c>
       <c r="K371" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L371" t="n">
+        <v>1</v>
+      </c>
+      <c r="M371" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14567,7 +15682,7 @@
         <v>4</v>
       </c>
       <c r="F372" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G372" t="n">
         <v>0</v>
@@ -14582,9 +15697,12 @@
         <v>0</v>
       </c>
       <c r="K372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L372" t="n">
+        <v>1</v>
+      </c>
+      <c r="M372" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14617,12 +15735,15 @@
         <v>0</v>
       </c>
       <c r="J373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K373" t="n">
+        <v>1</v>
+      </c>
+      <c r="L373" t="n">
         <v>3</v>
       </c>
-      <c r="L373" t="n">
+      <c r="M373" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14643,7 +15764,7 @@
         <v>7</v>
       </c>
       <c r="F374" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G374" t="n">
         <v>0</v>
@@ -14658,9 +15779,12 @@
         <v>0</v>
       </c>
       <c r="K374" t="n">
+        <v>0</v>
+      </c>
+      <c r="L374" t="n">
         <v>10</v>
       </c>
-      <c r="L374" t="n">
+      <c r="M374" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14687,10 +15811,10 @@
         <v>0</v>
       </c>
       <c r="H375" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I375" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J375" t="n">
         <v>0</v>
@@ -14699,6 +15823,9 @@
         <v>0</v>
       </c>
       <c r="L375" t="n">
+        <v>0</v>
+      </c>
+      <c r="M375" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14722,7 +15849,7 @@
         <v>1</v>
       </c>
       <c r="G376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -14734,9 +15861,12 @@
         <v>0</v>
       </c>
       <c r="K376" t="n">
+        <v>0</v>
+      </c>
+      <c r="L376" t="n">
         <v>4</v>
       </c>
-      <c r="L376" t="n">
+      <c r="M376" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14772,9 +15902,12 @@
         <v>0</v>
       </c>
       <c r="K377" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L377" t="n">
+        <v>2</v>
+      </c>
+      <c r="M377" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14795,7 +15928,7 @@
         <v>4</v>
       </c>
       <c r="F378" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G378" t="n">
         <v>0</v>
@@ -14810,9 +15943,12 @@
         <v>0</v>
       </c>
       <c r="K378" t="n">
+        <v>0</v>
+      </c>
+      <c r="L378" t="n">
         <v>3</v>
       </c>
-      <c r="L378" t="n">
+      <c r="M378" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14845,12 +15981,15 @@
         <v>0</v>
       </c>
       <c r="J379" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K379" t="n">
+        <v>1</v>
+      </c>
+      <c r="L379" t="n">
         <v>6</v>
       </c>
-      <c r="L379" t="n">
+      <c r="M379" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14871,7 +16010,7 @@
         <v>1</v>
       </c>
       <c r="F380" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G380" t="n">
         <v>0</v>
@@ -14886,9 +16025,12 @@
         <v>0</v>
       </c>
       <c r="K380" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L380" t="n">
+        <v>2</v>
+      </c>
+      <c r="M380" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14909,7 +16051,7 @@
         <v>9</v>
       </c>
       <c r="F381" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G381" t="n">
         <v>0</v>
@@ -14921,12 +16063,15 @@
         <v>0</v>
       </c>
       <c r="J381" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K381" t="n">
+        <v>1</v>
+      </c>
+      <c r="L381" t="n">
         <v>6</v>
       </c>
-      <c r="L381" t="n">
+      <c r="M381" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14947,10 +16092,10 @@
         <v>8</v>
       </c>
       <c r="F382" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -14962,9 +16107,12 @@
         <v>0</v>
       </c>
       <c r="K382" t="n">
+        <v>0</v>
+      </c>
+      <c r="L382" t="n">
         <v>6</v>
       </c>
-      <c r="L382" t="n">
+      <c r="M382" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14985,24 +16133,27 @@
         <v>6</v>
       </c>
       <c r="F383" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G383" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J383" t="n">
         <v>0</v>
       </c>
       <c r="K383" t="n">
+        <v>0</v>
+      </c>
+      <c r="L383" t="n">
         <v>4</v>
       </c>
-      <c r="L383" t="n">
+      <c r="M383" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15026,7 +16177,7 @@
         <v>1</v>
       </c>
       <c r="G384" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -15038,9 +16189,12 @@
         <v>0</v>
       </c>
       <c r="K384" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L384" t="n">
+        <v>1</v>
+      </c>
+      <c r="M384" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15064,10 +16218,10 @@
         <v>0</v>
       </c>
       <c r="G385" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H385" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I385" t="n">
         <v>0</v>
@@ -15079,6 +16233,9 @@
         <v>0</v>
       </c>
       <c r="L385" t="n">
+        <v>0</v>
+      </c>
+      <c r="M385" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15102,21 +16259,24 @@
         <v>0</v>
       </c>
       <c r="G386" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H386" t="n">
+        <v>1</v>
+      </c>
+      <c r="I386" t="n">
         <v>4</v>
       </c>
-      <c r="I386" t="n">
-        <v>0</v>
-      </c>
       <c r="J386" t="n">
         <v>0</v>
       </c>
       <c r="K386" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L386" t="n">
+        <v>2</v>
+      </c>
+      <c r="M386" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15137,10 +16297,10 @@
         <v>5</v>
       </c>
       <c r="F387" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G387" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -15152,9 +16312,12 @@
         <v>0</v>
       </c>
       <c r="K387" t="n">
+        <v>0</v>
+      </c>
+      <c r="L387" t="n">
         <v>4</v>
       </c>
-      <c r="L387" t="n">
+      <c r="M387" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15175,7 +16338,7 @@
         <v>4</v>
       </c>
       <c r="F388" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G388" t="n">
         <v>0</v>
@@ -15193,6 +16356,9 @@
         <v>0</v>
       </c>
       <c r="L388" t="n">
+        <v>0</v>
+      </c>
+      <c r="M388" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15213,7 +16379,7 @@
         <v>5</v>
       </c>
       <c r="F389" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G389" t="n">
         <v>0</v>
@@ -15228,9 +16394,12 @@
         <v>0</v>
       </c>
       <c r="K389" t="n">
+        <v>0</v>
+      </c>
+      <c r="L389" t="n">
         <v>3</v>
       </c>
-      <c r="L389" t="n">
+      <c r="M389" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15251,24 +16420,27 @@
         <v>6</v>
       </c>
       <c r="F390" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G390" t="n">
         <v>0</v>
       </c>
       <c r="H390" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I390" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J390" t="n">
         <v>0</v>
       </c>
       <c r="K390" t="n">
+        <v>0</v>
+      </c>
+      <c r="L390" t="n">
         <v>4</v>
       </c>
-      <c r="L390" t="n">
+      <c r="M390" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15289,7 +16461,7 @@
         <v>2</v>
       </c>
       <c r="F391" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G391" t="n">
         <v>0</v>
@@ -15304,9 +16476,12 @@
         <v>0</v>
       </c>
       <c r="K391" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L391" t="n">
+        <v>1</v>
+      </c>
+      <c r="M391" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15327,10 +16502,10 @@
         <v>11</v>
       </c>
       <c r="F392" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G392" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -15339,12 +16514,15 @@
         <v>0</v>
       </c>
       <c r="J392" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K392" t="n">
+        <v>2</v>
+      </c>
+      <c r="L392" t="n">
         <v>11</v>
       </c>
-      <c r="L392" t="n">
+      <c r="M392" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15365,24 +16543,27 @@
         <v>10</v>
       </c>
       <c r="F393" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G393" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H393" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I393" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J393" t="n">
         <v>0</v>
       </c>
       <c r="K393" t="n">
+        <v>0</v>
+      </c>
+      <c r="L393" t="n">
         <v>8</v>
       </c>
-      <c r="L393" t="n">
+      <c r="M393" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15421,6 +16602,9 @@
         <v>0</v>
       </c>
       <c r="L394" t="n">
+        <v>0</v>
+      </c>
+      <c r="M394" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15456,9 +16640,12 @@
         <v>0</v>
       </c>
       <c r="K395" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L395" t="n">
+        <v>2</v>
+      </c>
+      <c r="M395" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15479,10 +16666,10 @@
         <v>4</v>
       </c>
       <c r="F396" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G396" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -15494,9 +16681,12 @@
         <v>0</v>
       </c>
       <c r="K396" t="n">
+        <v>0</v>
+      </c>
+      <c r="L396" t="n">
         <v>4</v>
       </c>
-      <c r="L396" t="n">
+      <c r="M396" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15517,24 +16707,27 @@
         <v>22</v>
       </c>
       <c r="F397" t="n">
+        <v>2</v>
+      </c>
+      <c r="G397" t="n">
         <v>3</v>
       </c>
-      <c r="G397" t="n">
-        <v>0</v>
-      </c>
       <c r="H397" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I397" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J397" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K397" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="L397" t="n">
+        <v>17</v>
+      </c>
+      <c r="M397" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15555,24 +16748,27 @@
         <v>22</v>
       </c>
       <c r="F398" t="n">
+        <v>2</v>
+      </c>
+      <c r="G398" t="n">
         <v>4</v>
       </c>
-      <c r="G398" t="n">
-        <v>0</v>
-      </c>
       <c r="H398" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I398" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J398" t="n">
         <v>0</v>
       </c>
       <c r="K398" t="n">
+        <v>0</v>
+      </c>
+      <c r="L398" t="n">
         <v>16</v>
       </c>
-      <c r="L398" t="n">
+      <c r="M398" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15596,21 +16792,24 @@
         <v>0</v>
       </c>
       <c r="G399" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H399" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I399" t="n">
         <v>0</v>
       </c>
       <c r="J399" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K399" t="n">
+        <v>2</v>
+      </c>
+      <c r="L399" t="n">
         <v>3</v>
       </c>
-      <c r="L399" t="n">
+      <c r="M399" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15646,9 +16845,12 @@
         <v>0</v>
       </c>
       <c r="K400" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L400" t="n">
+        <v>2</v>
+      </c>
+      <c r="M400" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15669,7 +16871,7 @@
         <v>11</v>
       </c>
       <c r="F401" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G401" t="n">
         <v>0</v>
@@ -15681,12 +16883,15 @@
         <v>0</v>
       </c>
       <c r="J401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K401" t="n">
+        <v>1</v>
+      </c>
+      <c r="L401" t="n">
         <v>6</v>
       </c>
-      <c r="L401" t="n">
+      <c r="M401" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15707,10 +16912,10 @@
         <v>24</v>
       </c>
       <c r="F402" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G402" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -15722,9 +16927,12 @@
         <v>0</v>
       </c>
       <c r="K402" t="n">
+        <v>0</v>
+      </c>
+      <c r="L402" t="n">
         <v>21</v>
       </c>
-      <c r="L402" t="n">
+      <c r="M402" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15745,7 +16953,7 @@
         <v>0</v>
       </c>
       <c r="F403" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G403" t="n">
         <v>0</v>
@@ -15763,6 +16971,9 @@
         <v>0</v>
       </c>
       <c r="L403" t="n">
+        <v>0</v>
+      </c>
+      <c r="M403" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15783,7 +16994,7 @@
         <v>7</v>
       </c>
       <c r="F404" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G404" t="n">
         <v>0</v>
@@ -15798,9 +17009,12 @@
         <v>0</v>
       </c>
       <c r="K404" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L404" t="n">
+        <v>2</v>
+      </c>
+      <c r="M404" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15821,24 +17035,27 @@
         <v>3</v>
       </c>
       <c r="F405" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G405" t="n">
         <v>0</v>
       </c>
       <c r="H405" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I405" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J405" t="n">
         <v>0</v>
       </c>
       <c r="K405" t="n">
+        <v>0</v>
+      </c>
+      <c r="L405" t="n">
         <v>3</v>
       </c>
-      <c r="L405" t="n">
+      <c r="M405" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15877,6 +17094,9 @@
         <v>0</v>
       </c>
       <c r="L406" t="n">
+        <v>0</v>
+      </c>
+      <c r="M406" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15897,7 +17117,7 @@
         <v>1</v>
       </c>
       <c r="F407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G407" t="n">
         <v>0</v>
@@ -15909,12 +17129,15 @@
         <v>0</v>
       </c>
       <c r="J407" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L407" t="n">
+        <v>0</v>
+      </c>
+      <c r="M407" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15935,24 +17158,27 @@
         <v>4</v>
       </c>
       <c r="F408" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G408" t="n">
         <v>0</v>
       </c>
       <c r="H408" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I408" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J408" t="n">
         <v>0</v>
       </c>
       <c r="K408" t="n">
+        <v>0</v>
+      </c>
+      <c r="L408" t="n">
         <v>3</v>
       </c>
-      <c r="L408" t="n">
+      <c r="M408" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15973,24 +17199,27 @@
         <v>20</v>
       </c>
       <c r="F409" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G409" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H409" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I409" t="n">
         <v>0</v>
       </c>
       <c r="J409" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K409" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L409" t="n">
+        <v>7</v>
+      </c>
+      <c r="M409" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16011,7 +17240,7 @@
         <v>5</v>
       </c>
       <c r="F410" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G410" t="n">
         <v>0</v>
@@ -16026,9 +17255,12 @@
         <v>0</v>
       </c>
       <c r="K410" t="n">
+        <v>0</v>
+      </c>
+      <c r="L410" t="n">
         <v>6</v>
       </c>
-      <c r="L410" t="n">
+      <c r="M410" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16049,13 +17281,13 @@
         <v>24</v>
       </c>
       <c r="F411" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G411" t="n">
         <v>1</v>
       </c>
       <c r="H411" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I411" t="n">
         <v>0</v>
@@ -16064,9 +17296,12 @@
         <v>0</v>
       </c>
       <c r="K411" t="n">
+        <v>0</v>
+      </c>
+      <c r="L411" t="n">
         <v>9</v>
       </c>
-      <c r="L411" t="n">
+      <c r="M411" t="n">
         <v>2011</v>
       </c>
     </row>

--- a/Excel Files IPEDS/Trimmed/c2011_trimmed_file.xlsx
+++ b/Excel Files IPEDS/Trimmed/c2011_trimmed_file.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M411"/>
+  <dimension ref="A1:O411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,6 +491,16 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>C2MORT</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>CNRALT</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Year</t>
         </is>
       </c>
@@ -533,6 +543,12 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -574,6 +590,12 @@
         <v>4</v>
       </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -615,6 +637,12 @@
         <v>2</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -656,6 +684,12 @@
         <v>8</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -697,6 +731,12 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -738,6 +778,12 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -779,6 +825,12 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -820,6 +872,12 @@
         <v>3</v>
       </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -861,6 +919,12 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -902,6 +966,12 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -943,6 +1013,12 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -984,6 +1060,12 @@
         <v>4</v>
       </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8</v>
+      </c>
+      <c r="O13" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1025,6 +1107,12 @@
         <v>4</v>
       </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1066,6 +1154,12 @@
         <v>6</v>
       </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4</v>
+      </c>
+      <c r="O15" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1107,6 +1201,12 @@
         <v>1</v>
       </c>
       <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
+      </c>
+      <c r="O16" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1148,6 +1248,12 @@
         <v>3</v>
       </c>
       <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1189,6 +1295,12 @@
         <v>3</v>
       </c>
       <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1230,6 +1342,12 @@
         <v>2</v>
       </c>
       <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1271,6 +1389,12 @@
         <v>4</v>
       </c>
       <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
+      </c>
+      <c r="O20" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1312,6 +1436,12 @@
         <v>10</v>
       </c>
       <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>14</v>
+      </c>
+      <c r="O21" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1353,6 +1483,12 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1394,6 +1530,12 @@
         <v>3</v>
       </c>
       <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1435,6 +1577,12 @@
         <v>3</v>
       </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1476,6 +1624,12 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1517,6 +1671,12 @@
         <v>3</v>
       </c>
       <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1558,6 +1718,12 @@
         <v>18</v>
       </c>
       <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
+      </c>
+      <c r="O27" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1599,6 +1765,12 @@
         <v>15</v>
       </c>
       <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>5</v>
+      </c>
+      <c r="O28" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1640,6 +1812,12 @@
         <v>19</v>
       </c>
       <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1681,6 +1859,12 @@
         <v>5</v>
       </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>6</v>
+      </c>
+      <c r="O30" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1722,6 +1906,12 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1763,6 +1953,12 @@
         <v>17</v>
       </c>
       <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3</v>
+      </c>
+      <c r="O32" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1804,6 +2000,12 @@
         <v>3</v>
       </c>
       <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1845,6 +2047,12 @@
         <v>7</v>
       </c>
       <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1886,6 +2094,12 @@
         <v>14</v>
       </c>
       <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2</v>
+      </c>
+      <c r="O35" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1927,6 +2141,12 @@
         <v>8</v>
       </c>
       <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>11</v>
+      </c>
+      <c r="O36" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -1968,6 +2188,12 @@
         <v>3</v>
       </c>
       <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>7</v>
+      </c>
+      <c r="O37" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2009,6 +2235,12 @@
         <v>15</v>
       </c>
       <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2</v>
+      </c>
+      <c r="O38" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2050,6 +2282,12 @@
         <v>10</v>
       </c>
       <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2091,6 +2329,12 @@
         <v>13</v>
       </c>
       <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2132,6 +2376,12 @@
         <v>20</v>
       </c>
       <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>6</v>
+      </c>
+      <c r="O41" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2173,6 +2423,12 @@
         <v>8</v>
       </c>
       <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2214,6 +2470,12 @@
         <v>4</v>
       </c>
       <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2</v>
+      </c>
+      <c r="O43" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2255,6 +2517,12 @@
         <v>3</v>
       </c>
       <c r="M44" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2296,6 +2564,12 @@
         <v>7</v>
       </c>
       <c r="M45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2337,6 +2611,12 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2378,6 +2658,12 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3</v>
+      </c>
+      <c r="O47" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2419,6 +2705,12 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>9</v>
+      </c>
+      <c r="O48" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2460,6 +2752,12 @@
         <v>9</v>
       </c>
       <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>8</v>
+      </c>
+      <c r="O49" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2501,6 +2799,12 @@
         <v>22</v>
       </c>
       <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2</v>
+      </c>
+      <c r="O50" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2542,6 +2846,12 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2583,6 +2893,12 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2624,6 +2940,12 @@
         <v>4</v>
       </c>
       <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2665,6 +2987,12 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2706,6 +3034,12 @@
         <v>6</v>
       </c>
       <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>2</v>
+      </c>
+      <c r="O55" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2747,6 +3081,12 @@
         <v>2</v>
       </c>
       <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2788,6 +3128,12 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2829,6 +3175,12 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2870,6 +3222,12 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2911,6 +3269,12 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2952,6 +3316,12 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>2</v>
+      </c>
+      <c r="O61" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -2993,6 +3363,12 @@
         <v>6</v>
       </c>
       <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>10</v>
+      </c>
+      <c r="O62" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3034,6 +3410,12 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3075,6 +3457,12 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>1</v>
+      </c>
+      <c r="O64" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3116,6 +3504,12 @@
         <v>4</v>
       </c>
       <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>2</v>
+      </c>
+      <c r="O65" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3157,6 +3551,12 @@
         <v>8</v>
       </c>
       <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>2</v>
+      </c>
+      <c r="O66" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3198,6 +3598,12 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3239,6 +3645,12 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>1</v>
+      </c>
+      <c r="O68" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3280,6 +3692,12 @@
         <v>2</v>
       </c>
       <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>11</v>
+      </c>
+      <c r="O69" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3321,6 +3739,12 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3362,6 +3786,12 @@
         <v>2</v>
       </c>
       <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3403,6 +3833,12 @@
         <v>2</v>
       </c>
       <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>3</v>
+      </c>
+      <c r="O72" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3444,6 +3880,12 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>5</v>
+      </c>
+      <c r="O73" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3485,6 +3927,12 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>2</v>
+      </c>
+      <c r="O74" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3526,6 +3974,12 @@
         <v>2</v>
       </c>
       <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3567,6 +4021,12 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>2</v>
+      </c>
+      <c r="O76" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3608,6 +4068,12 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>2</v>
+      </c>
+      <c r="O77" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3649,6 +4115,12 @@
         <v>4</v>
       </c>
       <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>16</v>
+      </c>
+      <c r="O78" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3690,6 +4162,12 @@
         <v>3</v>
       </c>
       <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>4</v>
+      </c>
+      <c r="O79" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3731,6 +4209,12 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3772,6 +4256,12 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3813,6 +4303,12 @@
         <v>2</v>
       </c>
       <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>6</v>
+      </c>
+      <c r="O82" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3854,6 +4350,12 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>2</v>
+      </c>
+      <c r="O83" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3895,6 +4397,12 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3936,6 +4444,12 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -3977,6 +4491,12 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>3</v>
+      </c>
+      <c r="O86" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4018,6 +4538,12 @@
         <v>4</v>
       </c>
       <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>4</v>
+      </c>
+      <c r="O87" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4059,6 +4585,12 @@
         <v>7</v>
       </c>
       <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>9</v>
+      </c>
+      <c r="O88" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4100,6 +4632,12 @@
         <v>4</v>
       </c>
       <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>1</v>
+      </c>
+      <c r="O89" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4141,6 +4679,12 @@
         <v>6</v>
       </c>
       <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>15</v>
+      </c>
+      <c r="O90" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4182,6 +4726,12 @@
         <v>0</v>
       </c>
       <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>1</v>
+      </c>
+      <c r="O91" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4223,6 +4773,12 @@
         <v>2</v>
       </c>
       <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>4</v>
+      </c>
+      <c r="O92" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4264,6 +4820,12 @@
         <v>3</v>
       </c>
       <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>3</v>
+      </c>
+      <c r="O93" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4305,6 +4867,12 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>1</v>
+      </c>
+      <c r="O94" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4346,6 +4914,12 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>2</v>
+      </c>
+      <c r="O95" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4387,6 +4961,12 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>2</v>
+      </c>
+      <c r="O96" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4428,6 +5008,12 @@
         <v>7</v>
       </c>
       <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>3</v>
+      </c>
+      <c r="O97" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4469,6 +5055,12 @@
         <v>8</v>
       </c>
       <c r="M98" t="n">
+        <v>1</v>
+      </c>
+      <c r="N98" t="n">
+        <v>11</v>
+      </c>
+      <c r="O98" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4510,6 +5102,12 @@
         <v>3</v>
       </c>
       <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>2</v>
+      </c>
+      <c r="O99" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4551,6 +5149,12 @@
         <v>0</v>
       </c>
       <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>2</v>
+      </c>
+      <c r="O100" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4592,6 +5196,12 @@
         <v>5</v>
       </c>
       <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>7</v>
+      </c>
+      <c r="O101" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4633,6 +5243,12 @@
         <v>0</v>
       </c>
       <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>1</v>
+      </c>
+      <c r="O102" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4674,6 +5290,12 @@
         <v>2</v>
       </c>
       <c r="M103" t="n">
+        <v>1</v>
+      </c>
+      <c r="N103" t="n">
+        <v>2</v>
+      </c>
+      <c r="O103" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4715,6 +5337,12 @@
         <v>8</v>
       </c>
       <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
+        <v>1</v>
+      </c>
+      <c r="O104" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4756,6 +5384,12 @@
         <v>0</v>
       </c>
       <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>4</v>
+      </c>
+      <c r="O105" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4797,6 +5431,12 @@
         <v>3</v>
       </c>
       <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>4</v>
+      </c>
+      <c r="O106" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4838,6 +5478,12 @@
         <v>0</v>
       </c>
       <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4879,6 +5525,12 @@
         <v>4</v>
       </c>
       <c r="M108" t="n">
+        <v>1</v>
+      </c>
+      <c r="N108" t="n">
+        <v>9</v>
+      </c>
+      <c r="O108" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4920,6 +5572,12 @@
         <v>7</v>
       </c>
       <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
+        <v>3</v>
+      </c>
+      <c r="O109" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4961,6 +5619,12 @@
         <v>5</v>
       </c>
       <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5002,6 +5666,12 @@
         <v>2</v>
       </c>
       <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="n">
+        <v>4</v>
+      </c>
+      <c r="O111" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5043,6 +5713,12 @@
         <v>0</v>
       </c>
       <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="n">
+        <v>2</v>
+      </c>
+      <c r="O112" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5084,6 +5760,12 @@
         <v>3</v>
       </c>
       <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="n">
+        <v>6</v>
+      </c>
+      <c r="O113" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5125,6 +5807,12 @@
         <v>19</v>
       </c>
       <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="n">
+        <v>18</v>
+      </c>
+      <c r="O114" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5166,6 +5854,12 @@
         <v>0</v>
       </c>
       <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5207,6 +5901,12 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="n">
+        <v>1</v>
+      </c>
+      <c r="O116" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5248,6 +5948,12 @@
         <v>6</v>
       </c>
       <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5289,6 +5995,12 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5330,6 +6042,12 @@
         <v>2</v>
       </c>
       <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5371,6 +6089,12 @@
         <v>0</v>
       </c>
       <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
+        <v>2</v>
+      </c>
+      <c r="O120" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5412,6 +6136,12 @@
         <v>0</v>
       </c>
       <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5453,6 +6183,12 @@
         <v>0</v>
       </c>
       <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5494,6 +6230,12 @@
         <v>2</v>
       </c>
       <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5535,6 +6277,12 @@
         <v>2</v>
       </c>
       <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>5</v>
+      </c>
+      <c r="O124" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5576,6 +6324,12 @@
         <v>7</v>
       </c>
       <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5617,6 +6371,12 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>1</v>
+      </c>
+      <c r="O126" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5658,6 +6418,12 @@
         <v>6</v>
       </c>
       <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>2</v>
+      </c>
+      <c r="O127" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5699,6 +6465,12 @@
         <v>4</v>
       </c>
       <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
+        <v>6</v>
+      </c>
+      <c r="O128" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5740,6 +6512,12 @@
         <v>9</v>
       </c>
       <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>7</v>
+      </c>
+      <c r="O129" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5781,6 +6559,12 @@
         <v>3</v>
       </c>
       <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="n">
+        <v>6</v>
+      </c>
+      <c r="O130" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5822,6 +6606,12 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5863,6 +6653,12 @@
         <v>4</v>
       </c>
       <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
+        <v>2</v>
+      </c>
+      <c r="O132" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5904,6 +6700,12 @@
         <v>8</v>
       </c>
       <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
+        <v>6</v>
+      </c>
+      <c r="O133" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5945,6 +6747,12 @@
         <v>3</v>
       </c>
       <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -5986,6 +6794,12 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="n">
+        <v>3</v>
+      </c>
+      <c r="O135" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6027,6 +6841,12 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="n">
+        <v>1</v>
+      </c>
+      <c r="O136" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6068,6 +6888,12 @@
         <v>2</v>
       </c>
       <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
+        <v>7</v>
+      </c>
+      <c r="O137" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6109,6 +6935,12 @@
         <v>0</v>
       </c>
       <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6150,6 +6982,12 @@
         <v>4</v>
       </c>
       <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="n">
+        <v>4</v>
+      </c>
+      <c r="O139" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6191,6 +7029,12 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>3</v>
+      </c>
+      <c r="O140" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6232,6 +7076,12 @@
         <v>7</v>
       </c>
       <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>3</v>
+      </c>
+      <c r="O141" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6273,6 +7123,12 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6314,6 +7170,12 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>1</v>
+      </c>
+      <c r="O143" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6355,6 +7217,12 @@
         <v>6</v>
       </c>
       <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>5</v>
+      </c>
+      <c r="O144" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6396,6 +7264,12 @@
         <v>3</v>
       </c>
       <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="n">
+        <v>4</v>
+      </c>
+      <c r="O145" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6437,6 +7311,12 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" t="n">
+        <v>2</v>
+      </c>
+      <c r="O146" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6478,6 +7358,12 @@
         <v>0</v>
       </c>
       <c r="M147" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6519,6 +7405,12 @@
         <v>4</v>
       </c>
       <c r="M148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6560,6 +7452,12 @@
         <v>0</v>
       </c>
       <c r="M149" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" t="n">
+        <v>5</v>
+      </c>
+      <c r="O149" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6601,6 +7499,12 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="n">
+        <v>1</v>
+      </c>
+      <c r="O150" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6642,6 +7546,12 @@
         <v>2</v>
       </c>
       <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6683,6 +7593,12 @@
         <v>7</v>
       </c>
       <c r="M152" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" t="n">
+        <v>1</v>
+      </c>
+      <c r="O152" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6724,6 +7640,12 @@
         <v>8</v>
       </c>
       <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="n">
+        <v>5</v>
+      </c>
+      <c r="O153" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6765,6 +7687,12 @@
         <v>4</v>
       </c>
       <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="n">
+        <v>7</v>
+      </c>
+      <c r="O154" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6806,6 +7734,12 @@
         <v>4</v>
       </c>
       <c r="M155" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" t="n">
+        <v>2</v>
+      </c>
+      <c r="O155" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6847,6 +7781,12 @@
         <v>0</v>
       </c>
       <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="n">
+        <v>2</v>
+      </c>
+      <c r="O156" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6888,6 +7828,12 @@
         <v>10</v>
       </c>
       <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="n">
+        <v>4</v>
+      </c>
+      <c r="O157" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6929,6 +7875,12 @@
         <v>25</v>
       </c>
       <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="n">
+        <v>12</v>
+      </c>
+      <c r="O158" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -6970,6 +7922,12 @@
         <v>4</v>
       </c>
       <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7011,6 +7969,12 @@
         <v>0</v>
       </c>
       <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="n">
+        <v>5</v>
+      </c>
+      <c r="O160" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7052,6 +8016,12 @@
         <v>6</v>
       </c>
       <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="n">
+        <v>1</v>
+      </c>
+      <c r="O161" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7093,6 +8063,12 @@
         <v>4</v>
       </c>
       <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>5</v>
+      </c>
+      <c r="O162" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7134,6 +8110,12 @@
         <v>2</v>
       </c>
       <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7175,6 +8157,12 @@
         <v>3</v>
       </c>
       <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="n">
+        <v>2</v>
+      </c>
+      <c r="O164" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7216,6 +8204,12 @@
         <v>2</v>
       </c>
       <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7257,6 +8251,12 @@
         <v>0</v>
       </c>
       <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="n">
+        <v>1</v>
+      </c>
+      <c r="O166" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7298,6 +8298,12 @@
         <v>17</v>
       </c>
       <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="n">
+        <v>14</v>
+      </c>
+      <c r="O167" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7339,6 +8345,12 @@
         <v>10</v>
       </c>
       <c r="M168" t="n">
+        <v>1</v>
+      </c>
+      <c r="N168" t="n">
+        <v>19</v>
+      </c>
+      <c r="O168" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7380,6 +8392,12 @@
         <v>3</v>
       </c>
       <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="n">
+        <v>6</v>
+      </c>
+      <c r="O169" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7421,6 +8439,12 @@
         <v>1</v>
       </c>
       <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="n">
+        <v>5</v>
+      </c>
+      <c r="O170" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7462,6 +8486,12 @@
         <v>1</v>
       </c>
       <c r="M171" t="n">
+        <v>0</v>
+      </c>
+      <c r="N171" t="n">
+        <v>4</v>
+      </c>
+      <c r="O171" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7503,6 +8533,12 @@
         <v>1</v>
       </c>
       <c r="M172" t="n">
+        <v>0</v>
+      </c>
+      <c r="N172" t="n">
+        <v>6</v>
+      </c>
+      <c r="O172" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7544,6 +8580,12 @@
         <v>2</v>
       </c>
       <c r="M173" t="n">
+        <v>0</v>
+      </c>
+      <c r="N173" t="n">
+        <v>2</v>
+      </c>
+      <c r="O173" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7585,6 +8627,12 @@
         <v>1</v>
       </c>
       <c r="M174" t="n">
+        <v>0</v>
+      </c>
+      <c r="N174" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7626,6 +8674,12 @@
         <v>9</v>
       </c>
       <c r="M175" t="n">
+        <v>0</v>
+      </c>
+      <c r="N175" t="n">
+        <v>16</v>
+      </c>
+      <c r="O175" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7667,6 +8721,12 @@
         <v>0</v>
       </c>
       <c r="M176" t="n">
+        <v>0</v>
+      </c>
+      <c r="N176" t="n">
+        <v>2</v>
+      </c>
+      <c r="O176" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7708,6 +8768,12 @@
         <v>1</v>
       </c>
       <c r="M177" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" t="n">
+        <v>8</v>
+      </c>
+      <c r="O177" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7749,6 +8815,12 @@
         <v>0</v>
       </c>
       <c r="M178" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" t="n">
+        <v>4</v>
+      </c>
+      <c r="O178" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7790,6 +8862,12 @@
         <v>4</v>
       </c>
       <c r="M179" t="n">
+        <v>0</v>
+      </c>
+      <c r="N179" t="n">
+        <v>1</v>
+      </c>
+      <c r="O179" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7831,6 +8909,12 @@
         <v>3</v>
       </c>
       <c r="M180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" t="n">
+        <v>2</v>
+      </c>
+      <c r="O180" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7872,6 +8956,12 @@
         <v>1</v>
       </c>
       <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7913,6 +9003,12 @@
         <v>1</v>
       </c>
       <c r="M182" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" t="n">
+        <v>1</v>
+      </c>
+      <c r="O182" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7954,6 +9050,12 @@
         <v>3</v>
       </c>
       <c r="M183" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" t="n">
+        <v>5</v>
+      </c>
+      <c r="O183" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -7995,6 +9097,12 @@
         <v>2</v>
       </c>
       <c r="M184" t="n">
+        <v>0</v>
+      </c>
+      <c r="N184" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8036,6 +9144,12 @@
         <v>5</v>
       </c>
       <c r="M185" t="n">
+        <v>0</v>
+      </c>
+      <c r="N185" t="n">
+        <v>4</v>
+      </c>
+      <c r="O185" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8077,6 +9191,12 @@
         <v>14</v>
       </c>
       <c r="M186" t="n">
+        <v>2</v>
+      </c>
+      <c r="N186" t="n">
+        <v>4</v>
+      </c>
+      <c r="O186" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8118,6 +9238,12 @@
         <v>7</v>
       </c>
       <c r="M187" t="n">
+        <v>0</v>
+      </c>
+      <c r="N187" t="n">
+        <v>5</v>
+      </c>
+      <c r="O187" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8159,6 +9285,12 @@
         <v>2</v>
       </c>
       <c r="M188" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" t="n">
+        <v>6</v>
+      </c>
+      <c r="O188" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8200,6 +9332,12 @@
         <v>0</v>
       </c>
       <c r="M189" t="n">
+        <v>0</v>
+      </c>
+      <c r="N189" t="n">
+        <v>2</v>
+      </c>
+      <c r="O189" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8241,6 +9379,12 @@
         <v>0</v>
       </c>
       <c r="M190" t="n">
+        <v>0</v>
+      </c>
+      <c r="N190" t="n">
+        <v>2</v>
+      </c>
+      <c r="O190" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8282,6 +9426,12 @@
         <v>1</v>
       </c>
       <c r="M191" t="n">
+        <v>0</v>
+      </c>
+      <c r="N191" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8323,6 +9473,12 @@
         <v>1</v>
       </c>
       <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="n">
+        <v>6</v>
+      </c>
+      <c r="O192" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8364,6 +9520,12 @@
         <v>4</v>
       </c>
       <c r="M193" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" t="n">
+        <v>5</v>
+      </c>
+      <c r="O193" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8405,6 +9567,12 @@
         <v>1</v>
       </c>
       <c r="M194" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" t="n">
+        <v>3</v>
+      </c>
+      <c r="O194" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8446,6 +9614,12 @@
         <v>1</v>
       </c>
       <c r="M195" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" t="n">
+        <v>3</v>
+      </c>
+      <c r="O195" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8487,6 +9661,12 @@
         <v>1</v>
       </c>
       <c r="M196" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" t="n">
+        <v>1</v>
+      </c>
+      <c r="O196" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8528,6 +9708,12 @@
         <v>5</v>
       </c>
       <c r="M197" t="n">
+        <v>0</v>
+      </c>
+      <c r="N197" t="n">
+        <v>2</v>
+      </c>
+      <c r="O197" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8569,6 +9755,12 @@
         <v>10</v>
       </c>
       <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="n">
+        <v>5</v>
+      </c>
+      <c r="O198" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8610,6 +9802,12 @@
         <v>0</v>
       </c>
       <c r="M199" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" t="n">
+        <v>5</v>
+      </c>
+      <c r="O199" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8651,6 +9849,12 @@
         <v>0</v>
       </c>
       <c r="M200" t="n">
+        <v>0</v>
+      </c>
+      <c r="N200" t="n">
+        <v>0</v>
+      </c>
+      <c r="O200" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8692,6 +9896,12 @@
         <v>1</v>
       </c>
       <c r="M201" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8733,6 +9943,12 @@
         <v>1</v>
       </c>
       <c r="M202" t="n">
+        <v>0</v>
+      </c>
+      <c r="N202" t="n">
+        <v>6</v>
+      </c>
+      <c r="O202" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8774,6 +9990,12 @@
         <v>1</v>
       </c>
       <c r="M203" t="n">
+        <v>0</v>
+      </c>
+      <c r="N203" t="n">
+        <v>4</v>
+      </c>
+      <c r="O203" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8815,6 +10037,12 @@
         <v>2</v>
       </c>
       <c r="M204" t="n">
+        <v>0</v>
+      </c>
+      <c r="N204" t="n">
+        <v>6</v>
+      </c>
+      <c r="O204" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8856,6 +10084,12 @@
         <v>2</v>
       </c>
       <c r="M205" t="n">
+        <v>0</v>
+      </c>
+      <c r="N205" t="n">
+        <v>4</v>
+      </c>
+      <c r="O205" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8897,6 +10131,12 @@
         <v>3</v>
       </c>
       <c r="M206" t="n">
+        <v>0</v>
+      </c>
+      <c r="N206" t="n">
+        <v>6</v>
+      </c>
+      <c r="O206" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8938,6 +10178,12 @@
         <v>1</v>
       </c>
       <c r="M207" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" t="n">
+        <v>2</v>
+      </c>
+      <c r="O207" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -8979,6 +10225,12 @@
         <v>0</v>
       </c>
       <c r="M208" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" t="n">
+        <v>4</v>
+      </c>
+      <c r="O208" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9020,6 +10272,12 @@
         <v>3</v>
       </c>
       <c r="M209" t="n">
+        <v>0</v>
+      </c>
+      <c r="N209" t="n">
+        <v>1</v>
+      </c>
+      <c r="O209" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9061,6 +10319,12 @@
         <v>3</v>
       </c>
       <c r="M210" t="n">
+        <v>0</v>
+      </c>
+      <c r="N210" t="n">
+        <v>3</v>
+      </c>
+      <c r="O210" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9102,6 +10366,12 @@
         <v>11</v>
       </c>
       <c r="M211" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" t="n">
+        <v>4</v>
+      </c>
+      <c r="O211" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9143,6 +10413,12 @@
         <v>7</v>
       </c>
       <c r="M212" t="n">
+        <v>0</v>
+      </c>
+      <c r="N212" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9184,6 +10460,12 @@
         <v>6</v>
       </c>
       <c r="M213" t="n">
+        <v>0</v>
+      </c>
+      <c r="N213" t="n">
+        <v>5</v>
+      </c>
+      <c r="O213" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9225,6 +10507,12 @@
         <v>0</v>
       </c>
       <c r="M214" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9266,6 +10554,12 @@
         <v>2</v>
       </c>
       <c r="M215" t="n">
+        <v>0</v>
+      </c>
+      <c r="N215" t="n">
+        <v>3</v>
+      </c>
+      <c r="O215" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9307,6 +10601,12 @@
         <v>4</v>
       </c>
       <c r="M216" t="n">
+        <v>0</v>
+      </c>
+      <c r="N216" t="n">
+        <v>3</v>
+      </c>
+      <c r="O216" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9348,6 +10648,12 @@
         <v>0</v>
       </c>
       <c r="M217" t="n">
+        <v>0</v>
+      </c>
+      <c r="N217" t="n">
+        <v>2</v>
+      </c>
+      <c r="O217" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9389,6 +10695,12 @@
         <v>0</v>
       </c>
       <c r="M218" t="n">
+        <v>1</v>
+      </c>
+      <c r="N218" t="n">
+        <v>0</v>
+      </c>
+      <c r="O218" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9430,6 +10742,12 @@
         <v>2</v>
       </c>
       <c r="M219" t="n">
+        <v>0</v>
+      </c>
+      <c r="N219" t="n">
+        <v>1</v>
+      </c>
+      <c r="O219" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9471,6 +10789,12 @@
         <v>0</v>
       </c>
       <c r="M220" t="n">
+        <v>0</v>
+      </c>
+      <c r="N220" t="n">
+        <v>1</v>
+      </c>
+      <c r="O220" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9512,6 +10836,12 @@
         <v>3</v>
       </c>
       <c r="M221" t="n">
+        <v>0</v>
+      </c>
+      <c r="N221" t="n">
+        <v>6</v>
+      </c>
+      <c r="O221" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9553,6 +10883,12 @@
         <v>2</v>
       </c>
       <c r="M222" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" t="n">
+        <v>0</v>
+      </c>
+      <c r="O222" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9594,6 +10930,12 @@
         <v>3</v>
       </c>
       <c r="M223" t="n">
+        <v>0</v>
+      </c>
+      <c r="N223" t="n">
+        <v>2</v>
+      </c>
+      <c r="O223" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9635,6 +10977,12 @@
         <v>2</v>
       </c>
       <c r="M224" t="n">
+        <v>0</v>
+      </c>
+      <c r="N224" t="n">
+        <v>2</v>
+      </c>
+      <c r="O224" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9676,6 +11024,12 @@
         <v>0</v>
       </c>
       <c r="M225" t="n">
+        <v>0</v>
+      </c>
+      <c r="N225" t="n">
+        <v>2</v>
+      </c>
+      <c r="O225" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9717,6 +11071,12 @@
         <v>2</v>
       </c>
       <c r="M226" t="n">
+        <v>0</v>
+      </c>
+      <c r="N226" t="n">
+        <v>1</v>
+      </c>
+      <c r="O226" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9758,6 +11118,12 @@
         <v>2</v>
       </c>
       <c r="M227" t="n">
+        <v>0</v>
+      </c>
+      <c r="N227" t="n">
+        <v>1</v>
+      </c>
+      <c r="O227" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9799,6 +11165,12 @@
         <v>1</v>
       </c>
       <c r="M228" t="n">
+        <v>0</v>
+      </c>
+      <c r="N228" t="n">
+        <v>5</v>
+      </c>
+      <c r="O228" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9840,6 +11212,12 @@
         <v>5</v>
       </c>
       <c r="M229" t="n">
+        <v>0</v>
+      </c>
+      <c r="N229" t="n">
+        <v>6</v>
+      </c>
+      <c r="O229" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9881,6 +11259,12 @@
         <v>3</v>
       </c>
       <c r="M230" t="n">
+        <v>0</v>
+      </c>
+      <c r="N230" t="n">
+        <v>3</v>
+      </c>
+      <c r="O230" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9922,6 +11306,12 @@
         <v>1</v>
       </c>
       <c r="M231" t="n">
+        <v>0</v>
+      </c>
+      <c r="N231" t="n">
+        <v>5</v>
+      </c>
+      <c r="O231" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -9963,6 +11353,12 @@
         <v>3</v>
       </c>
       <c r="M232" t="n">
+        <v>0</v>
+      </c>
+      <c r="N232" t="n">
+        <v>1</v>
+      </c>
+      <c r="O232" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10004,6 +11400,12 @@
         <v>1</v>
       </c>
       <c r="M233" t="n">
+        <v>0</v>
+      </c>
+      <c r="N233" t="n">
+        <v>0</v>
+      </c>
+      <c r="O233" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10045,6 +11447,12 @@
         <v>5</v>
       </c>
       <c r="M234" t="n">
+        <v>0</v>
+      </c>
+      <c r="N234" t="n">
+        <v>4</v>
+      </c>
+      <c r="O234" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10086,6 +11494,12 @@
         <v>5</v>
       </c>
       <c r="M235" t="n">
+        <v>0</v>
+      </c>
+      <c r="N235" t="n">
+        <v>0</v>
+      </c>
+      <c r="O235" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10127,6 +11541,12 @@
         <v>0</v>
       </c>
       <c r="M236" t="n">
+        <v>0</v>
+      </c>
+      <c r="N236" t="n">
+        <v>4</v>
+      </c>
+      <c r="O236" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10168,6 +11588,12 @@
         <v>0</v>
       </c>
       <c r="M237" t="n">
+        <v>0</v>
+      </c>
+      <c r="N237" t="n">
+        <v>6</v>
+      </c>
+      <c r="O237" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10209,6 +11635,12 @@
         <v>3</v>
       </c>
       <c r="M238" t="n">
+        <v>0</v>
+      </c>
+      <c r="N238" t="n">
+        <v>0</v>
+      </c>
+      <c r="O238" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10250,6 +11682,12 @@
         <v>1</v>
       </c>
       <c r="M239" t="n">
+        <v>0</v>
+      </c>
+      <c r="N239" t="n">
+        <v>1</v>
+      </c>
+      <c r="O239" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10291,6 +11729,12 @@
         <v>6</v>
       </c>
       <c r="M240" t="n">
+        <v>0</v>
+      </c>
+      <c r="N240" t="n">
+        <v>6</v>
+      </c>
+      <c r="O240" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10332,6 +11776,12 @@
         <v>5</v>
       </c>
       <c r="M241" t="n">
+        <v>0</v>
+      </c>
+      <c r="N241" t="n">
+        <v>7</v>
+      </c>
+      <c r="O241" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10373,6 +11823,12 @@
         <v>12</v>
       </c>
       <c r="M242" t="n">
+        <v>1</v>
+      </c>
+      <c r="N242" t="n">
+        <v>11</v>
+      </c>
+      <c r="O242" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10414,6 +11870,12 @@
         <v>11</v>
       </c>
       <c r="M243" t="n">
+        <v>0</v>
+      </c>
+      <c r="N243" t="n">
+        <v>11</v>
+      </c>
+      <c r="O243" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10455,6 +11917,12 @@
         <v>0</v>
       </c>
       <c r="M244" t="n">
+        <v>0</v>
+      </c>
+      <c r="N244" t="n">
+        <v>0</v>
+      </c>
+      <c r="O244" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10496,6 +11964,12 @@
         <v>0</v>
       </c>
       <c r="M245" t="n">
+        <v>0</v>
+      </c>
+      <c r="N245" t="n">
+        <v>1</v>
+      </c>
+      <c r="O245" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10537,6 +12011,12 @@
         <v>1</v>
       </c>
       <c r="M246" t="n">
+        <v>0</v>
+      </c>
+      <c r="N246" t="n">
+        <v>5</v>
+      </c>
+      <c r="O246" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10578,6 +12058,12 @@
         <v>2</v>
       </c>
       <c r="M247" t="n">
+        <v>0</v>
+      </c>
+      <c r="N247" t="n">
+        <v>7</v>
+      </c>
+      <c r="O247" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10619,6 +12105,12 @@
         <v>2</v>
       </c>
       <c r="M248" t="n">
+        <v>0</v>
+      </c>
+      <c r="N248" t="n">
+        <v>0</v>
+      </c>
+      <c r="O248" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10660,6 +12152,12 @@
         <v>1</v>
       </c>
       <c r="M249" t="n">
+        <v>0</v>
+      </c>
+      <c r="N249" t="n">
+        <v>0</v>
+      </c>
+      <c r="O249" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10701,6 +12199,12 @@
         <v>1</v>
       </c>
       <c r="M250" t="n">
+        <v>0</v>
+      </c>
+      <c r="N250" t="n">
+        <v>1</v>
+      </c>
+      <c r="O250" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10742,6 +12246,12 @@
         <v>3</v>
       </c>
       <c r="M251" t="n">
+        <v>0</v>
+      </c>
+      <c r="N251" t="n">
+        <v>7</v>
+      </c>
+      <c r="O251" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10783,6 +12293,12 @@
         <v>7</v>
       </c>
       <c r="M252" t="n">
+        <v>1</v>
+      </c>
+      <c r="N252" t="n">
+        <v>2</v>
+      </c>
+      <c r="O252" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10824,6 +12340,12 @@
         <v>4</v>
       </c>
       <c r="M253" t="n">
+        <v>0</v>
+      </c>
+      <c r="N253" t="n">
+        <v>9</v>
+      </c>
+      <c r="O253" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10865,6 +12387,12 @@
         <v>11</v>
       </c>
       <c r="M254" t="n">
+        <v>0</v>
+      </c>
+      <c r="N254" t="n">
+        <v>9</v>
+      </c>
+      <c r="O254" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10906,6 +12434,12 @@
         <v>3</v>
       </c>
       <c r="M255" t="n">
+        <v>0</v>
+      </c>
+      <c r="N255" t="n">
+        <v>1</v>
+      </c>
+      <c r="O255" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10947,6 +12481,12 @@
         <v>1</v>
       </c>
       <c r="M256" t="n">
+        <v>0</v>
+      </c>
+      <c r="N256" t="n">
+        <v>0</v>
+      </c>
+      <c r="O256" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -10988,6 +12528,12 @@
         <v>4</v>
       </c>
       <c r="M257" t="n">
+        <v>0</v>
+      </c>
+      <c r="N257" t="n">
+        <v>0</v>
+      </c>
+      <c r="O257" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11029,6 +12575,12 @@
         <v>2</v>
       </c>
       <c r="M258" t="n">
+        <v>0</v>
+      </c>
+      <c r="N258" t="n">
+        <v>2</v>
+      </c>
+      <c r="O258" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11070,6 +12622,12 @@
         <v>1</v>
       </c>
       <c r="M259" t="n">
+        <v>0</v>
+      </c>
+      <c r="N259" t="n">
+        <v>0</v>
+      </c>
+      <c r="O259" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11111,6 +12669,12 @@
         <v>2</v>
       </c>
       <c r="M260" t="n">
+        <v>0</v>
+      </c>
+      <c r="N260" t="n">
+        <v>1</v>
+      </c>
+      <c r="O260" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11152,6 +12716,12 @@
         <v>4</v>
       </c>
       <c r="M261" t="n">
+        <v>0</v>
+      </c>
+      <c r="N261" t="n">
+        <v>6</v>
+      </c>
+      <c r="O261" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11193,6 +12763,12 @@
         <v>10</v>
       </c>
       <c r="M262" t="n">
+        <v>0</v>
+      </c>
+      <c r="N262" t="n">
+        <v>12</v>
+      </c>
+      <c r="O262" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11234,6 +12810,12 @@
         <v>6</v>
       </c>
       <c r="M263" t="n">
+        <v>0</v>
+      </c>
+      <c r="N263" t="n">
+        <v>13</v>
+      </c>
+      <c r="O263" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11275,6 +12857,12 @@
         <v>2</v>
       </c>
       <c r="M264" t="n">
+        <v>0</v>
+      </c>
+      <c r="N264" t="n">
+        <v>1</v>
+      </c>
+      <c r="O264" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11316,6 +12904,12 @@
         <v>2</v>
       </c>
       <c r="M265" t="n">
+        <v>0</v>
+      </c>
+      <c r="N265" t="n">
+        <v>1</v>
+      </c>
+      <c r="O265" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11357,6 +12951,12 @@
         <v>9</v>
       </c>
       <c r="M266" t="n">
+        <v>0</v>
+      </c>
+      <c r="N266" t="n">
+        <v>0</v>
+      </c>
+      <c r="O266" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11398,6 +12998,12 @@
         <v>3</v>
       </c>
       <c r="M267" t="n">
+        <v>0</v>
+      </c>
+      <c r="N267" t="n">
+        <v>0</v>
+      </c>
+      <c r="O267" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11439,6 +13045,12 @@
         <v>3</v>
       </c>
       <c r="M268" t="n">
+        <v>0</v>
+      </c>
+      <c r="N268" t="n">
+        <v>0</v>
+      </c>
+      <c r="O268" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11480,6 +13092,12 @@
         <v>3</v>
       </c>
       <c r="M269" t="n">
+        <v>0</v>
+      </c>
+      <c r="N269" t="n">
+        <v>0</v>
+      </c>
+      <c r="O269" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11521,6 +13139,12 @@
         <v>0</v>
       </c>
       <c r="M270" t="n">
+        <v>0</v>
+      </c>
+      <c r="N270" t="n">
+        <v>0</v>
+      </c>
+      <c r="O270" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11562,6 +13186,12 @@
         <v>9</v>
       </c>
       <c r="M271" t="n">
+        <v>0</v>
+      </c>
+      <c r="N271" t="n">
+        <v>3</v>
+      </c>
+      <c r="O271" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11603,6 +13233,12 @@
         <v>7</v>
       </c>
       <c r="M272" t="n">
+        <v>0</v>
+      </c>
+      <c r="N272" t="n">
+        <v>2</v>
+      </c>
+      <c r="O272" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11644,6 +13280,12 @@
         <v>0</v>
       </c>
       <c r="M273" t="n">
+        <v>0</v>
+      </c>
+      <c r="N273" t="n">
+        <v>0</v>
+      </c>
+      <c r="O273" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11685,6 +13327,12 @@
         <v>0</v>
       </c>
       <c r="M274" t="n">
+        <v>0</v>
+      </c>
+      <c r="N274" t="n">
+        <v>0</v>
+      </c>
+      <c r="O274" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11726,6 +13374,12 @@
         <v>8</v>
       </c>
       <c r="M275" t="n">
+        <v>0</v>
+      </c>
+      <c r="N275" t="n">
+        <v>9</v>
+      </c>
+      <c r="O275" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11767,6 +13421,12 @@
         <v>5</v>
       </c>
       <c r="M276" t="n">
+        <v>0</v>
+      </c>
+      <c r="N276" t="n">
+        <v>1</v>
+      </c>
+      <c r="O276" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11808,6 +13468,12 @@
         <v>1</v>
       </c>
       <c r="M277" t="n">
+        <v>0</v>
+      </c>
+      <c r="N277" t="n">
+        <v>0</v>
+      </c>
+      <c r="O277" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11849,6 +13515,12 @@
         <v>3</v>
       </c>
       <c r="M278" t="n">
+        <v>0</v>
+      </c>
+      <c r="N278" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11890,6 +13562,12 @@
         <v>1</v>
       </c>
       <c r="M279" t="n">
+        <v>0</v>
+      </c>
+      <c r="N279" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11931,6 +13609,12 @@
         <v>0</v>
       </c>
       <c r="M280" t="n">
+        <v>0</v>
+      </c>
+      <c r="N280" t="n">
+        <v>0</v>
+      </c>
+      <c r="O280" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -11972,6 +13656,12 @@
         <v>0</v>
       </c>
       <c r="M281" t="n">
+        <v>0</v>
+      </c>
+      <c r="N281" t="n">
+        <v>0</v>
+      </c>
+      <c r="O281" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12013,6 +13703,12 @@
         <v>0</v>
       </c>
       <c r="M282" t="n">
+        <v>0</v>
+      </c>
+      <c r="N282" t="n">
+        <v>0</v>
+      </c>
+      <c r="O282" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12054,6 +13750,12 @@
         <v>0</v>
       </c>
       <c r="M283" t="n">
+        <v>0</v>
+      </c>
+      <c r="N283" t="n">
+        <v>3</v>
+      </c>
+      <c r="O283" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12095,6 +13797,12 @@
         <v>1</v>
       </c>
       <c r="M284" t="n">
+        <v>0</v>
+      </c>
+      <c r="N284" t="n">
+        <v>3</v>
+      </c>
+      <c r="O284" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12136,6 +13844,12 @@
         <v>2</v>
       </c>
       <c r="M285" t="n">
+        <v>0</v>
+      </c>
+      <c r="N285" t="n">
+        <v>0</v>
+      </c>
+      <c r="O285" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12177,6 +13891,12 @@
         <v>0</v>
       </c>
       <c r="M286" t="n">
+        <v>0</v>
+      </c>
+      <c r="N286" t="n">
+        <v>4</v>
+      </c>
+      <c r="O286" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12218,6 +13938,12 @@
         <v>2</v>
       </c>
       <c r="M287" t="n">
+        <v>0</v>
+      </c>
+      <c r="N287" t="n">
+        <v>6</v>
+      </c>
+      <c r="O287" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12259,6 +13985,12 @@
         <v>0</v>
       </c>
       <c r="M288" t="n">
+        <v>0</v>
+      </c>
+      <c r="N288" t="n">
+        <v>2</v>
+      </c>
+      <c r="O288" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12300,6 +14032,12 @@
         <v>1</v>
       </c>
       <c r="M289" t="n">
+        <v>0</v>
+      </c>
+      <c r="N289" t="n">
+        <v>0</v>
+      </c>
+      <c r="O289" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12341,6 +14079,12 @@
         <v>0</v>
       </c>
       <c r="M290" t="n">
+        <v>0</v>
+      </c>
+      <c r="N290" t="n">
+        <v>0</v>
+      </c>
+      <c r="O290" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12382,6 +14126,12 @@
         <v>1</v>
       </c>
       <c r="M291" t="n">
+        <v>0</v>
+      </c>
+      <c r="N291" t="n">
+        <v>0</v>
+      </c>
+      <c r="O291" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12423,6 +14173,12 @@
         <v>0</v>
       </c>
       <c r="M292" t="n">
+        <v>0</v>
+      </c>
+      <c r="N292" t="n">
+        <v>4</v>
+      </c>
+      <c r="O292" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12464,6 +14220,12 @@
         <v>4</v>
       </c>
       <c r="M293" t="n">
+        <v>0</v>
+      </c>
+      <c r="N293" t="n">
+        <v>1</v>
+      </c>
+      <c r="O293" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12505,6 +14267,12 @@
         <v>8</v>
       </c>
       <c r="M294" t="n">
+        <v>0</v>
+      </c>
+      <c r="N294" t="n">
+        <v>0</v>
+      </c>
+      <c r="O294" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12546,6 +14314,12 @@
         <v>13</v>
       </c>
       <c r="M295" t="n">
+        <v>0</v>
+      </c>
+      <c r="N295" t="n">
+        <v>9</v>
+      </c>
+      <c r="O295" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12587,6 +14361,12 @@
         <v>2</v>
       </c>
       <c r="M296" t="n">
+        <v>0</v>
+      </c>
+      <c r="N296" t="n">
+        <v>3</v>
+      </c>
+      <c r="O296" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12628,6 +14408,12 @@
         <v>3</v>
       </c>
       <c r="M297" t="n">
+        <v>0</v>
+      </c>
+      <c r="N297" t="n">
+        <v>7</v>
+      </c>
+      <c r="O297" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12669,6 +14455,12 @@
         <v>1</v>
       </c>
       <c r="M298" t="n">
+        <v>0</v>
+      </c>
+      <c r="N298" t="n">
+        <v>0</v>
+      </c>
+      <c r="O298" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12710,6 +14502,12 @@
         <v>4</v>
       </c>
       <c r="M299" t="n">
+        <v>0</v>
+      </c>
+      <c r="N299" t="n">
+        <v>2</v>
+      </c>
+      <c r="O299" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12751,6 +14549,12 @@
         <v>0</v>
       </c>
       <c r="M300" t="n">
+        <v>0</v>
+      </c>
+      <c r="N300" t="n">
+        <v>0</v>
+      </c>
+      <c r="O300" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12792,6 +14596,12 @@
         <v>5</v>
       </c>
       <c r="M301" t="n">
+        <v>0</v>
+      </c>
+      <c r="N301" t="n">
+        <v>2</v>
+      </c>
+      <c r="O301" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12833,6 +14643,12 @@
         <v>0</v>
       </c>
       <c r="M302" t="n">
+        <v>0</v>
+      </c>
+      <c r="N302" t="n">
+        <v>1</v>
+      </c>
+      <c r="O302" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12874,6 +14690,12 @@
         <v>1</v>
       </c>
       <c r="M303" t="n">
+        <v>0</v>
+      </c>
+      <c r="N303" t="n">
+        <v>4</v>
+      </c>
+      <c r="O303" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12915,6 +14737,12 @@
         <v>2</v>
       </c>
       <c r="M304" t="n">
+        <v>0</v>
+      </c>
+      <c r="N304" t="n">
+        <v>2</v>
+      </c>
+      <c r="O304" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12956,6 +14784,12 @@
         <v>2</v>
       </c>
       <c r="M305" t="n">
+        <v>0</v>
+      </c>
+      <c r="N305" t="n">
+        <v>1</v>
+      </c>
+      <c r="O305" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -12997,6 +14831,12 @@
         <v>0</v>
       </c>
       <c r="M306" t="n">
+        <v>0</v>
+      </c>
+      <c r="N306" t="n">
+        <v>3</v>
+      </c>
+      <c r="O306" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13038,6 +14878,12 @@
         <v>2</v>
       </c>
       <c r="M307" t="n">
+        <v>0</v>
+      </c>
+      <c r="N307" t="n">
+        <v>0</v>
+      </c>
+      <c r="O307" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13079,6 +14925,12 @@
         <v>2</v>
       </c>
       <c r="M308" t="n">
+        <v>0</v>
+      </c>
+      <c r="N308" t="n">
+        <v>1</v>
+      </c>
+      <c r="O308" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13120,6 +14972,12 @@
         <v>2</v>
       </c>
       <c r="M309" t="n">
+        <v>0</v>
+      </c>
+      <c r="N309" t="n">
+        <v>3</v>
+      </c>
+      <c r="O309" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13161,6 +15019,12 @@
         <v>7</v>
       </c>
       <c r="M310" t="n">
+        <v>0</v>
+      </c>
+      <c r="N310" t="n">
+        <v>5</v>
+      </c>
+      <c r="O310" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13202,6 +15066,12 @@
         <v>4</v>
       </c>
       <c r="M311" t="n">
+        <v>0</v>
+      </c>
+      <c r="N311" t="n">
+        <v>1</v>
+      </c>
+      <c r="O311" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13243,6 +15113,12 @@
         <v>2</v>
       </c>
       <c r="M312" t="n">
+        <v>0</v>
+      </c>
+      <c r="N312" t="n">
+        <v>1</v>
+      </c>
+      <c r="O312" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13284,6 +15160,12 @@
         <v>0</v>
       </c>
       <c r="M313" t="n">
+        <v>0</v>
+      </c>
+      <c r="N313" t="n">
+        <v>0</v>
+      </c>
+      <c r="O313" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13325,6 +15207,12 @@
         <v>0</v>
       </c>
       <c r="M314" t="n">
+        <v>0</v>
+      </c>
+      <c r="N314" t="n">
+        <v>0</v>
+      </c>
+      <c r="O314" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13366,6 +15254,12 @@
         <v>7</v>
       </c>
       <c r="M315" t="n">
+        <v>0</v>
+      </c>
+      <c r="N315" t="n">
+        <v>8</v>
+      </c>
+      <c r="O315" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13407,6 +15301,12 @@
         <v>2</v>
       </c>
       <c r="M316" t="n">
+        <v>0</v>
+      </c>
+      <c r="N316" t="n">
+        <v>6</v>
+      </c>
+      <c r="O316" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13448,6 +15348,12 @@
         <v>5</v>
       </c>
       <c r="M317" t="n">
+        <v>0</v>
+      </c>
+      <c r="N317" t="n">
+        <v>3</v>
+      </c>
+      <c r="O317" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13489,6 +15395,12 @@
         <v>7</v>
       </c>
       <c r="M318" t="n">
+        <v>0</v>
+      </c>
+      <c r="N318" t="n">
+        <v>1</v>
+      </c>
+      <c r="O318" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13530,6 +15442,12 @@
         <v>4</v>
       </c>
       <c r="M319" t="n">
+        <v>0</v>
+      </c>
+      <c r="N319" t="n">
+        <v>6</v>
+      </c>
+      <c r="O319" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13571,6 +15489,12 @@
         <v>19</v>
       </c>
       <c r="M320" t="n">
+        <v>0</v>
+      </c>
+      <c r="N320" t="n">
+        <v>5</v>
+      </c>
+      <c r="O320" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13612,6 +15536,12 @@
         <v>8</v>
       </c>
       <c r="M321" t="n">
+        <v>0</v>
+      </c>
+      <c r="N321" t="n">
+        <v>2</v>
+      </c>
+      <c r="O321" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13653,6 +15583,12 @@
         <v>5</v>
       </c>
       <c r="M322" t="n">
+        <v>0</v>
+      </c>
+      <c r="N322" t="n">
+        <v>7</v>
+      </c>
+      <c r="O322" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13694,6 +15630,12 @@
         <v>1</v>
       </c>
       <c r="M323" t="n">
+        <v>0</v>
+      </c>
+      <c r="N323" t="n">
+        <v>5</v>
+      </c>
+      <c r="O323" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13735,6 +15677,12 @@
         <v>0</v>
       </c>
       <c r="M324" t="n">
+        <v>0</v>
+      </c>
+      <c r="N324" t="n">
+        <v>4</v>
+      </c>
+      <c r="O324" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13776,6 +15724,12 @@
         <v>1</v>
       </c>
       <c r="M325" t="n">
+        <v>0</v>
+      </c>
+      <c r="N325" t="n">
+        <v>0</v>
+      </c>
+      <c r="O325" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13817,6 +15771,12 @@
         <v>4</v>
       </c>
       <c r="M326" t="n">
+        <v>0</v>
+      </c>
+      <c r="N326" t="n">
+        <v>7</v>
+      </c>
+      <c r="O326" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13858,6 +15818,12 @@
         <v>5</v>
       </c>
       <c r="M327" t="n">
+        <v>0</v>
+      </c>
+      <c r="N327" t="n">
+        <v>10</v>
+      </c>
+      <c r="O327" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13899,6 +15865,12 @@
         <v>0</v>
       </c>
       <c r="M328" t="n">
+        <v>0</v>
+      </c>
+      <c r="N328" t="n">
+        <v>1</v>
+      </c>
+      <c r="O328" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13940,6 +15912,12 @@
         <v>1</v>
       </c>
       <c r="M329" t="n">
+        <v>0</v>
+      </c>
+      <c r="N329" t="n">
+        <v>0</v>
+      </c>
+      <c r="O329" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -13981,6 +15959,12 @@
         <v>1</v>
       </c>
       <c r="M330" t="n">
+        <v>0</v>
+      </c>
+      <c r="N330" t="n">
+        <v>2</v>
+      </c>
+      <c r="O330" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14022,6 +16006,12 @@
         <v>5</v>
       </c>
       <c r="M331" t="n">
+        <v>0</v>
+      </c>
+      <c r="N331" t="n">
+        <v>0</v>
+      </c>
+      <c r="O331" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14063,6 +16053,12 @@
         <v>1</v>
       </c>
       <c r="M332" t="n">
+        <v>0</v>
+      </c>
+      <c r="N332" t="n">
+        <v>5</v>
+      </c>
+      <c r="O332" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14104,6 +16100,12 @@
         <v>1</v>
       </c>
       <c r="M333" t="n">
+        <v>0</v>
+      </c>
+      <c r="N333" t="n">
+        <v>6</v>
+      </c>
+      <c r="O333" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14145,6 +16147,12 @@
         <v>2</v>
       </c>
       <c r="M334" t="n">
+        <v>0</v>
+      </c>
+      <c r="N334" t="n">
+        <v>0</v>
+      </c>
+      <c r="O334" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14186,6 +16194,12 @@
         <v>0</v>
       </c>
       <c r="M335" t="n">
+        <v>0</v>
+      </c>
+      <c r="N335" t="n">
+        <v>2</v>
+      </c>
+      <c r="O335" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14227,6 +16241,12 @@
         <v>0</v>
       </c>
       <c r="M336" t="n">
+        <v>0</v>
+      </c>
+      <c r="N336" t="n">
+        <v>1</v>
+      </c>
+      <c r="O336" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14268,6 +16288,12 @@
         <v>4</v>
       </c>
       <c r="M337" t="n">
+        <v>0</v>
+      </c>
+      <c r="N337" t="n">
+        <v>1</v>
+      </c>
+      <c r="O337" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14309,6 +16335,12 @@
         <v>4</v>
       </c>
       <c r="M338" t="n">
+        <v>0</v>
+      </c>
+      <c r="N338" t="n">
+        <v>1</v>
+      </c>
+      <c r="O338" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14350,6 +16382,12 @@
         <v>2</v>
       </c>
       <c r="M339" t="n">
+        <v>0</v>
+      </c>
+      <c r="N339" t="n">
+        <v>3</v>
+      </c>
+      <c r="O339" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14391,6 +16429,12 @@
         <v>5</v>
       </c>
       <c r="M340" t="n">
+        <v>0</v>
+      </c>
+      <c r="N340" t="n">
+        <v>1</v>
+      </c>
+      <c r="O340" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14432,6 +16476,12 @@
         <v>4</v>
       </c>
       <c r="M341" t="n">
+        <v>0</v>
+      </c>
+      <c r="N341" t="n">
+        <v>5</v>
+      </c>
+      <c r="O341" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14473,6 +16523,12 @@
         <v>0</v>
       </c>
       <c r="M342" t="n">
+        <v>0</v>
+      </c>
+      <c r="N342" t="n">
+        <v>0</v>
+      </c>
+      <c r="O342" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14514,6 +16570,12 @@
         <v>0</v>
       </c>
       <c r="M343" t="n">
+        <v>0</v>
+      </c>
+      <c r="N343" t="n">
+        <v>0</v>
+      </c>
+      <c r="O343" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14555,6 +16617,12 @@
         <v>5</v>
       </c>
       <c r="M344" t="n">
+        <v>0</v>
+      </c>
+      <c r="N344" t="n">
+        <v>0</v>
+      </c>
+      <c r="O344" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14596,6 +16664,12 @@
         <v>1</v>
       </c>
       <c r="M345" t="n">
+        <v>0</v>
+      </c>
+      <c r="N345" t="n">
+        <v>1</v>
+      </c>
+      <c r="O345" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14637,6 +16711,12 @@
         <v>3</v>
       </c>
       <c r="M346" t="n">
+        <v>0</v>
+      </c>
+      <c r="N346" t="n">
+        <v>0</v>
+      </c>
+      <c r="O346" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14678,6 +16758,12 @@
         <v>1</v>
       </c>
       <c r="M347" t="n">
+        <v>1</v>
+      </c>
+      <c r="N347" t="n">
+        <v>2</v>
+      </c>
+      <c r="O347" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14719,6 +16805,12 @@
         <v>1</v>
       </c>
       <c r="M348" t="n">
+        <v>0</v>
+      </c>
+      <c r="N348" t="n">
+        <v>7</v>
+      </c>
+      <c r="O348" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14760,6 +16852,12 @@
         <v>3</v>
       </c>
       <c r="M349" t="n">
+        <v>0</v>
+      </c>
+      <c r="N349" t="n">
+        <v>7</v>
+      </c>
+      <c r="O349" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14801,6 +16899,12 @@
         <v>2</v>
       </c>
       <c r="M350" t="n">
+        <v>0</v>
+      </c>
+      <c r="N350" t="n">
+        <v>0</v>
+      </c>
+      <c r="O350" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14842,6 +16946,12 @@
         <v>2</v>
       </c>
       <c r="M351" t="n">
+        <v>0</v>
+      </c>
+      <c r="N351" t="n">
+        <v>0</v>
+      </c>
+      <c r="O351" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14883,6 +16993,12 @@
         <v>0</v>
       </c>
       <c r="M352" t="n">
+        <v>0</v>
+      </c>
+      <c r="N352" t="n">
+        <v>5</v>
+      </c>
+      <c r="O352" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14924,6 +17040,12 @@
         <v>3</v>
       </c>
       <c r="M353" t="n">
+        <v>0</v>
+      </c>
+      <c r="N353" t="n">
+        <v>10</v>
+      </c>
+      <c r="O353" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -14965,6 +17087,12 @@
         <v>5</v>
       </c>
       <c r="M354" t="n">
+        <v>0</v>
+      </c>
+      <c r="N354" t="n">
+        <v>3</v>
+      </c>
+      <c r="O354" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15006,6 +17134,12 @@
         <v>0</v>
       </c>
       <c r="M355" t="n">
+        <v>0</v>
+      </c>
+      <c r="N355" t="n">
+        <v>0</v>
+      </c>
+      <c r="O355" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15047,6 +17181,12 @@
         <v>0</v>
       </c>
       <c r="M356" t="n">
+        <v>0</v>
+      </c>
+      <c r="N356" t="n">
+        <v>1</v>
+      </c>
+      <c r="O356" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15088,6 +17228,12 @@
         <v>0</v>
       </c>
       <c r="M357" t="n">
+        <v>0</v>
+      </c>
+      <c r="N357" t="n">
+        <v>0</v>
+      </c>
+      <c r="O357" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15129,6 +17275,12 @@
         <v>3</v>
       </c>
       <c r="M358" t="n">
+        <v>0</v>
+      </c>
+      <c r="N358" t="n">
+        <v>0</v>
+      </c>
+      <c r="O358" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15170,6 +17322,12 @@
         <v>5</v>
       </c>
       <c r="M359" t="n">
+        <v>0</v>
+      </c>
+      <c r="N359" t="n">
+        <v>7</v>
+      </c>
+      <c r="O359" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15211,6 +17369,12 @@
         <v>2</v>
       </c>
       <c r="M360" t="n">
+        <v>0</v>
+      </c>
+      <c r="N360" t="n">
+        <v>13</v>
+      </c>
+      <c r="O360" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15252,6 +17416,12 @@
         <v>1</v>
       </c>
       <c r="M361" t="n">
+        <v>0</v>
+      </c>
+      <c r="N361" t="n">
+        <v>2</v>
+      </c>
+      <c r="O361" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15293,6 +17463,12 @@
         <v>2</v>
       </c>
       <c r="M362" t="n">
+        <v>0</v>
+      </c>
+      <c r="N362" t="n">
+        <v>2</v>
+      </c>
+      <c r="O362" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15334,6 +17510,12 @@
         <v>3</v>
       </c>
       <c r="M363" t="n">
+        <v>0</v>
+      </c>
+      <c r="N363" t="n">
+        <v>5</v>
+      </c>
+      <c r="O363" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15375,6 +17557,12 @@
         <v>9</v>
       </c>
       <c r="M364" t="n">
+        <v>0</v>
+      </c>
+      <c r="N364" t="n">
+        <v>12</v>
+      </c>
+      <c r="O364" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15416,6 +17604,12 @@
         <v>4</v>
       </c>
       <c r="M365" t="n">
+        <v>0</v>
+      </c>
+      <c r="N365" t="n">
+        <v>7</v>
+      </c>
+      <c r="O365" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15457,6 +17651,12 @@
         <v>3</v>
       </c>
       <c r="M366" t="n">
+        <v>0</v>
+      </c>
+      <c r="N366" t="n">
+        <v>1</v>
+      </c>
+      <c r="O366" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15498,6 +17698,12 @@
         <v>0</v>
       </c>
       <c r="M367" t="n">
+        <v>0</v>
+      </c>
+      <c r="N367" t="n">
+        <v>2</v>
+      </c>
+      <c r="O367" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15539,6 +17745,12 @@
         <v>1</v>
       </c>
       <c r="M368" t="n">
+        <v>0</v>
+      </c>
+      <c r="N368" t="n">
+        <v>0</v>
+      </c>
+      <c r="O368" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15580,6 +17792,12 @@
         <v>1</v>
       </c>
       <c r="M369" t="n">
+        <v>0</v>
+      </c>
+      <c r="N369" t="n">
+        <v>1</v>
+      </c>
+      <c r="O369" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15621,6 +17839,12 @@
         <v>3</v>
       </c>
       <c r="M370" t="n">
+        <v>0</v>
+      </c>
+      <c r="N370" t="n">
+        <v>1</v>
+      </c>
+      <c r="O370" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15662,6 +17886,12 @@
         <v>1</v>
       </c>
       <c r="M371" t="n">
+        <v>0</v>
+      </c>
+      <c r="N371" t="n">
+        <v>3</v>
+      </c>
+      <c r="O371" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15703,6 +17933,12 @@
         <v>1</v>
       </c>
       <c r="M372" t="n">
+        <v>0</v>
+      </c>
+      <c r="N372" t="n">
+        <v>5</v>
+      </c>
+      <c r="O372" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15744,6 +17980,12 @@
         <v>3</v>
       </c>
       <c r="M373" t="n">
+        <v>0</v>
+      </c>
+      <c r="N373" t="n">
+        <v>1</v>
+      </c>
+      <c r="O373" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15785,6 +18027,12 @@
         <v>10</v>
       </c>
       <c r="M374" t="n">
+        <v>0</v>
+      </c>
+      <c r="N374" t="n">
+        <v>0</v>
+      </c>
+      <c r="O374" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15826,6 +18074,12 @@
         <v>0</v>
       </c>
       <c r="M375" t="n">
+        <v>0</v>
+      </c>
+      <c r="N375" t="n">
+        <v>1</v>
+      </c>
+      <c r="O375" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15867,6 +18121,12 @@
         <v>4</v>
       </c>
       <c r="M376" t="n">
+        <v>0</v>
+      </c>
+      <c r="N376" t="n">
+        <v>0</v>
+      </c>
+      <c r="O376" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15908,6 +18168,12 @@
         <v>2</v>
       </c>
       <c r="M377" t="n">
+        <v>0</v>
+      </c>
+      <c r="N377" t="n">
+        <v>2</v>
+      </c>
+      <c r="O377" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15949,6 +18215,12 @@
         <v>3</v>
       </c>
       <c r="M378" t="n">
+        <v>0</v>
+      </c>
+      <c r="N378" t="n">
+        <v>4</v>
+      </c>
+      <c r="O378" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -15990,6 +18262,12 @@
         <v>6</v>
       </c>
       <c r="M379" t="n">
+        <v>0</v>
+      </c>
+      <c r="N379" t="n">
+        <v>2</v>
+      </c>
+      <c r="O379" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16031,6 +18309,12 @@
         <v>2</v>
       </c>
       <c r="M380" t="n">
+        <v>0</v>
+      </c>
+      <c r="N380" t="n">
+        <v>0</v>
+      </c>
+      <c r="O380" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16072,6 +18356,12 @@
         <v>6</v>
       </c>
       <c r="M381" t="n">
+        <v>1</v>
+      </c>
+      <c r="N381" t="n">
+        <v>5</v>
+      </c>
+      <c r="O381" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16113,6 +18403,12 @@
         <v>6</v>
       </c>
       <c r="M382" t="n">
+        <v>0</v>
+      </c>
+      <c r="N382" t="n">
+        <v>5</v>
+      </c>
+      <c r="O382" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16154,6 +18450,12 @@
         <v>4</v>
       </c>
       <c r="M383" t="n">
+        <v>0</v>
+      </c>
+      <c r="N383" t="n">
+        <v>0</v>
+      </c>
+      <c r="O383" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16195,6 +18497,12 @@
         <v>1</v>
       </c>
       <c r="M384" t="n">
+        <v>0</v>
+      </c>
+      <c r="N384" t="n">
+        <v>0</v>
+      </c>
+      <c r="O384" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16236,6 +18544,12 @@
         <v>0</v>
       </c>
       <c r="M385" t="n">
+        <v>0</v>
+      </c>
+      <c r="N385" t="n">
+        <v>0</v>
+      </c>
+      <c r="O385" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16277,6 +18591,12 @@
         <v>2</v>
       </c>
       <c r="M386" t="n">
+        <v>0</v>
+      </c>
+      <c r="N386" t="n">
+        <v>1</v>
+      </c>
+      <c r="O386" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16318,6 +18638,12 @@
         <v>4</v>
       </c>
       <c r="M387" t="n">
+        <v>0</v>
+      </c>
+      <c r="N387" t="n">
+        <v>3</v>
+      </c>
+      <c r="O387" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16359,6 +18685,12 @@
         <v>0</v>
       </c>
       <c r="M388" t="n">
+        <v>1</v>
+      </c>
+      <c r="N388" t="n">
+        <v>6</v>
+      </c>
+      <c r="O388" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16400,6 +18732,12 @@
         <v>3</v>
       </c>
       <c r="M389" t="n">
+        <v>0</v>
+      </c>
+      <c r="N389" t="n">
+        <v>7</v>
+      </c>
+      <c r="O389" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16441,6 +18779,12 @@
         <v>4</v>
       </c>
       <c r="M390" t="n">
+        <v>0</v>
+      </c>
+      <c r="N390" t="n">
+        <v>2</v>
+      </c>
+      <c r="O390" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16482,6 +18826,12 @@
         <v>1</v>
       </c>
       <c r="M391" t="n">
+        <v>0</v>
+      </c>
+      <c r="N391" t="n">
+        <v>4</v>
+      </c>
+      <c r="O391" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16523,6 +18873,12 @@
         <v>11</v>
       </c>
       <c r="M392" t="n">
+        <v>0</v>
+      </c>
+      <c r="N392" t="n">
+        <v>5</v>
+      </c>
+      <c r="O392" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16564,6 +18920,12 @@
         <v>8</v>
       </c>
       <c r="M393" t="n">
+        <v>0</v>
+      </c>
+      <c r="N393" t="n">
+        <v>6</v>
+      </c>
+      <c r="O393" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16605,6 +18967,12 @@
         <v>0</v>
       </c>
       <c r="M394" t="n">
+        <v>0</v>
+      </c>
+      <c r="N394" t="n">
+        <v>0</v>
+      </c>
+      <c r="O394" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16646,6 +19014,12 @@
         <v>2</v>
       </c>
       <c r="M395" t="n">
+        <v>0</v>
+      </c>
+      <c r="N395" t="n">
+        <v>4</v>
+      </c>
+      <c r="O395" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16687,6 +19061,12 @@
         <v>4</v>
       </c>
       <c r="M396" t="n">
+        <v>0</v>
+      </c>
+      <c r="N396" t="n">
+        <v>1</v>
+      </c>
+      <c r="O396" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16728,6 +19108,12 @@
         <v>17</v>
       </c>
       <c r="M397" t="n">
+        <v>0</v>
+      </c>
+      <c r="N397" t="n">
+        <v>2</v>
+      </c>
+      <c r="O397" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16769,6 +19155,12 @@
         <v>16</v>
       </c>
       <c r="M398" t="n">
+        <v>0</v>
+      </c>
+      <c r="N398" t="n">
+        <v>3</v>
+      </c>
+      <c r="O398" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16810,6 +19202,12 @@
         <v>3</v>
       </c>
       <c r="M399" t="n">
+        <v>0</v>
+      </c>
+      <c r="N399" t="n">
+        <v>1</v>
+      </c>
+      <c r="O399" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16851,6 +19249,12 @@
         <v>2</v>
       </c>
       <c r="M400" t="n">
+        <v>0</v>
+      </c>
+      <c r="N400" t="n">
+        <v>3</v>
+      </c>
+      <c r="O400" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16892,6 +19296,12 @@
         <v>6</v>
       </c>
       <c r="M401" t="n">
+        <v>0</v>
+      </c>
+      <c r="N401" t="n">
+        <v>8</v>
+      </c>
+      <c r="O401" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16933,6 +19343,12 @@
         <v>21</v>
       </c>
       <c r="M402" t="n">
+        <v>0</v>
+      </c>
+      <c r="N402" t="n">
+        <v>7</v>
+      </c>
+      <c r="O402" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -16974,6 +19390,12 @@
         <v>0</v>
       </c>
       <c r="M403" t="n">
+        <v>0</v>
+      </c>
+      <c r="N403" t="n">
+        <v>1</v>
+      </c>
+      <c r="O403" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -17015,6 +19437,12 @@
         <v>2</v>
       </c>
       <c r="M404" t="n">
+        <v>0</v>
+      </c>
+      <c r="N404" t="n">
+        <v>6</v>
+      </c>
+      <c r="O404" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -17056,6 +19484,12 @@
         <v>3</v>
       </c>
       <c r="M405" t="n">
+        <v>0</v>
+      </c>
+      <c r="N405" t="n">
+        <v>1</v>
+      </c>
+      <c r="O405" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -17097,6 +19531,12 @@
         <v>0</v>
       </c>
       <c r="M406" t="n">
+        <v>0</v>
+      </c>
+      <c r="N406" t="n">
+        <v>0</v>
+      </c>
+      <c r="O406" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -17138,6 +19578,12 @@
         <v>0</v>
       </c>
       <c r="M407" t="n">
+        <v>0</v>
+      </c>
+      <c r="N407" t="n">
+        <v>1</v>
+      </c>
+      <c r="O407" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -17179,6 +19625,12 @@
         <v>3</v>
       </c>
       <c r="M408" t="n">
+        <v>0</v>
+      </c>
+      <c r="N408" t="n">
+        <v>1</v>
+      </c>
+      <c r="O408" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -17220,6 +19672,12 @@
         <v>7</v>
       </c>
       <c r="M409" t="n">
+        <v>1</v>
+      </c>
+      <c r="N409" t="n">
+        <v>11</v>
+      </c>
+      <c r="O409" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -17261,6 +19719,12 @@
         <v>6</v>
       </c>
       <c r="M410" t="n">
+        <v>0</v>
+      </c>
+      <c r="N410" t="n">
+        <v>2</v>
+      </c>
+      <c r="O410" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -17302,6 +19766,12 @@
         <v>9</v>
       </c>
       <c r="M411" t="n">
+        <v>0</v>
+      </c>
+      <c r="N411" t="n">
+        <v>17</v>
+      </c>
+      <c r="O411" t="n">
         <v>2011</v>
       </c>
     </row>

--- a/Excel Files IPEDS/Trimmed/c2011_trimmed_file.xlsx
+++ b/Excel Files IPEDS/Trimmed/c2011_trimmed_file.xlsx
@@ -14,99 +14,102 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
-    <t>UNITID</t>
+    <t>unitid</t>
   </si>
   <si>
-    <t>CIPCODE</t>
+    <t>cipcode</t>
   </si>
   <si>
-    <t>CTOTALT</t>
+    <t>ctotalt</t>
   </si>
   <si>
-    <t>AWLEVEL</t>
+    <t>awlevel</t>
   </si>
   <si>
-    <t>CTOTALM</t>
+    <t>ctotalm</t>
   </si>
   <si>
-    <t>CTOTALW</t>
+    <t>ctotalw</t>
   </si>
   <si>
-    <t>CUNKNT</t>
+    <t>cunknt</t>
   </si>
   <si>
-    <t>CBKAAT</t>
+    <t>cbkaat</t>
   </si>
   <si>
-    <t>CASIAT</t>
+    <t>casiat</t>
   </si>
   <si>
-    <t>CNHPIT</t>
+    <t>cnhpit</t>
   </si>
   <si>
-    <t>CHISPT</t>
+    <t>chispt</t>
   </si>
   <si>
-    <t>CWHITT</t>
+    <t>cwhitt</t>
   </si>
   <si>
-    <t>C2MORT</t>
+    <t>c2mort</t>
   </si>
   <si>
-    <t>CNRALT</t>
+    <t>cnralt</t>
   </si>
   <si>
-    <t>CBKAAM</t>
+    <t>cbkaam</t>
   </si>
   <si>
-    <t>CASIAM</t>
+    <t>casiam</t>
   </si>
   <si>
-    <t>CNHPIM</t>
+    <t>cnhpim</t>
   </si>
   <si>
-    <t>CHISPM</t>
+    <t>chispm</t>
   </si>
   <si>
-    <t>CWHITM</t>
+    <t>cwhitm</t>
   </si>
   <si>
-    <t>CUNKNM</t>
+    <t>cunknm</t>
   </si>
   <si>
-    <t>C2MORM</t>
+    <t>c2morm</t>
   </si>
   <si>
-    <t>CNRALM</t>
+    <t>cnralm</t>
   </si>
   <si>
-    <t>CBKAAW</t>
+    <t>cbkaaw</t>
   </si>
   <si>
-    <t>CASIAW</t>
+    <t>casiaw</t>
   </si>
   <si>
-    <t>CNHPIW</t>
+    <t>cnhpiw</t>
   </si>
   <si>
-    <t>CHISPW</t>
+    <t>chispw</t>
   </si>
   <si>
-    <t>CWHITW</t>
+    <t>cwhitw</t>
   </si>
   <si>
-    <t>CUNKNW</t>
+    <t>cunknw</t>
   </si>
   <si>
-    <t>C2MORW</t>
+    <t>c2morw</t>
   </si>
   <si>
-    <t>CNRALW</t>
+    <t>cnralw</t>
   </si>
   <si>
-    <t>Year</t>
+    <t>majornum</t>
+  </si>
+  <si>
+    <t>year</t>
   </si>
 </sst>
 </file>
@@ -464,10 +467,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE411"/>
+  <dimension ref="A1:AF411"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -561,8 +564,11 @@
       <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:31">
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
       <c r="A2">
         <v>100654</v>
       </c>
@@ -654,10 +660,13 @@
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF2">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32">
       <c r="A3">
         <v>100663</v>
       </c>
@@ -749,10 +758,13 @@
         <v>1</v>
       </c>
       <c r="AE3">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF3">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32">
       <c r="A4">
         <v>100663</v>
       </c>
@@ -844,10 +856,13 @@
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF4">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32">
       <c r="A5">
         <v>100706</v>
       </c>
@@ -939,10 +954,13 @@
         <v>1</v>
       </c>
       <c r="AE5">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF5">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32">
       <c r="A6">
         <v>100706</v>
       </c>
@@ -1034,10 +1052,13 @@
         <v>3</v>
       </c>
       <c r="AE6">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF6">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32">
       <c r="A7">
         <v>100751</v>
       </c>
@@ -1129,10 +1150,13 @@
         <v>0</v>
       </c>
       <c r="AE7">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF7">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32">
       <c r="A8">
         <v>100751</v>
       </c>
@@ -1224,10 +1248,13 @@
         <v>1</v>
       </c>
       <c r="AE8">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF8">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32">
       <c r="A9">
         <v>100858</v>
       </c>
@@ -1319,10 +1346,13 @@
         <v>1</v>
       </c>
       <c r="AE9">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF9">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32">
       <c r="A10">
         <v>100858</v>
       </c>
@@ -1414,10 +1444,13 @@
         <v>1</v>
       </c>
       <c r="AE10">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF10">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32">
       <c r="A11">
         <v>102614</v>
       </c>
@@ -1509,10 +1542,13 @@
         <v>0</v>
       </c>
       <c r="AE11">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF11">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32">
       <c r="A12">
         <v>102614</v>
       </c>
@@ -1604,10 +1640,13 @@
         <v>0</v>
       </c>
       <c r="AE12">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF12">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32">
       <c r="A13">
         <v>104151</v>
       </c>
@@ -1699,10 +1738,13 @@
         <v>3</v>
       </c>
       <c r="AE13">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF13">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32">
       <c r="A14">
         <v>104151</v>
       </c>
@@ -1794,10 +1836,13 @@
         <v>1</v>
       </c>
       <c r="AE14">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF14">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32">
       <c r="A15">
         <v>104179</v>
       </c>
@@ -1889,10 +1934,13 @@
         <v>0</v>
       </c>
       <c r="AE15">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF15">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32">
       <c r="A16">
         <v>104179</v>
       </c>
@@ -1984,10 +2032,13 @@
         <v>0</v>
       </c>
       <c r="AE16">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="17" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF16">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32">
       <c r="A17">
         <v>105330</v>
       </c>
@@ -2079,10 +2130,13 @@
         <v>0</v>
       </c>
       <c r="AE17">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="18" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF17">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32">
       <c r="A18">
         <v>106397</v>
       </c>
@@ -2174,10 +2228,13 @@
         <v>0</v>
       </c>
       <c r="AE18">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="19" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF18">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32">
       <c r="A19">
         <v>106397</v>
       </c>
@@ -2269,10 +2326,13 @@
         <v>1</v>
       </c>
       <c r="AE19">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="20" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF19">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32">
       <c r="A20">
         <v>110404</v>
       </c>
@@ -2364,10 +2424,13 @@
         <v>1</v>
       </c>
       <c r="AE20">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF20">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32">
       <c r="A21">
         <v>110404</v>
       </c>
@@ -2459,10 +2522,13 @@
         <v>2</v>
       </c>
       <c r="AE21">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF21">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32">
       <c r="A22">
         <v>110556</v>
       </c>
@@ -2554,10 +2620,13 @@
         <v>1</v>
       </c>
       <c r="AE22">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF22">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32">
       <c r="A23">
         <v>110565</v>
       </c>
@@ -2649,10 +2718,13 @@
         <v>0</v>
       </c>
       <c r="AE23">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF23">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32">
       <c r="A24">
         <v>110583</v>
       </c>
@@ -2744,10 +2816,13 @@
         <v>0</v>
       </c>
       <c r="AE24">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF24">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32">
       <c r="A25">
         <v>110592</v>
       </c>
@@ -2839,10 +2914,13 @@
         <v>0</v>
       </c>
       <c r="AE25">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="26" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF25">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32">
       <c r="A26">
         <v>110608</v>
       </c>
@@ -2934,10 +3012,13 @@
         <v>1</v>
       </c>
       <c r="AE26">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF26">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="27" spans="1:32">
       <c r="A27">
         <v>110635</v>
       </c>
@@ -3029,10 +3110,13 @@
         <v>0</v>
       </c>
       <c r="AE27">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF27">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32">
       <c r="A28">
         <v>110635</v>
       </c>
@@ -3124,10 +3208,13 @@
         <v>1</v>
       </c>
       <c r="AE28">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF28">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32">
       <c r="A29">
         <v>110644</v>
       </c>
@@ -3219,10 +3306,13 @@
         <v>0</v>
       </c>
       <c r="AE29">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="30" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF29">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="30" spans="1:32">
       <c r="A30">
         <v>110644</v>
       </c>
@@ -3314,10 +3404,13 @@
         <v>2</v>
       </c>
       <c r="AE30">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="31" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF30">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="31" spans="1:32">
       <c r="A31">
         <v>110644</v>
       </c>
@@ -3409,10 +3502,13 @@
         <v>0</v>
       </c>
       <c r="AE31">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="32" spans="1:31">
+        <v>2</v>
+      </c>
+      <c r="AF31">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="32" spans="1:32">
       <c r="A32">
         <v>110653</v>
       </c>
@@ -3504,10 +3600,13 @@
         <v>0</v>
       </c>
       <c r="AE32">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="33" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF32">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="33" spans="1:32">
       <c r="A33">
         <v>110653</v>
       </c>
@@ -3599,10 +3698,13 @@
         <v>0</v>
       </c>
       <c r="AE33">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="34" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF33">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="34" spans="1:32">
       <c r="A34">
         <v>110662</v>
       </c>
@@ -3694,10 +3796,13 @@
         <v>0</v>
       </c>
       <c r="AE34">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="35" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF34">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="35" spans="1:32">
       <c r="A35">
         <v>110662</v>
       </c>
@@ -3789,10 +3894,13 @@
         <v>0</v>
       </c>
       <c r="AE35">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="36" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF35">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="36" spans="1:32">
       <c r="A36">
         <v>110671</v>
       </c>
@@ -3884,10 +3992,13 @@
         <v>2</v>
       </c>
       <c r="AE36">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="37" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF36">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="37" spans="1:32">
       <c r="A37">
         <v>110671</v>
       </c>
@@ -3979,10 +4090,13 @@
         <v>1</v>
       </c>
       <c r="AE37">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="38" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF37">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="38" spans="1:32">
       <c r="A38">
         <v>110680</v>
       </c>
@@ -4074,10 +4188,13 @@
         <v>0</v>
       </c>
       <c r="AE38">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="39" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF38">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="39" spans="1:32">
       <c r="A39">
         <v>110680</v>
       </c>
@@ -4169,10 +4286,13 @@
         <v>0</v>
       </c>
       <c r="AE39">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="40" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF39">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="40" spans="1:32">
       <c r="A40">
         <v>110705</v>
       </c>
@@ -4264,10 +4384,13 @@
         <v>0</v>
       </c>
       <c r="AE40">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="41" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF40">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="41" spans="1:32">
       <c r="A41">
         <v>110705</v>
       </c>
@@ -4359,10 +4482,13 @@
         <v>2</v>
       </c>
       <c r="AE41">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="42" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF41">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="42" spans="1:32">
       <c r="A42">
         <v>110714</v>
       </c>
@@ -4454,10 +4580,13 @@
         <v>0</v>
       </c>
       <c r="AE42">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="43" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF42">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="43" spans="1:32">
       <c r="A43">
         <v>110714</v>
       </c>
@@ -4549,10 +4678,13 @@
         <v>0</v>
       </c>
       <c r="AE43">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="44" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF43">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="44" spans="1:32">
       <c r="A44">
         <v>122409</v>
       </c>
@@ -4644,10 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AE44">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="45" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF44">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="45" spans="1:32">
       <c r="A45">
         <v>122597</v>
       </c>
@@ -4739,10 +4874,13 @@
         <v>0</v>
       </c>
       <c r="AE45">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="46" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF45">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="46" spans="1:32">
       <c r="A46">
         <v>122755</v>
       </c>
@@ -4834,10 +4972,13 @@
         <v>0</v>
       </c>
       <c r="AE46">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="47" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF46">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="47" spans="1:32">
       <c r="A47">
         <v>123961</v>
       </c>
@@ -4929,10 +5070,13 @@
         <v>1</v>
       </c>
       <c r="AE47">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="48" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF47">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="48" spans="1:32">
       <c r="A48">
         <v>123961</v>
       </c>
@@ -5024,10 +5168,13 @@
         <v>0</v>
       </c>
       <c r="AE48">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="49" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF48">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="49" spans="1:32">
       <c r="A49">
         <v>126614</v>
       </c>
@@ -5119,10 +5266,13 @@
         <v>1</v>
       </c>
       <c r="AE49">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="50" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF49">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="50" spans="1:32">
       <c r="A50">
         <v>126614</v>
       </c>
@@ -5214,10 +5364,13 @@
         <v>0</v>
       </c>
       <c r="AE50">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="51" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF50">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="51" spans="1:32">
       <c r="A51">
         <v>126614</v>
       </c>
@@ -5309,10 +5462,13 @@
         <v>0</v>
       </c>
       <c r="AE51">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="52" spans="1:31">
+        <v>2</v>
+      </c>
+      <c r="AF51">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="52" spans="1:32">
       <c r="A52">
         <v>126614</v>
       </c>
@@ -5404,10 +5560,13 @@
         <v>0</v>
       </c>
       <c r="AE52">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="53" spans="1:31">
+        <v>2</v>
+      </c>
+      <c r="AF52">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="53" spans="1:32">
       <c r="A53">
         <v>126775</v>
       </c>
@@ -5499,10 +5658,13 @@
         <v>0</v>
       </c>
       <c r="AE53">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="54" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF53">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="54" spans="1:32">
       <c r="A54">
         <v>126775</v>
       </c>
@@ -5594,10 +5756,13 @@
         <v>0</v>
       </c>
       <c r="AE54">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="55" spans="1:31">
+        <v>2</v>
+      </c>
+      <c r="AF54">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="55" spans="1:32">
       <c r="A55">
         <v>126818</v>
       </c>
@@ -5689,10 +5854,13 @@
         <v>0</v>
       </c>
       <c r="AE55">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="56" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF55">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="56" spans="1:32">
       <c r="A56">
         <v>126818</v>
       </c>
@@ -5784,10 +5952,13 @@
         <v>0</v>
       </c>
       <c r="AE56">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="57" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF56">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="57" spans="1:32">
       <c r="A57">
         <v>126818</v>
       </c>
@@ -5879,10 +6050,13 @@
         <v>0</v>
       </c>
       <c r="AE57">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="58" spans="1:31">
+        <v>2</v>
+      </c>
+      <c r="AF57">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="58" spans="1:32">
       <c r="A58">
         <v>126818</v>
       </c>
@@ -5974,10 +6148,13 @@
         <v>0</v>
       </c>
       <c r="AE58">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="59" spans="1:31">
+        <v>2</v>
+      </c>
+      <c r="AF58">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="59" spans="1:32">
       <c r="A59">
         <v>127060</v>
       </c>
@@ -6069,10 +6246,13 @@
         <v>1</v>
       </c>
       <c r="AE59">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="60" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF59">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="60" spans="1:32">
       <c r="A60">
         <v>127060</v>
       </c>
@@ -6164,10 +6344,13 @@
         <v>1</v>
       </c>
       <c r="AE60">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="61" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF60">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="61" spans="1:32">
       <c r="A61">
         <v>129020</v>
       </c>
@@ -6259,10 +6442,13 @@
         <v>0</v>
       </c>
       <c r="AE61">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="62" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF61">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="62" spans="1:32">
       <c r="A62">
         <v>129020</v>
       </c>
@@ -6354,10 +6540,13 @@
         <v>0</v>
       </c>
       <c r="AE62">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="63" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF62">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="63" spans="1:32">
       <c r="A63">
         <v>130697</v>
       </c>
@@ -6449,10 +6638,13 @@
         <v>1</v>
       </c>
       <c r="AE63">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="64" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF63">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="64" spans="1:32">
       <c r="A64">
         <v>130697</v>
       </c>
@@ -6544,10 +6736,13 @@
         <v>0</v>
       </c>
       <c r="AE64">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="65" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF64">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="65" spans="1:32">
       <c r="A65">
         <v>130794</v>
       </c>
@@ -6639,10 +6834,13 @@
         <v>0</v>
       </c>
       <c r="AE65">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="66" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF65">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="66" spans="1:32">
       <c r="A66">
         <v>130794</v>
       </c>
@@ -6734,10 +6932,13 @@
         <v>1</v>
       </c>
       <c r="AE66">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="67" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF66">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="67" spans="1:32">
       <c r="A67">
         <v>130934</v>
       </c>
@@ -6829,10 +7030,13 @@
         <v>0</v>
       </c>
       <c r="AE67">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="68" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF67">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="68" spans="1:32">
       <c r="A68">
         <v>130943</v>
       </c>
@@ -6924,10 +7128,13 @@
         <v>0</v>
       </c>
       <c r="AE68">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="69" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF68">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="69" spans="1:32">
       <c r="A69">
         <v>130943</v>
       </c>
@@ -7019,10 +7226,13 @@
         <v>2</v>
       </c>
       <c r="AE69">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="70" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF69">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="70" spans="1:32">
       <c r="A70">
         <v>131283</v>
       </c>
@@ -7114,10 +7324,13 @@
         <v>0</v>
       </c>
       <c r="AE70">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="71" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF70">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="71" spans="1:32">
       <c r="A71">
         <v>131283</v>
       </c>
@@ -7209,10 +7422,13 @@
         <v>0</v>
       </c>
       <c r="AE71">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="72" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF71">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="72" spans="1:32">
       <c r="A72">
         <v>131469</v>
       </c>
@@ -7304,10 +7520,13 @@
         <v>1</v>
       </c>
       <c r="AE72">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="73" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF72">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="73" spans="1:32">
       <c r="A73">
         <v>131469</v>
       </c>
@@ -7399,10 +7618,13 @@
         <v>1</v>
       </c>
       <c r="AE73">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="74" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF73">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="74" spans="1:32">
       <c r="A74">
         <v>131496</v>
       </c>
@@ -7494,10 +7716,13 @@
         <v>2</v>
       </c>
       <c r="AE74">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="75" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF74">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="75" spans="1:32">
       <c r="A75">
         <v>131496</v>
       </c>
@@ -7589,10 +7814,13 @@
         <v>1</v>
       </c>
       <c r="AE75">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="76" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF75">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="76" spans="1:32">
       <c r="A76">
         <v>131520</v>
       </c>
@@ -7684,10 +7912,13 @@
         <v>1</v>
       </c>
       <c r="AE76">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="77" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF76">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="77" spans="1:32">
       <c r="A77">
         <v>131520</v>
       </c>
@@ -7779,10 +8010,13 @@
         <v>1</v>
       </c>
       <c r="AE77">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="78" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF77">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="78" spans="1:32">
       <c r="A78">
         <v>132903</v>
       </c>
@@ -7874,10 +8108,13 @@
         <v>4</v>
       </c>
       <c r="AE78">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="79" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF78">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="79" spans="1:32">
       <c r="A79">
         <v>132903</v>
       </c>
@@ -7969,10 +8206,13 @@
         <v>0</v>
       </c>
       <c r="AE79">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="80" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF79">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="80" spans="1:32">
       <c r="A80">
         <v>133650</v>
       </c>
@@ -8064,10 +8304,13 @@
         <v>0</v>
       </c>
       <c r="AE80">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="81" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF80">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="81" spans="1:32">
       <c r="A81">
         <v>133650</v>
       </c>
@@ -8159,10 +8402,13 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="82" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF81">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="82" spans="1:32">
       <c r="A82">
         <v>133669</v>
       </c>
@@ -8254,10 +8500,13 @@
         <v>3</v>
       </c>
       <c r="AE82">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="83" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF82">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="83" spans="1:32">
       <c r="A83">
         <v>133881</v>
       </c>
@@ -8349,10 +8598,13 @@
         <v>1</v>
       </c>
       <c r="AE83">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="84" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF83">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="84" spans="1:32">
       <c r="A84">
         <v>133881</v>
       </c>
@@ -8444,10 +8696,13 @@
         <v>0</v>
       </c>
       <c r="AE84">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="85" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF84">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="85" spans="1:32">
       <c r="A85">
         <v>133951</v>
       </c>
@@ -8539,10 +8794,13 @@
         <v>0</v>
       </c>
       <c r="AE85">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="86" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF85">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="86" spans="1:32">
       <c r="A86">
         <v>133951</v>
       </c>
@@ -8634,10 +8892,13 @@
         <v>0</v>
       </c>
       <c r="AE86">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="87" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF86">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="87" spans="1:32">
       <c r="A87">
         <v>134097</v>
       </c>
@@ -8729,10 +8990,13 @@
         <v>0</v>
       </c>
       <c r="AE87">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="88" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF87">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="88" spans="1:32">
       <c r="A88">
         <v>134097</v>
       </c>
@@ -8824,10 +9088,13 @@
         <v>0</v>
       </c>
       <c r="AE88">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="89" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF88">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="89" spans="1:32">
       <c r="A89">
         <v>134130</v>
       </c>
@@ -8919,10 +9186,13 @@
         <v>0</v>
       </c>
       <c r="AE89">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="90" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF89">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="90" spans="1:32">
       <c r="A90">
         <v>134130</v>
       </c>
@@ -9014,10 +9284,13 @@
         <v>2</v>
       </c>
       <c r="AE90">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="91" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF90">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="91" spans="1:32">
       <c r="A91">
         <v>135726</v>
       </c>
@@ -9109,10 +9382,13 @@
         <v>0</v>
       </c>
       <c r="AE91">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="92" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF91">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="92" spans="1:32">
       <c r="A92">
         <v>137351</v>
       </c>
@@ -9204,10 +9480,13 @@
         <v>1</v>
       </c>
       <c r="AE92">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="93" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF92">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="93" spans="1:32">
       <c r="A93">
         <v>137351</v>
       </c>
@@ -9299,10 +9578,13 @@
         <v>1</v>
       </c>
       <c r="AE93">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="94" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF93">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="94" spans="1:32">
       <c r="A94">
         <v>138947</v>
       </c>
@@ -9394,10 +9676,13 @@
         <v>0</v>
       </c>
       <c r="AE94">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="95" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF94">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="95" spans="1:32">
       <c r="A95">
         <v>139658</v>
       </c>
@@ -9489,10 +9774,13 @@
         <v>1</v>
       </c>
       <c r="AE95">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="96" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF95">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="96" spans="1:32">
       <c r="A96">
         <v>139658</v>
       </c>
@@ -9584,10 +9872,13 @@
         <v>2</v>
       </c>
       <c r="AE96">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="97" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF96">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="97" spans="1:32">
       <c r="A97">
         <v>139755</v>
       </c>
@@ -9679,10 +9970,13 @@
         <v>1</v>
       </c>
       <c r="AE97">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="98" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF97">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="98" spans="1:32">
       <c r="A98">
         <v>139755</v>
       </c>
@@ -9774,10 +10068,13 @@
         <v>1</v>
       </c>
       <c r="AE98">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="99" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF98">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="99" spans="1:32">
       <c r="A99">
         <v>139940</v>
       </c>
@@ -9869,10 +10166,13 @@
         <v>1</v>
       </c>
       <c r="AE99">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="100" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF99">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="100" spans="1:32">
       <c r="A100">
         <v>139940</v>
       </c>
@@ -9964,10 +10264,13 @@
         <v>1</v>
       </c>
       <c r="AE100">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="101" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF100">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="101" spans="1:32">
       <c r="A101">
         <v>139959</v>
       </c>
@@ -10059,10 +10362,13 @@
         <v>2</v>
       </c>
       <c r="AE101">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="102" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF101">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="102" spans="1:32">
       <c r="A102">
         <v>141574</v>
       </c>
@@ -10154,10 +10460,13 @@
         <v>0</v>
       </c>
       <c r="AE102">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="103" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF102">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="103" spans="1:32">
       <c r="A103">
         <v>141574</v>
       </c>
@@ -10249,10 +10558,13 @@
         <v>0</v>
       </c>
       <c r="AE103">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="104" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF103">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="104" spans="1:32">
       <c r="A104">
         <v>142276</v>
       </c>
@@ -10344,10 +10656,13 @@
         <v>0</v>
       </c>
       <c r="AE104">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="105" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF104">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="105" spans="1:32">
       <c r="A105">
         <v>142276</v>
       </c>
@@ -10439,10 +10754,13 @@
         <v>1</v>
       </c>
       <c r="AE105">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="106" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF105">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="106" spans="1:32">
       <c r="A106">
         <v>142285</v>
       </c>
@@ -10534,10 +10852,13 @@
         <v>1</v>
       </c>
       <c r="AE106">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="107" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF106">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="107" spans="1:32">
       <c r="A107">
         <v>142285</v>
       </c>
@@ -10629,10 +10950,13 @@
         <v>0</v>
       </c>
       <c r="AE107">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="108" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF107">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="108" spans="1:32">
       <c r="A108">
         <v>144050</v>
       </c>
@@ -10724,10 +11048,13 @@
         <v>3</v>
       </c>
       <c r="AE108">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="109" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF108">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="109" spans="1:32">
       <c r="A109">
         <v>144050</v>
       </c>
@@ -10819,10 +11146,13 @@
         <v>0</v>
       </c>
       <c r="AE109">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="110" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF109">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="110" spans="1:32">
       <c r="A110">
         <v>144740</v>
       </c>
@@ -10914,10 +11244,13 @@
         <v>0</v>
       </c>
       <c r="AE110">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="111" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF110">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="111" spans="1:32">
       <c r="A111">
         <v>145600</v>
       </c>
@@ -11009,10 +11342,13 @@
         <v>1</v>
       </c>
       <c r="AE111">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="112" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF111">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="112" spans="1:32">
       <c r="A112">
         <v>145600</v>
       </c>
@@ -11104,10 +11440,13 @@
         <v>0</v>
       </c>
       <c r="AE112">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="113" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF112">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="113" spans="1:32">
       <c r="A113">
         <v>145637</v>
       </c>
@@ -11199,10 +11538,13 @@
         <v>0</v>
       </c>
       <c r="AE113">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="114" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF113">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="114" spans="1:32">
       <c r="A114">
         <v>145637</v>
       </c>
@@ -11294,10 +11636,13 @@
         <v>3</v>
       </c>
       <c r="AE114">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="115" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF114">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="115" spans="1:32">
       <c r="A115">
         <v>145725</v>
       </c>
@@ -11389,10 +11734,13 @@
         <v>0</v>
       </c>
       <c r="AE115">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="116" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF115">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="116" spans="1:32">
       <c r="A116">
         <v>145725</v>
       </c>
@@ -11484,10 +11832,13 @@
         <v>0</v>
       </c>
       <c r="AE116">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="117" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF116">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="117" spans="1:32">
       <c r="A117">
         <v>147703</v>
       </c>
@@ -11579,10 +11930,13 @@
         <v>0</v>
       </c>
       <c r="AE117">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="118" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF117">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="118" spans="1:32">
       <c r="A118">
         <v>147703</v>
       </c>
@@ -11674,10 +12028,13 @@
         <v>0</v>
       </c>
       <c r="AE118">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="119" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF118">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="119" spans="1:32">
       <c r="A119">
         <v>149222</v>
       </c>
@@ -11769,10 +12126,13 @@
         <v>0</v>
       </c>
       <c r="AE119">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="120" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF119">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="120" spans="1:32">
       <c r="A120">
         <v>149222</v>
       </c>
@@ -11864,10 +12224,13 @@
         <v>0</v>
       </c>
       <c r="AE120">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="121" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF120">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="121" spans="1:32">
       <c r="A121">
         <v>149222</v>
       </c>
@@ -11959,10 +12322,13 @@
         <v>0</v>
       </c>
       <c r="AE121">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="122" spans="1:31">
+        <v>2</v>
+      </c>
+      <c r="AF121">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="122" spans="1:32">
       <c r="A122">
         <v>149222</v>
       </c>
@@ -12054,10 +12420,13 @@
         <v>0</v>
       </c>
       <c r="AE122">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="123" spans="1:31">
+        <v>2</v>
+      </c>
+      <c r="AF122">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="123" spans="1:32">
       <c r="A123">
         <v>149231</v>
       </c>
@@ -12149,10 +12518,13 @@
         <v>0</v>
       </c>
       <c r="AE123">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="124" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF123">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="124" spans="1:32">
       <c r="A124">
         <v>149772</v>
       </c>
@@ -12244,10 +12616,13 @@
         <v>1</v>
       </c>
       <c r="AE124">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="125" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF124">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="125" spans="1:32">
       <c r="A125">
         <v>150136</v>
       </c>
@@ -12339,10 +12714,13 @@
         <v>1</v>
       </c>
       <c r="AE125">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="126" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF125">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="126" spans="1:32">
       <c r="A126">
         <v>151111</v>
       </c>
@@ -12434,10 +12812,13 @@
         <v>0</v>
       </c>
       <c r="AE126">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="127" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF126">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="127" spans="1:32">
       <c r="A127">
         <v>151351</v>
       </c>
@@ -12529,10 +12910,13 @@
         <v>0</v>
       </c>
       <c r="AE127">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="128" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF127">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="128" spans="1:32">
       <c r="A128">
         <v>151351</v>
       </c>
@@ -12624,10 +13008,13 @@
         <v>1</v>
       </c>
       <c r="AE128">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="129" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF128">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="129" spans="1:32">
       <c r="A129">
         <v>152080</v>
       </c>
@@ -12719,10 +13106,13 @@
         <v>3</v>
       </c>
       <c r="AE129">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="130" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF129">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="130" spans="1:32">
       <c r="A130">
         <v>152080</v>
       </c>
@@ -12814,10 +13204,13 @@
         <v>2</v>
       </c>
       <c r="AE130">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="131" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF130">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="131" spans="1:32">
       <c r="A131">
         <v>153603</v>
       </c>
@@ -12909,10 +13302,13 @@
         <v>0</v>
       </c>
       <c r="AE131">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="132" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF131">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="132" spans="1:32">
       <c r="A132">
         <v>153658</v>
       </c>
@@ -13004,10 +13400,13 @@
         <v>2</v>
       </c>
       <c r="AE132">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="133" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF132">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="133" spans="1:32">
       <c r="A133">
         <v>153658</v>
       </c>
@@ -13099,10 +13498,13 @@
         <v>1</v>
       </c>
       <c r="AE133">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="134" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF133">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="134" spans="1:32">
       <c r="A134">
         <v>155317</v>
       </c>
@@ -13194,10 +13596,13 @@
         <v>0</v>
       </c>
       <c r="AE134">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="135" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF134">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="135" spans="1:32">
       <c r="A135">
         <v>155317</v>
       </c>
@@ -13289,10 +13694,13 @@
         <v>0</v>
       </c>
       <c r="AE135">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="136" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF135">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="136" spans="1:32">
       <c r="A136">
         <v>155399</v>
       </c>
@@ -13384,10 +13792,13 @@
         <v>0</v>
       </c>
       <c r="AE136">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="137" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF136">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="137" spans="1:32">
       <c r="A137">
         <v>155399</v>
       </c>
@@ -13479,10 +13890,13 @@
         <v>0</v>
       </c>
       <c r="AE137">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="138" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF137">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="138" spans="1:32">
       <c r="A138">
         <v>155681</v>
       </c>
@@ -13574,10 +13988,13 @@
         <v>0</v>
       </c>
       <c r="AE138">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="139" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF138">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="139" spans="1:32">
       <c r="A139">
         <v>157085</v>
       </c>
@@ -13669,10 +14086,13 @@
         <v>1</v>
       </c>
       <c r="AE139">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="140" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF139">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="140" spans="1:32">
       <c r="A140">
         <v>157085</v>
       </c>
@@ -13764,10 +14184,13 @@
         <v>0</v>
       </c>
       <c r="AE140">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="141" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF140">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="141" spans="1:32">
       <c r="A141">
         <v>157289</v>
       </c>
@@ -13859,10 +14282,13 @@
         <v>0</v>
       </c>
       <c r="AE141">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="142" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF141">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="142" spans="1:32">
       <c r="A142">
         <v>157289</v>
       </c>
@@ -13954,10 +14380,13 @@
         <v>0</v>
       </c>
       <c r="AE142">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="143" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF142">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="143" spans="1:32">
       <c r="A143">
         <v>159391</v>
       </c>
@@ -14049,10 +14478,13 @@
         <v>0</v>
       </c>
       <c r="AE143">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="144" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF143">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="144" spans="1:32">
       <c r="A144">
         <v>159391</v>
       </c>
@@ -14144,10 +14576,13 @@
         <v>1</v>
       </c>
       <c r="AE144">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="145" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF144">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="145" spans="1:32">
       <c r="A145">
         <v>159647</v>
       </c>
@@ -14239,10 +14674,13 @@
         <v>2</v>
       </c>
       <c r="AE145">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="146" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF145">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="146" spans="1:32">
       <c r="A146">
         <v>159939</v>
       </c>
@@ -14334,10 +14772,13 @@
         <v>0</v>
       </c>
       <c r="AE146">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="147" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF146">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="147" spans="1:32">
       <c r="A147">
         <v>160621</v>
       </c>
@@ -14429,10 +14870,13 @@
         <v>0</v>
       </c>
       <c r="AE147">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="148" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF147">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="148" spans="1:32">
       <c r="A148">
         <v>160658</v>
       </c>
@@ -14524,10 +14968,13 @@
         <v>0</v>
       </c>
       <c r="AE148">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="149" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF148">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="149" spans="1:32">
       <c r="A149">
         <v>160755</v>
       </c>
@@ -14619,10 +15066,13 @@
         <v>1</v>
       </c>
       <c r="AE149">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="150" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF149">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="150" spans="1:32">
       <c r="A150">
         <v>160755</v>
       </c>
@@ -14714,10 +15164,13 @@
         <v>0</v>
       </c>
       <c r="AE150">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="151" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF150">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="151" spans="1:32">
       <c r="A151">
         <v>161253</v>
       </c>
@@ -14809,10 +15262,13 @@
         <v>0</v>
       </c>
       <c r="AE151">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="152" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF151">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="152" spans="1:32">
       <c r="A152">
         <v>161253</v>
       </c>
@@ -14904,10 +15360,13 @@
         <v>0</v>
       </c>
       <c r="AE152">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="153" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF152">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="153" spans="1:32">
       <c r="A153">
         <v>162928</v>
       </c>
@@ -14999,10 +15458,13 @@
         <v>1</v>
       </c>
       <c r="AE153">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="154" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF153">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="154" spans="1:32">
       <c r="A154">
         <v>162928</v>
       </c>
@@ -15094,10 +15556,13 @@
         <v>1</v>
       </c>
       <c r="AE154">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="155" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF154">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="155" spans="1:32">
       <c r="A155">
         <v>163268</v>
       </c>
@@ -15189,10 +15654,13 @@
         <v>1</v>
       </c>
       <c r="AE155">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="156" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF155">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="156" spans="1:32">
       <c r="A156">
         <v>163268</v>
       </c>
@@ -15284,10 +15752,13 @@
         <v>0</v>
       </c>
       <c r="AE156">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="157" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF156">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="157" spans="1:32">
       <c r="A157">
         <v>163286</v>
       </c>
@@ -15379,10 +15850,13 @@
         <v>0</v>
       </c>
       <c r="AE157">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="158" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF157">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="158" spans="1:32">
       <c r="A158">
         <v>163286</v>
       </c>
@@ -15474,10 +15948,13 @@
         <v>3</v>
       </c>
       <c r="AE158">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="159" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF158">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="159" spans="1:32">
       <c r="A159">
         <v>164924</v>
       </c>
@@ -15569,10 +16046,13 @@
         <v>0</v>
       </c>
       <c r="AE159">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="160" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF159">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="160" spans="1:32">
       <c r="A160">
         <v>164924</v>
       </c>
@@ -15664,10 +16144,13 @@
         <v>0</v>
       </c>
       <c r="AE160">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="161" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF160">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="161" spans="1:32">
       <c r="A161">
         <v>164988</v>
       </c>
@@ -15759,10 +16242,13 @@
         <v>1</v>
       </c>
       <c r="AE161">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="162" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF161">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="162" spans="1:32">
       <c r="A162">
         <v>164988</v>
       </c>
@@ -15854,10 +16340,13 @@
         <v>1</v>
       </c>
       <c r="AE162">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="163" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF162">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="163" spans="1:32">
       <c r="A163">
         <v>165015</v>
       </c>
@@ -15949,10 +16438,13 @@
         <v>0</v>
       </c>
       <c r="AE163">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="164" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF163">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="164" spans="1:32">
       <c r="A164">
         <v>165015</v>
       </c>
@@ -16044,10 +16536,13 @@
         <v>0</v>
       </c>
       <c r="AE164">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="165" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF164">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="165" spans="1:32">
       <c r="A165">
         <v>165334</v>
       </c>
@@ -16139,10 +16634,13 @@
         <v>0</v>
       </c>
       <c r="AE165">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="166" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF165">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="166" spans="1:32">
       <c r="A166">
         <v>165334</v>
       </c>
@@ -16234,10 +16732,13 @@
         <v>0</v>
       </c>
       <c r="AE166">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="167" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF166">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="167" spans="1:32">
       <c r="A167">
         <v>166027</v>
       </c>
@@ -16329,10 +16830,13 @@
         <v>4</v>
       </c>
       <c r="AE167">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="168" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF167">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="168" spans="1:32">
       <c r="A168">
         <v>166027</v>
       </c>
@@ -16424,10 +16928,13 @@
         <v>4</v>
       </c>
       <c r="AE168">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="169" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF168">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="169" spans="1:32">
       <c r="A169">
         <v>166513</v>
       </c>
@@ -16519,10 +17026,13 @@
         <v>1</v>
       </c>
       <c r="AE169">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="170" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF169">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="170" spans="1:32">
       <c r="A170">
         <v>166513</v>
       </c>
@@ -16614,10 +17124,13 @@
         <v>1</v>
       </c>
       <c r="AE170">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="171" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF170">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="171" spans="1:32">
       <c r="A171">
         <v>166629</v>
       </c>
@@ -16709,10 +17222,13 @@
         <v>2</v>
       </c>
       <c r="AE171">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="172" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF171">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="172" spans="1:32">
       <c r="A172">
         <v>166629</v>
       </c>
@@ -16804,10 +17320,13 @@
         <v>1</v>
       </c>
       <c r="AE172">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="173" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF172">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="173" spans="1:32">
       <c r="A173">
         <v>166638</v>
       </c>
@@ -16899,10 +17418,13 @@
         <v>0</v>
       </c>
       <c r="AE173">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="174" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF173">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="174" spans="1:32">
       <c r="A174">
         <v>166683</v>
       </c>
@@ -16994,10 +17516,13 @@
         <v>0</v>
       </c>
       <c r="AE174">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="175" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF174">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="175" spans="1:32">
       <c r="A175">
         <v>166683</v>
       </c>
@@ -17089,10 +17614,13 @@
         <v>4</v>
       </c>
       <c r="AE175">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="176" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF175">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="176" spans="1:32">
       <c r="A176">
         <v>167358</v>
       </c>
@@ -17184,10 +17712,13 @@
         <v>0</v>
       </c>
       <c r="AE176">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="177" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF176">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="177" spans="1:32">
       <c r="A177">
         <v>167358</v>
       </c>
@@ -17279,10 +17810,13 @@
         <v>1</v>
       </c>
       <c r="AE177">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="178" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF177">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="178" spans="1:32">
       <c r="A178">
         <v>167987</v>
       </c>
@@ -17374,10 +17908,13 @@
         <v>0</v>
       </c>
       <c r="AE178">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="179" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF178">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="179" spans="1:32">
       <c r="A179">
         <v>168148</v>
       </c>
@@ -17469,10 +18006,13 @@
         <v>1</v>
       </c>
       <c r="AE179">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="180" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF179">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="180" spans="1:32">
       <c r="A180">
         <v>168148</v>
       </c>
@@ -17564,10 +18104,13 @@
         <v>0</v>
       </c>
       <c r="AE180">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="181" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF180">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="181" spans="1:32">
       <c r="A181">
         <v>168421</v>
       </c>
@@ -17659,10 +18202,13 @@
         <v>0</v>
       </c>
       <c r="AE181">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="182" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF181">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="182" spans="1:32">
       <c r="A182">
         <v>168421</v>
       </c>
@@ -17754,10 +18300,13 @@
         <v>0</v>
       </c>
       <c r="AE182">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="183" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF182">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="183" spans="1:32">
       <c r="A183">
         <v>169248</v>
       </c>
@@ -17849,10 +18398,13 @@
         <v>1</v>
       </c>
       <c r="AE183">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="184" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF183">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="184" spans="1:32">
       <c r="A184">
         <v>169798</v>
       </c>
@@ -17944,10 +18496,13 @@
         <v>0</v>
       </c>
       <c r="AE184">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="185" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF184">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="185" spans="1:32">
       <c r="A185">
         <v>170976</v>
       </c>
@@ -18039,10 +18594,13 @@
         <v>1</v>
       </c>
       <c r="AE185">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="186" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF185">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="186" spans="1:32">
       <c r="A186">
         <v>170976</v>
       </c>
@@ -18134,10 +18692,13 @@
         <v>0</v>
       </c>
       <c r="AE186">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="187" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF186">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="187" spans="1:32">
       <c r="A187">
         <v>171100</v>
       </c>
@@ -18229,10 +18790,13 @@
         <v>2</v>
       </c>
       <c r="AE187">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="188" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF187">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="188" spans="1:32">
       <c r="A188">
         <v>171100</v>
       </c>
@@ -18324,10 +18888,13 @@
         <v>2</v>
       </c>
       <c r="AE188">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="189" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF188">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="189" spans="1:32">
       <c r="A189">
         <v>171128</v>
       </c>
@@ -18419,10 +18986,13 @@
         <v>1</v>
       </c>
       <c r="AE189">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="190" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF189">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="190" spans="1:32">
       <c r="A190">
         <v>171128</v>
       </c>
@@ -18514,10 +19084,13 @@
         <v>0</v>
       </c>
       <c r="AE190">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="191" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF190">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="191" spans="1:32">
       <c r="A191">
         <v>171571</v>
       </c>
@@ -18609,10 +19182,13 @@
         <v>0</v>
       </c>
       <c r="AE191">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="192" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF191">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="192" spans="1:32">
       <c r="A192">
         <v>172644</v>
       </c>
@@ -18704,10 +19280,13 @@
         <v>2</v>
       </c>
       <c r="AE192">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="193" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF192">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="193" spans="1:32">
       <c r="A193">
         <v>172644</v>
       </c>
@@ -18799,10 +19378,13 @@
         <v>0</v>
       </c>
       <c r="AE193">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="194" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF193">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="194" spans="1:32">
       <c r="A194">
         <v>172699</v>
       </c>
@@ -18894,10 +19476,13 @@
         <v>2</v>
       </c>
       <c r="AE194">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="195" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF194">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="195" spans="1:32">
       <c r="A195">
         <v>172699</v>
       </c>
@@ -18989,10 +19574,13 @@
         <v>1</v>
       </c>
       <c r="AE195">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="196" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF195">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="196" spans="1:32">
       <c r="A196">
         <v>173920</v>
       </c>
@@ -19084,10 +19672,13 @@
         <v>1</v>
       </c>
       <c r="AE196">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="197" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF196">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="197" spans="1:32">
       <c r="A197">
         <v>174066</v>
       </c>
@@ -19179,10 +19770,13 @@
         <v>2</v>
       </c>
       <c r="AE197">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="198" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF197">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="198" spans="1:32">
       <c r="A198">
         <v>174066</v>
       </c>
@@ -19274,10 +19868,13 @@
         <v>0</v>
       </c>
       <c r="AE198">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="199" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF198">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="199" spans="1:32">
       <c r="A199">
         <v>174233</v>
       </c>
@@ -19369,10 +19966,13 @@
         <v>0</v>
       </c>
       <c r="AE199">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="200" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF199">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="200" spans="1:32">
       <c r="A200">
         <v>176017</v>
       </c>
@@ -19464,10 +20064,13 @@
         <v>0</v>
       </c>
       <c r="AE200">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="201" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF200">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="201" spans="1:32">
       <c r="A201">
         <v>176017</v>
       </c>
@@ -19559,10 +20162,13 @@
         <v>0</v>
       </c>
       <c r="AE201">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="202" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF201">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="202" spans="1:32">
       <c r="A202">
         <v>176080</v>
       </c>
@@ -19654,10 +20260,13 @@
         <v>2</v>
       </c>
       <c r="AE202">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="203" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF202">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="203" spans="1:32">
       <c r="A203">
         <v>176372</v>
       </c>
@@ -19749,10 +20358,13 @@
         <v>1</v>
       </c>
       <c r="AE203">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="204" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF203">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="204" spans="1:32">
       <c r="A204">
         <v>178396</v>
       </c>
@@ -19844,10 +20456,13 @@
         <v>3</v>
       </c>
       <c r="AE204">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="205" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF204">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="205" spans="1:32">
       <c r="A205">
         <v>178396</v>
       </c>
@@ -19939,10 +20554,13 @@
         <v>1</v>
       </c>
       <c r="AE205">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="206" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF205">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="206" spans="1:32">
       <c r="A206">
         <v>178402</v>
       </c>
@@ -20034,10 +20652,13 @@
         <v>1</v>
       </c>
       <c r="AE206">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="207" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF206">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="207" spans="1:32">
       <c r="A207">
         <v>178411</v>
       </c>
@@ -20129,10 +20750,13 @@
         <v>2</v>
       </c>
       <c r="AE207">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="208" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF207">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="208" spans="1:32">
       <c r="A208">
         <v>178411</v>
       </c>
@@ -20224,10 +20848,13 @@
         <v>1</v>
       </c>
       <c r="AE208">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="209" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF208">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="209" spans="1:32">
       <c r="A209">
         <v>178420</v>
       </c>
@@ -20319,10 +20946,13 @@
         <v>0</v>
       </c>
       <c r="AE209">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="210" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF209">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="210" spans="1:32">
       <c r="A210">
         <v>179867</v>
       </c>
@@ -20414,10 +21044,13 @@
         <v>1</v>
       </c>
       <c r="AE210">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="211" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF210">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="211" spans="1:32">
       <c r="A211">
         <v>179867</v>
       </c>
@@ -20509,10 +21142,13 @@
         <v>0</v>
       </c>
       <c r="AE211">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="212" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF211">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="212" spans="1:32">
       <c r="A212">
         <v>180461</v>
       </c>
@@ -20604,10 +21240,13 @@
         <v>0</v>
       </c>
       <c r="AE212">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="213" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF212">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="213" spans="1:32">
       <c r="A213">
         <v>180461</v>
       </c>
@@ -20699,10 +21338,13 @@
         <v>2</v>
       </c>
       <c r="AE213">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="214" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF213">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="214" spans="1:32">
       <c r="A214">
         <v>180489</v>
       </c>
@@ -20794,10 +21436,13 @@
         <v>0</v>
       </c>
       <c r="AE214">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="215" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF214">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="215" spans="1:32">
       <c r="A215">
         <v>181002</v>
       </c>
@@ -20889,10 +21534,13 @@
         <v>0</v>
       </c>
       <c r="AE215">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="216" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF215">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="216" spans="1:32">
       <c r="A216">
         <v>181464</v>
       </c>
@@ -20984,10 +21632,13 @@
         <v>1</v>
       </c>
       <c r="AE216">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="217" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF216">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="217" spans="1:32">
       <c r="A217">
         <v>181464</v>
       </c>
@@ -21079,10 +21730,13 @@
         <v>2</v>
       </c>
       <c r="AE217">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="218" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF217">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="218" spans="1:32">
       <c r="A218">
         <v>182281</v>
       </c>
@@ -21174,10 +21828,13 @@
         <v>0</v>
       </c>
       <c r="AE218">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="219" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF218">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="219" spans="1:32">
       <c r="A219">
         <v>182281</v>
       </c>
@@ -21269,10 +21926,13 @@
         <v>0</v>
       </c>
       <c r="AE219">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="220" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF219">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="220" spans="1:32">
       <c r="A220">
         <v>182290</v>
       </c>
@@ -21364,10 +22024,13 @@
         <v>0</v>
       </c>
       <c r="AE220">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="221" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF220">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="221" spans="1:32">
       <c r="A221">
         <v>182290</v>
       </c>
@@ -21459,10 +22122,13 @@
         <v>2</v>
       </c>
       <c r="AE221">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="222" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF221">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="222" spans="1:32">
       <c r="A222">
         <v>182670</v>
       </c>
@@ -21554,10 +22220,13 @@
         <v>0</v>
       </c>
       <c r="AE222">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="223" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF222">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="223" spans="1:32">
       <c r="A223">
         <v>182670</v>
       </c>
@@ -21649,10 +22318,13 @@
         <v>0</v>
       </c>
       <c r="AE223">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="224" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF223">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="224" spans="1:32">
       <c r="A224">
         <v>183044</v>
       </c>
@@ -21744,10 +22416,13 @@
         <v>2</v>
       </c>
       <c r="AE224">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="225" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF224">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="225" spans="1:32">
       <c r="A225">
         <v>183044</v>
       </c>
@@ -21839,10 +22514,13 @@
         <v>1</v>
       </c>
       <c r="AE225">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="226" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF225">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="226" spans="1:32">
       <c r="A226">
         <v>185828</v>
       </c>
@@ -21934,10 +22612,13 @@
         <v>0</v>
       </c>
       <c r="AE226">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="227" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF226">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="227" spans="1:32">
       <c r="A227">
         <v>185828</v>
       </c>
@@ -22029,10 +22710,13 @@
         <v>0</v>
       </c>
       <c r="AE227">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="228" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF227">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="228" spans="1:32">
       <c r="A228">
         <v>186131</v>
       </c>
@@ -22124,10 +22808,13 @@
         <v>1</v>
       </c>
       <c r="AE228">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="229" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF228">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="229" spans="1:32">
       <c r="A229">
         <v>186131</v>
       </c>
@@ -22219,10 +22906,13 @@
         <v>1</v>
       </c>
       <c r="AE229">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="230" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF229">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="230" spans="1:32">
       <c r="A230">
         <v>186867</v>
       </c>
@@ -22314,10 +23004,13 @@
         <v>0</v>
       </c>
       <c r="AE230">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="231" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF230">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="231" spans="1:32">
       <c r="A231">
         <v>186867</v>
       </c>
@@ -22409,10 +23102,13 @@
         <v>1</v>
       </c>
       <c r="AE231">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="232" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF231">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="232" spans="1:32">
       <c r="A232">
         <v>187967</v>
       </c>
@@ -22504,10 +23200,13 @@
         <v>0</v>
       </c>
       <c r="AE232">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="233" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF232">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="233" spans="1:32">
       <c r="A233">
         <v>187967</v>
       </c>
@@ -22599,10 +23298,13 @@
         <v>0</v>
       </c>
       <c r="AE233">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="234" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF233">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="234" spans="1:32">
       <c r="A234">
         <v>187985</v>
       </c>
@@ -22694,10 +23396,13 @@
         <v>2</v>
       </c>
       <c r="AE234">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="235" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF234">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="235" spans="1:32">
       <c r="A235">
         <v>187985</v>
       </c>
@@ -22789,10 +23494,13 @@
         <v>0</v>
       </c>
       <c r="AE235">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="236" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF235">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="236" spans="1:32">
       <c r="A236">
         <v>188030</v>
       </c>
@@ -22884,10 +23592,13 @@
         <v>0</v>
       </c>
       <c r="AE236">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="237" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF236">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="237" spans="1:32">
       <c r="A237">
         <v>188030</v>
       </c>
@@ -22979,10 +23690,13 @@
         <v>1</v>
       </c>
       <c r="AE237">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="238" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF237">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="238" spans="1:32">
       <c r="A238">
         <v>190044</v>
       </c>
@@ -23074,10 +23788,13 @@
         <v>0</v>
       </c>
       <c r="AE238">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="239" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF238">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="239" spans="1:32">
       <c r="A239">
         <v>190044</v>
       </c>
@@ -23169,10 +23886,13 @@
         <v>0</v>
       </c>
       <c r="AE239">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="240" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF239">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="240" spans="1:32">
       <c r="A240">
         <v>190150</v>
       </c>
@@ -23264,10 +23984,13 @@
         <v>1</v>
       </c>
       <c r="AE240">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="241" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF240">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="241" spans="1:32">
       <c r="A241">
         <v>190150</v>
       </c>
@@ -23359,10 +24082,13 @@
         <v>2</v>
       </c>
       <c r="AE241">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="242" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF241">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="242" spans="1:32">
       <c r="A242">
         <v>190415</v>
       </c>
@@ -23454,10 +24180,13 @@
         <v>0</v>
       </c>
       <c r="AE242">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="243" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF242">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="243" spans="1:32">
       <c r="A243">
         <v>190415</v>
       </c>
@@ -23549,10 +24278,13 @@
         <v>2</v>
       </c>
       <c r="AE243">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="244" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF243">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="244" spans="1:32">
       <c r="A244">
         <v>190549</v>
       </c>
@@ -23644,10 +24376,13 @@
         <v>0</v>
       </c>
       <c r="AE244">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="245" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF244">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="245" spans="1:32">
       <c r="A245">
         <v>190567</v>
       </c>
@@ -23739,10 +24474,13 @@
         <v>1</v>
       </c>
       <c r="AE245">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="246" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF245">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="246" spans="1:32">
       <c r="A246">
         <v>190576</v>
       </c>
@@ -23834,10 +24572,13 @@
         <v>0</v>
       </c>
       <c r="AE246">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="247" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF246">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="247" spans="1:32">
       <c r="A247">
         <v>190576</v>
       </c>
@@ -23929,10 +24670,13 @@
         <v>3</v>
       </c>
       <c r="AE247">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="248" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF247">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="248" spans="1:32">
       <c r="A248">
         <v>190594</v>
       </c>
@@ -24024,10 +24768,13 @@
         <v>0</v>
       </c>
       <c r="AE248">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="249" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF248">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="249" spans="1:32">
       <c r="A249">
         <v>190664</v>
       </c>
@@ -24119,10 +24866,13 @@
         <v>0</v>
       </c>
       <c r="AE249">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="250" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF249">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="250" spans="1:32">
       <c r="A250">
         <v>193900</v>
       </c>
@@ -24214,10 +24964,13 @@
         <v>0</v>
       </c>
       <c r="AE250">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="251" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF250">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="251" spans="1:32">
       <c r="A251">
         <v>193900</v>
       </c>
@@ -24309,10 +25062,13 @@
         <v>0</v>
       </c>
       <c r="AE251">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="252" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF251">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="252" spans="1:32">
       <c r="A252">
         <v>194824</v>
       </c>
@@ -24404,10 +25160,13 @@
         <v>1</v>
       </c>
       <c r="AE252">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="253" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF252">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="253" spans="1:32">
       <c r="A253">
         <v>194824</v>
       </c>
@@ -24499,10 +25258,13 @@
         <v>0</v>
       </c>
       <c r="AE253">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="254" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF253">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="254" spans="1:32">
       <c r="A254">
         <v>195030</v>
       </c>
@@ -24594,10 +25356,13 @@
         <v>1</v>
       </c>
       <c r="AE254">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="255" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF254">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="255" spans="1:32">
       <c r="A255">
         <v>195030</v>
       </c>
@@ -24689,10 +25454,13 @@
         <v>1</v>
       </c>
       <c r="AE255">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="256" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF255">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="256" spans="1:32">
       <c r="A256">
         <v>195030</v>
       </c>
@@ -24784,10 +25552,13 @@
         <v>0</v>
       </c>
       <c r="AE256">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="257" spans="1:31">
+        <v>2</v>
+      </c>
+      <c r="AF256">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="257" spans="1:32">
       <c r="A257">
         <v>196060</v>
       </c>
@@ -24879,10 +25650,13 @@
         <v>0</v>
       </c>
       <c r="AE257">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="258" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF257">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="258" spans="1:32">
       <c r="A258">
         <v>196060</v>
       </c>
@@ -24974,10 +25748,13 @@
         <v>0</v>
       </c>
       <c r="AE258">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="259" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF258">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="259" spans="1:32">
       <c r="A259">
         <v>196079</v>
       </c>
@@ -25069,10 +25846,13 @@
         <v>0</v>
       </c>
       <c r="AE259">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="260" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF259">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="260" spans="1:32">
       <c r="A260">
         <v>196088</v>
       </c>
@@ -25164,10 +25944,13 @@
         <v>1</v>
       </c>
       <c r="AE260">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="261" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF260">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="261" spans="1:32">
       <c r="A261">
         <v>196088</v>
       </c>
@@ -25259,10 +26042,13 @@
         <v>1</v>
       </c>
       <c r="AE261">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="262" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF261">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="262" spans="1:32">
       <c r="A262">
         <v>196097</v>
       </c>
@@ -25354,10 +26140,13 @@
         <v>2</v>
       </c>
       <c r="AE262">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="263" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF262">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="263" spans="1:32">
       <c r="A263">
         <v>196097</v>
       </c>
@@ -25449,10 +26238,13 @@
         <v>2</v>
       </c>
       <c r="AE263">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="264" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF263">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="264" spans="1:32">
       <c r="A264">
         <v>196413</v>
       </c>
@@ -25544,10 +26336,13 @@
         <v>0</v>
       </c>
       <c r="AE264">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="265" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF264">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="265" spans="1:32">
       <c r="A265">
         <v>196413</v>
       </c>
@@ -25639,10 +26434,13 @@
         <v>1</v>
       </c>
       <c r="AE265">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="266" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF265">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="266" spans="1:32">
       <c r="A266">
         <v>197869</v>
       </c>
@@ -25734,10 +26532,13 @@
         <v>0</v>
       </c>
       <c r="AE266">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="267" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF266">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="267" spans="1:32">
       <c r="A267">
         <v>198419</v>
       </c>
@@ -25829,10 +26630,13 @@
         <v>0</v>
       </c>
       <c r="AE267">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="268" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF267">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="268" spans="1:32">
       <c r="A268">
         <v>198419</v>
       </c>
@@ -25924,10 +26728,13 @@
         <v>0</v>
       </c>
       <c r="AE268">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="269" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF268">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="269" spans="1:32">
       <c r="A269">
         <v>198464</v>
       </c>
@@ -26019,10 +26826,13 @@
         <v>0</v>
       </c>
       <c r="AE269">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="270" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF269">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="270" spans="1:32">
       <c r="A270">
         <v>199102</v>
       </c>
@@ -26114,10 +26924,13 @@
         <v>0</v>
       </c>
       <c r="AE270">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="271" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF270">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="271" spans="1:32">
       <c r="A271">
         <v>199120</v>
       </c>
@@ -26209,10 +27022,13 @@
         <v>0</v>
       </c>
       <c r="AE271">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="272" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF271">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="272" spans="1:32">
       <c r="A272">
         <v>199120</v>
       </c>
@@ -26304,10 +27120,13 @@
         <v>0</v>
       </c>
       <c r="AE272">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="273" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF272">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="273" spans="1:32">
       <c r="A273">
         <v>199139</v>
       </c>
@@ -26399,10 +27218,13 @@
         <v>0</v>
       </c>
       <c r="AE273">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="274" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF273">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="274" spans="1:32">
       <c r="A274">
         <v>199157</v>
       </c>
@@ -26494,10 +27316,13 @@
         <v>0</v>
       </c>
       <c r="AE274">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="275" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF274">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="275" spans="1:32">
       <c r="A275">
         <v>199193</v>
       </c>
@@ -26589,10 +27414,13 @@
         <v>2</v>
       </c>
       <c r="AE275">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="276" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF275">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="276" spans="1:32">
       <c r="A276">
         <v>199193</v>
       </c>
@@ -26684,10 +27512,13 @@
         <v>0</v>
       </c>
       <c r="AE276">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="277" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF276">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="277" spans="1:32">
       <c r="A277">
         <v>199847</v>
       </c>
@@ -26779,10 +27610,13 @@
         <v>0</v>
       </c>
       <c r="AE277">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="278" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF277">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="278" spans="1:32">
       <c r="A278">
         <v>199847</v>
       </c>
@@ -26874,10 +27708,13 @@
         <v>0</v>
       </c>
       <c r="AE278">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="279" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF278">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="279" spans="1:32">
       <c r="A279">
         <v>200280</v>
       </c>
@@ -26969,10 +27806,13 @@
         <v>0</v>
       </c>
       <c r="AE279">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="280" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF279">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="280" spans="1:32">
       <c r="A280">
         <v>200280</v>
       </c>
@@ -27064,10 +27904,13 @@
         <v>0</v>
       </c>
       <c r="AE280">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="281" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF280">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="281" spans="1:32">
       <c r="A281">
         <v>200332</v>
       </c>
@@ -27159,10 +28002,13 @@
         <v>0</v>
       </c>
       <c r="AE281">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="282" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF281">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="282" spans="1:32">
       <c r="A282">
         <v>200332</v>
       </c>
@@ -27254,10 +28100,13 @@
         <v>0</v>
       </c>
       <c r="AE282">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="283" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF282">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="283" spans="1:32">
       <c r="A283">
         <v>200800</v>
       </c>
@@ -27349,10 +28198,13 @@
         <v>1</v>
       </c>
       <c r="AE283">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="284" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF283">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="284" spans="1:32">
       <c r="A284">
         <v>201441</v>
       </c>
@@ -27444,10 +28296,13 @@
         <v>1</v>
       </c>
       <c r="AE284">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="285" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF284">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="285" spans="1:32">
       <c r="A285">
         <v>201645</v>
       </c>
@@ -27539,10 +28394,13 @@
         <v>0</v>
       </c>
       <c r="AE285">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="286" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF285">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="286" spans="1:32">
       <c r="A286">
         <v>201645</v>
       </c>
@@ -27634,10 +28492,13 @@
         <v>1</v>
       </c>
       <c r="AE286">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="287" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF286">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="287" spans="1:32">
       <c r="A287">
         <v>201885</v>
       </c>
@@ -27729,10 +28590,13 @@
         <v>2</v>
       </c>
       <c r="AE287">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="288" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF287">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="288" spans="1:32">
       <c r="A288">
         <v>201885</v>
       </c>
@@ -27824,10 +28688,13 @@
         <v>0</v>
       </c>
       <c r="AE288">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="289" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF288">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="289" spans="1:32">
       <c r="A289">
         <v>202134</v>
       </c>
@@ -27919,10 +28786,13 @@
         <v>0</v>
       </c>
       <c r="AE289">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="290" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF289">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="290" spans="1:32">
       <c r="A290">
         <v>203368</v>
       </c>
@@ -28014,10 +28884,13 @@
         <v>0</v>
       </c>
       <c r="AE290">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="291" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF290">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="291" spans="1:32">
       <c r="A291">
         <v>203517</v>
       </c>
@@ -28109,10 +28982,13 @@
         <v>0</v>
       </c>
       <c r="AE291">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="292" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF291">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="292" spans="1:32">
       <c r="A292">
         <v>203517</v>
       </c>
@@ -28204,10 +29080,13 @@
         <v>0</v>
       </c>
       <c r="AE292">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="293" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF292">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="293" spans="1:32">
       <c r="A293">
         <v>204024</v>
       </c>
@@ -28299,10 +29178,13 @@
         <v>1</v>
       </c>
       <c r="AE293">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="294" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF293">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="294" spans="1:32">
       <c r="A294">
         <v>204796</v>
       </c>
@@ -28394,10 +29276,13 @@
         <v>0</v>
       </c>
       <c r="AE294">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="295" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF294">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="295" spans="1:32">
       <c r="A295">
         <v>204796</v>
       </c>
@@ -28489,10 +29374,13 @@
         <v>1</v>
       </c>
       <c r="AE295">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="296" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF295">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="296" spans="1:32">
       <c r="A296">
         <v>204857</v>
       </c>
@@ -28584,10 +29472,13 @@
         <v>0</v>
       </c>
       <c r="AE296">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="297" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF296">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="297" spans="1:32">
       <c r="A297">
         <v>204857</v>
       </c>
@@ -28679,10 +29570,13 @@
         <v>2</v>
       </c>
       <c r="AE297">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="298" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF297">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="298" spans="1:32">
       <c r="A298">
         <v>206084</v>
       </c>
@@ -28774,10 +29668,13 @@
         <v>0</v>
       </c>
       <c r="AE298">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="299" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF298">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="299" spans="1:32">
       <c r="A299">
         <v>206084</v>
       </c>
@@ -28869,10 +29766,13 @@
         <v>0</v>
       </c>
       <c r="AE299">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="300" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF299">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="300" spans="1:32">
       <c r="A300">
         <v>206084</v>
       </c>
@@ -28964,10 +29864,13 @@
         <v>0</v>
       </c>
       <c r="AE300">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="301" spans="1:31">
+        <v>2</v>
+      </c>
+      <c r="AF300">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="301" spans="1:32">
       <c r="A301">
         <v>206604</v>
       </c>
@@ -29059,10 +29962,13 @@
         <v>0</v>
       </c>
       <c r="AE301">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="302" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF301">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="302" spans="1:32">
       <c r="A302">
         <v>207388</v>
       </c>
@@ -29154,10 +30060,13 @@
         <v>1</v>
       </c>
       <c r="AE302">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="303" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF302">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="303" spans="1:32">
       <c r="A303">
         <v>207388</v>
       </c>
@@ -29249,10 +30158,13 @@
         <v>1</v>
       </c>
       <c r="AE303">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="304" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF303">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="304" spans="1:32">
       <c r="A304">
         <v>207500</v>
       </c>
@@ -29344,10 +30256,13 @@
         <v>0</v>
       </c>
       <c r="AE304">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="305" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF304">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="305" spans="1:32">
       <c r="A305">
         <v>207500</v>
       </c>
@@ -29439,10 +30354,13 @@
         <v>0</v>
       </c>
       <c r="AE305">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="306" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF305">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="306" spans="1:32">
       <c r="A306">
         <v>207971</v>
       </c>
@@ -29534,10 +30452,13 @@
         <v>1</v>
       </c>
       <c r="AE306">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="307" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF306">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="307" spans="1:32">
       <c r="A307">
         <v>209542</v>
       </c>
@@ -29629,10 +30550,13 @@
         <v>0</v>
       </c>
       <c r="AE307">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="308" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF307">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="308" spans="1:32">
       <c r="A308">
         <v>209542</v>
       </c>
@@ -29724,10 +30648,13 @@
         <v>0</v>
       </c>
       <c r="AE308">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="309" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF308">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="309" spans="1:32">
       <c r="A309">
         <v>209551</v>
       </c>
@@ -29819,10 +30746,13 @@
         <v>0</v>
       </c>
       <c r="AE309">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="310" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF309">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="310" spans="1:32">
       <c r="A310">
         <v>209551</v>
       </c>
@@ -29914,10 +30844,13 @@
         <v>1</v>
       </c>
       <c r="AE310">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="311" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF310">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="311" spans="1:32">
       <c r="A311">
         <v>209807</v>
       </c>
@@ -30009,10 +30942,13 @@
         <v>1</v>
       </c>
       <c r="AE311">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="312" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF311">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="312" spans="1:32">
       <c r="A312">
         <v>209807</v>
       </c>
@@ -30104,10 +31040,13 @@
         <v>0</v>
       </c>
       <c r="AE312">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="313" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF312">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="313" spans="1:32">
       <c r="A313">
         <v>211273</v>
       </c>
@@ -30199,10 +31138,13 @@
         <v>0</v>
       </c>
       <c r="AE313">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="314" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF313">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="314" spans="1:32">
       <c r="A314">
         <v>211361</v>
       </c>
@@ -30294,10 +31236,13 @@
         <v>0</v>
       </c>
       <c r="AE314">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="315" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF314">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="315" spans="1:32">
       <c r="A315">
         <v>211440</v>
       </c>
@@ -30389,10 +31334,13 @@
         <v>0</v>
       </c>
       <c r="AE315">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="316" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF315">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="316" spans="1:32">
       <c r="A316">
         <v>211440</v>
       </c>
@@ -30484,10 +31432,13 @@
         <v>1</v>
       </c>
       <c r="AE316">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="317" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF316">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="317" spans="1:32">
       <c r="A317">
         <v>213543</v>
       </c>
@@ -30579,10 +31530,13 @@
         <v>1</v>
       </c>
       <c r="AE317">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="318" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF317">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="318" spans="1:32">
       <c r="A318">
         <v>213543</v>
       </c>
@@ -30674,10 +31628,13 @@
         <v>1</v>
       </c>
       <c r="AE318">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="319" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF318">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="319" spans="1:32">
       <c r="A319">
         <v>214777</v>
       </c>
@@ -30769,10 +31726,13 @@
         <v>0</v>
       </c>
       <c r="AE319">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="320" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF319">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="320" spans="1:32">
       <c r="A320">
         <v>215062</v>
       </c>
@@ -30864,10 +31824,13 @@
         <v>1</v>
       </c>
       <c r="AE320">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="321" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF320">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="321" spans="1:32">
       <c r="A321">
         <v>215062</v>
       </c>
@@ -30959,10 +31922,13 @@
         <v>1</v>
       </c>
       <c r="AE321">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="322" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF321">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="322" spans="1:32">
       <c r="A322">
         <v>215293</v>
       </c>
@@ -31054,10 +32020,13 @@
         <v>2</v>
       </c>
       <c r="AE322">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="323" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF322">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="323" spans="1:32">
       <c r="A323">
         <v>215293</v>
       </c>
@@ -31149,10 +32118,13 @@
         <v>0</v>
       </c>
       <c r="AE323">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="324" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF323">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="324" spans="1:32">
       <c r="A324">
         <v>216339</v>
       </c>
@@ -31244,10 +32216,13 @@
         <v>3</v>
       </c>
       <c r="AE324">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="325" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF324">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="325" spans="1:32">
       <c r="A325">
         <v>216339</v>
       </c>
@@ -31339,10 +32314,13 @@
         <v>0</v>
       </c>
       <c r="AE325">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="326" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF325">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="326" spans="1:32">
       <c r="A326">
         <v>217156</v>
       </c>
@@ -31434,10 +32412,13 @@
         <v>4</v>
       </c>
       <c r="AE326">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="327" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF326">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="327" spans="1:32">
       <c r="A327">
         <v>217156</v>
       </c>
@@ -31529,10 +32510,13 @@
         <v>1</v>
       </c>
       <c r="AE327">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="328" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF327">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="328" spans="1:32">
       <c r="A328">
         <v>217484</v>
       </c>
@@ -31624,10 +32608,13 @@
         <v>0</v>
       </c>
       <c r="AE328">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="329" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF328">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="329" spans="1:32">
       <c r="A329">
         <v>217484</v>
       </c>
@@ -31719,10 +32706,13 @@
         <v>0</v>
       </c>
       <c r="AE329">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="330" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF329">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="330" spans="1:32">
       <c r="A330">
         <v>217882</v>
       </c>
@@ -31814,10 +32804,13 @@
         <v>1</v>
       </c>
       <c r="AE330">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="331" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF330">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="331" spans="1:32">
       <c r="A331">
         <v>217882</v>
       </c>
@@ -31909,10 +32902,13 @@
         <v>0</v>
       </c>
       <c r="AE331">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="332" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF331">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="332" spans="1:32">
       <c r="A332">
         <v>218663</v>
       </c>
@@ -32004,10 +33000,13 @@
         <v>0</v>
       </c>
       <c r="AE332">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="333" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF332">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="333" spans="1:32">
       <c r="A333">
         <v>218663</v>
       </c>
@@ -32099,10 +33098,13 @@
         <v>0</v>
       </c>
       <c r="AE333">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="334" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF333">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="334" spans="1:32">
       <c r="A334">
         <v>219347</v>
       </c>
@@ -32194,10 +33196,13 @@
         <v>0</v>
       </c>
       <c r="AE334">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="335" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF334">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="335" spans="1:32">
       <c r="A335">
         <v>219356</v>
       </c>
@@ -32289,10 +33294,13 @@
         <v>0</v>
       </c>
       <c r="AE335">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="336" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF335">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="336" spans="1:32">
       <c r="A336">
         <v>220181</v>
       </c>
@@ -32384,10 +33392,13 @@
         <v>0</v>
       </c>
       <c r="AE336">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="337" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF336">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="337" spans="1:32">
       <c r="A337">
         <v>220862</v>
       </c>
@@ -32479,10 +33490,13 @@
         <v>1</v>
       </c>
       <c r="AE337">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="338" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF337">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="338" spans="1:32">
       <c r="A338">
         <v>221759</v>
       </c>
@@ -32574,10 +33588,13 @@
         <v>0</v>
       </c>
       <c r="AE338">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="339" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF338">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="339" spans="1:32">
       <c r="A339">
         <v>221759</v>
       </c>
@@ -32669,10 +33686,13 @@
         <v>1</v>
       </c>
       <c r="AE339">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="340" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF339">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="340" spans="1:32">
       <c r="A340">
         <v>221999</v>
       </c>
@@ -32764,10 +33784,13 @@
         <v>0</v>
       </c>
       <c r="AE340">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="341" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF340">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="341" spans="1:32">
       <c r="A341">
         <v>221999</v>
       </c>
@@ -32859,10 +33882,13 @@
         <v>3</v>
       </c>
       <c r="AE341">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="342" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF341">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="342" spans="1:32">
       <c r="A342">
         <v>221999</v>
       </c>
@@ -32954,10 +33980,13 @@
         <v>0</v>
       </c>
       <c r="AE342">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="343" spans="1:31">
+        <v>2</v>
+      </c>
+      <c r="AF342">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="343" spans="1:32">
       <c r="A343">
         <v>221999</v>
       </c>
@@ -33049,10 +34078,13 @@
         <v>0</v>
       </c>
       <c r="AE343">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="344" spans="1:31">
+        <v>2</v>
+      </c>
+      <c r="AF343">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="344" spans="1:32">
       <c r="A344">
         <v>223232</v>
       </c>
@@ -33144,10 +34176,13 @@
         <v>0</v>
       </c>
       <c r="AE344">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="345" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF344">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="345" spans="1:32">
       <c r="A345">
         <v>223232</v>
       </c>
@@ -33239,10 +34274,13 @@
         <v>0</v>
       </c>
       <c r="AE345">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="346" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF345">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="346" spans="1:32">
       <c r="A346">
         <v>224554</v>
       </c>
@@ -33334,10 +34372,13 @@
         <v>0</v>
       </c>
       <c r="AE346">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="347" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF346">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="347" spans="1:32">
       <c r="A347">
         <v>225414</v>
       </c>
@@ -33429,10 +34470,13 @@
         <v>0</v>
       </c>
       <c r="AE347">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="348" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF347">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="348" spans="1:32">
       <c r="A348">
         <v>225511</v>
       </c>
@@ -33524,10 +34568,13 @@
         <v>2</v>
       </c>
       <c r="AE348">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="349" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF348">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="349" spans="1:32">
       <c r="A349">
         <v>225511</v>
       </c>
@@ -33619,10 +34666,13 @@
         <v>1</v>
       </c>
       <c r="AE349">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="350" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF349">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="350" spans="1:32">
       <c r="A350">
         <v>227216</v>
       </c>
@@ -33714,10 +34764,13 @@
         <v>0</v>
       </c>
       <c r="AE350">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="351" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF350">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="351" spans="1:32">
       <c r="A351">
         <v>227216</v>
       </c>
@@ -33809,10 +34862,13 @@
         <v>0</v>
       </c>
       <c r="AE351">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="352" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF351">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="352" spans="1:32">
       <c r="A352">
         <v>227377</v>
       </c>
@@ -33904,10 +34960,13 @@
         <v>0</v>
       </c>
       <c r="AE352">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="353" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF352">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="353" spans="1:32">
       <c r="A353">
         <v>227757</v>
       </c>
@@ -33999,10 +35058,13 @@
         <v>1</v>
       </c>
       <c r="AE353">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="354" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF353">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="354" spans="1:32">
       <c r="A354">
         <v>227757</v>
       </c>
@@ -34094,10 +35156,13 @@
         <v>2</v>
       </c>
       <c r="AE354">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="355" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF354">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="355" spans="1:32">
       <c r="A355">
         <v>228246</v>
       </c>
@@ -34189,10 +35254,13 @@
         <v>0</v>
       </c>
       <c r="AE355">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="356" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF355">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="356" spans="1:32">
       <c r="A356">
         <v>228246</v>
       </c>
@@ -34284,10 +35352,13 @@
         <v>0</v>
       </c>
       <c r="AE356">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="357" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF356">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="357" spans="1:32">
       <c r="A357">
         <v>228431</v>
       </c>
@@ -34379,10 +35450,13 @@
         <v>0</v>
       </c>
       <c r="AE357">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="358" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF357">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="358" spans="1:32">
       <c r="A358">
         <v>228459</v>
       </c>
@@ -34474,10 +35548,13 @@
         <v>0</v>
       </c>
       <c r="AE358">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="359" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF358">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="359" spans="1:32">
       <c r="A359">
         <v>228723</v>
       </c>
@@ -34569,10 +35646,13 @@
         <v>1</v>
       </c>
       <c r="AE359">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="360" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF359">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="360" spans="1:32">
       <c r="A360">
         <v>228723</v>
       </c>
@@ -34664,10 +35744,13 @@
         <v>2</v>
       </c>
       <c r="AE360">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="361" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF360">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="361" spans="1:32">
       <c r="A361">
         <v>228769</v>
       </c>
@@ -34759,10 +35842,13 @@
         <v>1</v>
       </c>
       <c r="AE361">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="362" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF361">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="362" spans="1:32">
       <c r="A362">
         <v>228769</v>
       </c>
@@ -34854,10 +35940,13 @@
         <v>1</v>
       </c>
       <c r="AE362">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="363" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF362">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="363" spans="1:32">
       <c r="A363">
         <v>228778</v>
       </c>
@@ -34949,10 +36038,13 @@
         <v>0</v>
       </c>
       <c r="AE363">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="364" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF363">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="364" spans="1:32">
       <c r="A364">
         <v>228778</v>
       </c>
@@ -35044,10 +36136,13 @@
         <v>0</v>
       </c>
       <c r="AE364">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="365" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF364">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="365" spans="1:32">
       <c r="A365">
         <v>228787</v>
       </c>
@@ -35139,10 +36234,13 @@
         <v>2</v>
       </c>
       <c r="AE365">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="366" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF365">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="366" spans="1:32">
       <c r="A366">
         <v>228787</v>
       </c>
@@ -35234,10 +36332,13 @@
         <v>0</v>
       </c>
       <c r="AE366">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="367" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF366">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="367" spans="1:32">
       <c r="A367">
         <v>228796</v>
       </c>
@@ -35329,10 +36430,13 @@
         <v>1</v>
       </c>
       <c r="AE367">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="368" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF367">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="368" spans="1:32">
       <c r="A368">
         <v>228875</v>
       </c>
@@ -35424,10 +36528,13 @@
         <v>0</v>
       </c>
       <c r="AE368">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="369" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF368">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="369" spans="1:32">
       <c r="A369">
         <v>228875</v>
       </c>
@@ -35519,10 +36626,13 @@
         <v>0</v>
       </c>
       <c r="AE369">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="370" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF369">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="370" spans="1:32">
       <c r="A370">
         <v>229027</v>
       </c>
@@ -35614,10 +36724,13 @@
         <v>1</v>
       </c>
       <c r="AE370">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="371" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF370">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="371" spans="1:32">
       <c r="A371">
         <v>229027</v>
       </c>
@@ -35709,10 +36822,13 @@
         <v>1</v>
       </c>
       <c r="AE371">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="372" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF371">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="372" spans="1:32">
       <c r="A372">
         <v>229115</v>
       </c>
@@ -35804,10 +36920,13 @@
         <v>2</v>
       </c>
       <c r="AE372">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="373" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF372">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="373" spans="1:32">
       <c r="A373">
         <v>229115</v>
       </c>
@@ -35899,10 +37018,13 @@
         <v>0</v>
       </c>
       <c r="AE373">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="374" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF373">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="374" spans="1:32">
       <c r="A374">
         <v>230038</v>
       </c>
@@ -35994,10 +37116,13 @@
         <v>0</v>
       </c>
       <c r="AE374">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="375" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF374">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="375" spans="1:32">
       <c r="A375">
         <v>230038</v>
       </c>
@@ -36089,10 +37214,13 @@
         <v>0</v>
       </c>
       <c r="AE375">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="376" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF375">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="376" spans="1:32">
       <c r="A376">
         <v>230728</v>
       </c>
@@ -36184,10 +37312,13 @@
         <v>0</v>
       </c>
       <c r="AE376">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="377" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF376">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="377" spans="1:32">
       <c r="A377">
         <v>230728</v>
       </c>
@@ -36279,10 +37410,13 @@
         <v>0</v>
       </c>
       <c r="AE377">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="378" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF377">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="378" spans="1:32">
       <c r="A378">
         <v>230764</v>
       </c>
@@ -36374,10 +37508,13 @@
         <v>1</v>
       </c>
       <c r="AE378">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="379" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF378">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="379" spans="1:32">
       <c r="A379">
         <v>230764</v>
       </c>
@@ -36469,10 +37606,13 @@
         <v>0</v>
       </c>
       <c r="AE379">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="380" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF379">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="380" spans="1:32">
       <c r="A380">
         <v>231174</v>
       </c>
@@ -36564,10 +37704,13 @@
         <v>0</v>
       </c>
       <c r="AE380">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="381" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF380">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="381" spans="1:32">
       <c r="A381">
         <v>231624</v>
       </c>
@@ -36659,10 +37802,13 @@
         <v>1</v>
       </c>
       <c r="AE381">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="382" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF381">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="382" spans="1:32">
       <c r="A382">
         <v>231624</v>
       </c>
@@ -36754,10 +37900,13 @@
         <v>2</v>
       </c>
       <c r="AE382">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="383" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF382">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="383" spans="1:32">
       <c r="A383">
         <v>232186</v>
       </c>
@@ -36849,10 +37998,13 @@
         <v>0</v>
       </c>
       <c r="AE383">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="384" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF383">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="384" spans="1:32">
       <c r="A384">
         <v>232186</v>
       </c>
@@ -36944,10 +38096,13 @@
         <v>0</v>
       </c>
       <c r="AE384">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="385" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF384">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="385" spans="1:32">
       <c r="A385">
         <v>232265</v>
       </c>
@@ -37039,10 +38194,13 @@
         <v>0</v>
       </c>
       <c r="AE385">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="386" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF385">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="386" spans="1:32">
       <c r="A386">
         <v>232265</v>
       </c>
@@ -37134,10 +38292,13 @@
         <v>0</v>
       </c>
       <c r="AE386">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="387" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF386">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="387" spans="1:32">
       <c r="A387">
         <v>232982</v>
       </c>
@@ -37229,10 +38390,13 @@
         <v>0</v>
       </c>
       <c r="AE387">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="388" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF387">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="388" spans="1:32">
       <c r="A388">
         <v>232982</v>
       </c>
@@ -37324,10 +38488,13 @@
         <v>2</v>
       </c>
       <c r="AE388">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="389" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF388">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="389" spans="1:32">
       <c r="A389">
         <v>233921</v>
       </c>
@@ -37419,10 +38586,13 @@
         <v>4</v>
       </c>
       <c r="AE389">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="390" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF389">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="390" spans="1:32">
       <c r="A390">
         <v>233921</v>
       </c>
@@ -37514,10 +38684,13 @@
         <v>1</v>
       </c>
       <c r="AE390">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="391" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF390">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="391" spans="1:32">
       <c r="A391">
         <v>234030</v>
       </c>
@@ -37609,10 +38782,13 @@
         <v>3</v>
       </c>
       <c r="AE391">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="392" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF391">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="392" spans="1:32">
       <c r="A392">
         <v>234076</v>
       </c>
@@ -37704,10 +38880,13 @@
         <v>5</v>
       </c>
       <c r="AE392">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="393" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF392">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="393" spans="1:32">
       <c r="A393">
         <v>234076</v>
       </c>
@@ -37799,10 +38978,13 @@
         <v>2</v>
       </c>
       <c r="AE393">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="394" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF393">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="394" spans="1:32">
       <c r="A394">
         <v>234155</v>
       </c>
@@ -37894,10 +39076,13 @@
         <v>0</v>
       </c>
       <c r="AE394">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="395" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF394">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="395" spans="1:32">
       <c r="A395">
         <v>236939</v>
       </c>
@@ -37989,10 +39174,13 @@
         <v>0</v>
       </c>
       <c r="AE395">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="396" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF395">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="396" spans="1:32">
       <c r="A396">
         <v>236939</v>
       </c>
@@ -38084,10 +39272,13 @@
         <v>0</v>
       </c>
       <c r="AE396">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="397" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF396">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="397" spans="1:32">
       <c r="A397">
         <v>236948</v>
       </c>
@@ -38179,10 +39370,13 @@
         <v>0</v>
       </c>
       <c r="AE397">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="398" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF397">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="398" spans="1:32">
       <c r="A398">
         <v>236948</v>
       </c>
@@ -38274,10 +39468,13 @@
         <v>1</v>
       </c>
       <c r="AE398">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="399" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF398">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="399" spans="1:32">
       <c r="A399">
         <v>238032</v>
       </c>
@@ -38369,10 +39566,13 @@
         <v>0</v>
       </c>
       <c r="AE399">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="400" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF399">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="400" spans="1:32">
       <c r="A400">
         <v>238032</v>
       </c>
@@ -38464,10 +39664,13 @@
         <v>0</v>
       </c>
       <c r="AE400">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="401" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF400">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="401" spans="1:32">
       <c r="A401">
         <v>240444</v>
       </c>
@@ -38559,10 +39762,13 @@
         <v>2</v>
       </c>
       <c r="AE401">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="402" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF401">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="402" spans="1:32">
       <c r="A402">
         <v>240444</v>
       </c>
@@ -38654,10 +39860,13 @@
         <v>3</v>
       </c>
       <c r="AE402">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="403" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF402">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="403" spans="1:32">
       <c r="A403">
         <v>240453</v>
       </c>
@@ -38749,10 +39958,13 @@
         <v>1</v>
       </c>
       <c r="AE403">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="404" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF403">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="404" spans="1:32">
       <c r="A404">
         <v>240453</v>
       </c>
@@ -38844,10 +40056,13 @@
         <v>1</v>
       </c>
       <c r="AE404">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="405" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF404">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="405" spans="1:32">
       <c r="A405">
         <v>240727</v>
       </c>
@@ -38939,10 +40154,13 @@
         <v>0</v>
       </c>
       <c r="AE405">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="406" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF405">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="406" spans="1:32">
       <c r="A406">
         <v>240727</v>
       </c>
@@ -39034,10 +40252,13 @@
         <v>0</v>
       </c>
       <c r="AE406">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="407" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF406">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="407" spans="1:32">
       <c r="A407">
         <v>243197</v>
       </c>
@@ -39129,10 +40350,13 @@
         <v>1</v>
       </c>
       <c r="AE407">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="408" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF407">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="408" spans="1:32">
       <c r="A408">
         <v>243744</v>
       </c>
@@ -39224,10 +40448,13 @@
         <v>0</v>
       </c>
       <c r="AE408">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="409" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF408">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="409" spans="1:32">
       <c r="A409">
         <v>243744</v>
       </c>
@@ -39319,10 +40546,13 @@
         <v>2</v>
       </c>
       <c r="AE409">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="410" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF409">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="410" spans="1:32">
       <c r="A410">
         <v>243780</v>
       </c>
@@ -39414,10 +40644,13 @@
         <v>1</v>
       </c>
       <c r="AE410">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="411" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF410">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="411" spans="1:32">
       <c r="A411">
         <v>243780</v>
       </c>
@@ -39509,6 +40742,9 @@
         <v>3</v>
       </c>
       <c r="AE411">
+        <v>1</v>
+      </c>
+      <c r="AF411">
         <v>2011</v>
       </c>
     </row>
